--- a/Hoàng/2025/T5/BIDV QUẢNG NAM (62-2025)/DANH MỤC BIDV QUẢNG NAM - điều chỉnh DM FINAL.xlsx
+++ b/Hoàng/2025/T5/BIDV QUẢNG NAM (62-2025)/DANH MỤC BIDV QUẢNG NAM - điều chỉnh DM FINAL.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\BIDV QUẢNG NAM (62-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E480464C-2437-4C9F-9CDF-D83D62C18B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FD75CD-1687-4CCB-B556-D5245D1CD8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIX NĂM SINH" sheetId="11" r:id="rId1"/>
     <sheet name="TN" sheetId="3" r:id="rId2"/>
     <sheet name="BẢNG CHỌN" sheetId="8" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="12" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="13" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId5"/>
+    <sheet name="TÌNH KHÁM NGÀY 26.05" sheetId="14" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BẢNG CHỌN'!$A$3:$DV$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FIX NĂM SINH'!$A$3:$E$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'TÌNH KHÁM NGÀY 26.05'!$A$1:$F$81</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">TN!$A$1:$F$233</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">TN!$32:$32</definedName>
   </definedNames>
@@ -78,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3310" uniqueCount="758">
   <si>
     <t>Ghi chú</t>
   </si>
@@ -2339,9 +2342,6 @@
     <t>Mức phí khám</t>
   </si>
   <si>
-    <t>XUẤT HOÁ ĐƠN LẺ PHẦN VƯỢT HẠN MỨC</t>
-  </si>
-  <si>
     <t>XUẤT HOÁ ĐƠN LẺ PHẦN NỘI SOI DẠ DÀY</t>
   </si>
   <si>
@@ -2360,9 +2360,6 @@
     <t>THỜI GIAN ĐI KHÁM</t>
   </si>
   <si>
-    <t>XUÂT HOÁ ĐƠN PHẦN HẠN MỨC THEO THÔNG TIN CCCD ĐÃ LƯU</t>
-  </si>
-  <si>
     <t>XUẤT HOÁ ĐƠN PHẦN CHÊNH LỆCH, ĐÃ XUẤT HOÁ ĐƠN LẺ</t>
   </si>
   <si>
@@ -2372,7 +2369,19 @@
     <t>ĐÃ XUẤT HOÁ ĐƠN LẺ 1.968.000 đồng (NỘI SOI) - HUỶ HOÁ ĐƠN NÀY, CHỐT CP, LÀM BẢNG KÊ CHI TIẾT RIÊNG ĐỐI VỚI TH NÀY ( CÔNG TY THANH TOÁN ĐÚNG HẠN MỨC  3,5 triệu - KHÁCH HÀNG CÒN BAO NHIÊU … )</t>
   </si>
   <si>
-    <t>XUẤT HOÁ ĐƠN LẺ PHẦN NỘI SOI ( KHỎI CẦN, CHỈ CẦN GỬI BẢNG KÊ CHI PHÍ )</t>
+    <t xml:space="preserve">XUẤT HOÁ ĐƠN LẺ PHẦN VƯỢT HẠN MỨC (KHÔNG VƯỢT HẠN MỨC) </t>
+  </si>
+  <si>
+    <t>XUÂT HOÁ ĐƠN PHẦN HẠN MỨC THEO THÔNG TIN CCCD ĐÃ LƯU (KHÔNG VƯỢT HẠN MỨC)</t>
+  </si>
+  <si>
+    <t>XUẤT HOÁ ĐƠN LẺ PHẦN NỘI SOI ( KHỎI CẦN XUẤT LẺ, CHỈ CẦN GỬI BẢNG KÊ CHI PHÍ )</t>
+  </si>
+  <si>
+    <t>Ngày Khám</t>
+  </si>
+  <si>
+    <t>XOÁ DANH MỤC NỘI SOI</t>
   </si>
 </sst>
 </file>
@@ -3064,7 +3073,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3818,6 +3827,14 @@
     <xf numFmtId="165" fontId="24" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="25" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="25" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="25" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="25" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="25" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3833,6 +3850,108 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3842,11 +3961,8 @@
     <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3857,11 +3973,47 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3884,18 +4036,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3904,132 +4047,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="24" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4057,7 +4074,7 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4065,6 +4082,24 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4501,28 +4536,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="295" t="s">
         <v>260</v>
       </c>
-      <c r="B1" s="290" t="s">
+      <c r="B1" s="296" t="s">
         <v>654</v>
       </c>
-      <c r="C1" s="289" t="s">
+      <c r="C1" s="295" t="s">
         <v>421</v>
       </c>
-      <c r="D1" s="289" t="s">
+      <c r="D1" s="295" t="s">
         <v>422</v>
       </c>
-      <c r="E1" s="290" t="s">
+      <c r="E1" s="296" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="129" customFormat="1" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="289"/>
-      <c r="B2" s="291"/>
-      <c r="C2" s="289"/>
-      <c r="D2" s="289"/>
-      <c r="E2" s="291"/>
+      <c r="A2" s="295"/>
+      <c r="B2" s="297"/>
+      <c r="C2" s="295"/>
+      <c r="D2" s="295"/>
+      <c r="E2" s="297"/>
       <c r="M2" s="212"/>
     </row>
     <row r="3" spans="1:14" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7753,13 +7788,13 @@
       </c>
     </row>
     <row r="84" spans="1:14" s="137" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="287" t="s">
+      <c r="A84" s="293" t="s">
         <v>414</v>
       </c>
-      <c r="B84" s="288"/>
-      <c r="C84" s="288"/>
-      <c r="D84" s="288"/>
-      <c r="E84" s="288"/>
+      <c r="B84" s="294"/>
+      <c r="C84" s="294"/>
+      <c r="D84" s="294"/>
+      <c r="E84" s="294"/>
       <c r="M84" s="213"/>
     </row>
   </sheetData>
@@ -7773,7 +7808,7 @@
     <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7800,43 +7835,43 @@
       <c r="A1" s="22"/>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
-      <c r="D1" s="337" t="s">
+      <c r="D1" s="299" t="s">
         <v>313</v>
       </c>
-      <c r="E1" s="337"/>
-      <c r="F1" s="337"/>
+      <c r="E1" s="299"/>
+      <c r="F1" s="299"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
-      <c r="D2" s="338"/>
-      <c r="E2" s="338"/>
-      <c r="F2" s="338"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="300"/>
+      <c r="F2" s="300"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
-      <c r="F3" s="338"/>
+      <c r="D3" s="300"/>
+      <c r="E3" s="300"/>
+      <c r="F3" s="300"/>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="338"/>
-      <c r="E4" s="338"/>
-      <c r="F4" s="338"/>
+      <c r="D4" s="300"/>
+      <c r="E4" s="300"/>
+      <c r="F4" s="300"/>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="338"/>
-      <c r="E5" s="338"/>
-      <c r="F5" s="338"/>
+      <c r="D5" s="300"/>
+      <c r="E5" s="300"/>
+      <c r="F5" s="300"/>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
@@ -7847,14 +7882,14 @@
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="339" t="s">
+      <c r="A7" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="339"/>
-      <c r="C7" s="339"/>
-      <c r="D7" s="339"/>
-      <c r="E7" s="339"/>
-      <c r="F7" s="339"/>
+      <c r="B7" s="301"/>
+      <c r="C7" s="301"/>
+      <c r="D7" s="301"/>
+      <c r="E7" s="301"/>
+      <c r="F7" s="301"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -7876,27 +7911,27 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
-      <c r="B9" s="345" t="s">
+      <c r="B9" s="309" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="345"/>
-      <c r="D9" s="345"/>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="C9" s="309"/>
+      <c r="D9" s="309"/>
+      <c r="E9" s="309"/>
+      <c r="F9" s="309"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="346" t="s">
+      <c r="A10" s="310" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="347"/>
-      <c r="C10" s="347"/>
-      <c r="D10" s="347"/>
-      <c r="E10" s="347"/>
-      <c r="F10" s="348"/>
+      <c r="B10" s="311"/>
+      <c r="C10" s="311"/>
+      <c r="D10" s="311"/>
+      <c r="E10" s="311"/>
+      <c r="F10" s="312"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -7904,12 +7939,12 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="349"/>
-      <c r="B11" s="350"/>
-      <c r="C11" s="350"/>
-      <c r="D11" s="350"/>
-      <c r="E11" s="350"/>
-      <c r="F11" s="351"/>
+      <c r="A11" s="313"/>
+      <c r="B11" s="314"/>
+      <c r="C11" s="314"/>
+      <c r="D11" s="314"/>
+      <c r="E11" s="314"/>
+      <c r="F11" s="315"/>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
@@ -7928,10 +7963,10 @@
       <c r="A13" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="B13" s="343" t="s">
+      <c r="B13" s="307" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="343"/>
+      <c r="C13" s="307"/>
       <c r="D13" s="33" t="s">
         <v>4</v>
       </c>
@@ -7944,77 +7979,77 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="352">
+      <c r="A14" s="316">
         <v>1</v>
       </c>
-      <c r="B14" s="295" t="s">
+      <c r="B14" s="319" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="352" t="s">
+      <c r="C14" s="316" t="s">
         <v>328</v>
       </c>
       <c r="D14" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="332">
+      <c r="E14" s="322">
         <v>200000</v>
       </c>
-      <c r="F14" s="355"/>
+      <c r="F14" s="325"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="353"/>
-      <c r="B15" s="316"/>
-      <c r="C15" s="353"/>
+      <c r="A15" s="317"/>
+      <c r="B15" s="320"/>
+      <c r="C15" s="317"/>
       <c r="D15" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="333"/>
-      <c r="F15" s="356"/>
+      <c r="E15" s="323"/>
+      <c r="F15" s="326"/>
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="353"/>
-      <c r="B16" s="316"/>
-      <c r="C16" s="353"/>
+      <c r="A16" s="317"/>
+      <c r="B16" s="320"/>
+      <c r="C16" s="317"/>
       <c r="D16" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="333"/>
-      <c r="F16" s="356"/>
+      <c r="E16" s="323"/>
+      <c r="F16" s="326"/>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A17" s="353"/>
-      <c r="B17" s="316"/>
-      <c r="C17" s="353"/>
+      <c r="A17" s="317"/>
+      <c r="B17" s="320"/>
+      <c r="C17" s="317"/>
       <c r="D17" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="333"/>
-      <c r="F17" s="356"/>
+      <c r="E17" s="323"/>
+      <c r="F17" s="326"/>
       <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A18" s="353"/>
-      <c r="B18" s="316"/>
-      <c r="C18" s="353"/>
+      <c r="A18" s="317"/>
+      <c r="B18" s="320"/>
+      <c r="C18" s="317"/>
       <c r="D18" s="36" t="s">
         <v>413</v>
       </c>
-      <c r="E18" s="333"/>
-      <c r="F18" s="356"/>
+      <c r="E18" s="323"/>
+      <c r="F18" s="326"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="354"/>
-      <c r="B19" s="296"/>
-      <c r="C19" s="354"/>
+      <c r="A19" s="318"/>
+      <c r="B19" s="321"/>
+      <c r="C19" s="318"/>
       <c r="D19" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="334"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="324"/>
+      <c r="F19" s="327"/>
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -8097,7 +8132,7 @@
       <c r="A24" s="38">
         <v>6</v>
       </c>
-      <c r="B24" s="336" t="s">
+      <c r="B24" s="298" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="42" t="s">
@@ -8106,10 +8141,10 @@
       <c r="D24" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="342">
+      <c r="E24" s="304">
         <v>60000</v>
       </c>
-      <c r="F24" s="300" t="s">
+      <c r="F24" s="305" t="s">
         <v>383</v>
       </c>
       <c r="G24" s="12"/>
@@ -8118,15 +8153,15 @@
       <c r="A25" s="38">
         <v>7</v>
       </c>
-      <c r="B25" s="336"/>
+      <c r="B25" s="298"/>
       <c r="C25" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="342"/>
-      <c r="F25" s="301"/>
+      <c r="E25" s="304"/>
+      <c r="F25" s="306"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -8166,12 +8201,12 @@
       <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="340" t="s">
+      <c r="A28" s="302" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="344"/>
-      <c r="C28" s="344"/>
-      <c r="D28" s="341"/>
+      <c r="B28" s="308"/>
+      <c r="C28" s="308"/>
+      <c r="D28" s="303"/>
       <c r="E28" s="34">
         <f>SUM(E14:E27)</f>
         <v>564000</v>
@@ -8212,10 +8247,10 @@
       <c r="A32" s="63" t="s">
         <v>260</v>
       </c>
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="341"/>
+      <c r="C32" s="303"/>
       <c r="D32" s="63" t="s">
         <v>4</v>
       </c>
@@ -8318,7 +8353,7 @@
       <c r="A38" s="38">
         <v>5</v>
       </c>
-      <c r="B38" s="295" t="s">
+      <c r="B38" s="319" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="42" t="s">
@@ -8339,7 +8374,7 @@
       <c r="A39" s="38">
         <v>6</v>
       </c>
-      <c r="B39" s="296"/>
+      <c r="B39" s="321"/>
       <c r="C39" s="42" t="s">
         <v>275</v>
       </c>
@@ -8358,7 +8393,7 @@
       <c r="A40" s="38">
         <v>7</v>
       </c>
-      <c r="B40" s="309" t="s">
+      <c r="B40" s="339" t="s">
         <v>61</v>
       </c>
       <c r="C40" s="42" t="s">
@@ -8370,7 +8405,7 @@
       <c r="E40" s="72">
         <v>41000</v>
       </c>
-      <c r="F40" s="297" t="s">
+      <c r="F40" s="336" t="s">
         <v>379</v>
       </c>
       <c r="G40" s="12"/>
@@ -8379,7 +8414,7 @@
       <c r="A41" s="38">
         <v>8</v>
       </c>
-      <c r="B41" s="309"/>
+      <c r="B41" s="339"/>
       <c r="C41" s="42" t="s">
         <v>64</v>
       </c>
@@ -8389,14 +8424,14 @@
       <c r="E41" s="72">
         <v>59000</v>
       </c>
-      <c r="F41" s="298"/>
+      <c r="F41" s="337"/>
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>9</v>
       </c>
-      <c r="B42" s="309"/>
+      <c r="B42" s="339"/>
       <c r="C42" s="42" t="s">
         <v>66</v>
       </c>
@@ -8406,14 +8441,14 @@
       <c r="E42" s="72">
         <v>59000</v>
       </c>
-      <c r="F42" s="298"/>
+      <c r="F42" s="337"/>
       <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>10</v>
       </c>
-      <c r="B43" s="309"/>
+      <c r="B43" s="339"/>
       <c r="C43" s="42" t="s">
         <v>68</v>
       </c>
@@ -8423,14 +8458,14 @@
       <c r="E43" s="72">
         <v>47000</v>
       </c>
-      <c r="F43" s="298"/>
+      <c r="F43" s="337"/>
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>11</v>
       </c>
-      <c r="B44" s="309"/>
+      <c r="B44" s="339"/>
       <c r="C44" s="42" t="s">
         <v>70</v>
       </c>
@@ -8440,7 +8475,7 @@
       <c r="E44" s="72">
         <v>41000</v>
       </c>
-      <c r="F44" s="299"/>
+      <c r="F44" s="338"/>
       <c r="G44" s="12"/>
     </row>
     <row r="45" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -8466,7 +8501,7 @@
       <c r="A46" s="38">
         <v>13</v>
       </c>
-      <c r="B46" s="295" t="s">
+      <c r="B46" s="319" t="s">
         <v>278</v>
       </c>
       <c r="C46" s="36" t="s">
@@ -8478,7 +8513,7 @@
       <c r="E46" s="75">
         <v>62000</v>
       </c>
-      <c r="F46" s="297" t="s">
+      <c r="F46" s="336" t="s">
         <v>380</v>
       </c>
       <c r="G46" s="12"/>
@@ -8487,7 +8522,7 @@
       <c r="A47" s="38">
         <v>14</v>
       </c>
-      <c r="B47" s="316"/>
+      <c r="B47" s="320"/>
       <c r="C47" s="36" t="s">
         <v>197</v>
       </c>
@@ -8497,14 +8532,14 @@
       <c r="E47" s="75">
         <v>165000</v>
       </c>
-      <c r="F47" s="298"/>
+      <c r="F47" s="337"/>
       <c r="G47" s="12"/>
     </row>
     <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>15</v>
       </c>
-      <c r="B48" s="296"/>
+      <c r="B48" s="321"/>
       <c r="C48" s="36" t="s">
         <v>202</v>
       </c>
@@ -8514,14 +8549,14 @@
       <c r="E48" s="75">
         <v>116000</v>
       </c>
-      <c r="F48" s="299"/>
+      <c r="F48" s="338"/>
       <c r="G48" s="12"/>
     </row>
     <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>16</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="319" t="s">
         <v>273</v>
       </c>
       <c r="C49" s="36" t="s">
@@ -8540,7 +8575,7 @@
       <c r="A50" s="38">
         <v>17</v>
       </c>
-      <c r="B50" s="316"/>
+      <c r="B50" s="320"/>
       <c r="C50" s="36" t="s">
         <v>270</v>
       </c>
@@ -8550,7 +8585,7 @@
       <c r="E50" s="75">
         <v>130000</v>
       </c>
-      <c r="F50" s="297" t="s">
+      <c r="F50" s="336" t="s">
         <v>380</v>
       </c>
       <c r="G50" s="12"/>
@@ -8559,7 +8594,7 @@
       <c r="A51" s="38">
         <v>18</v>
       </c>
-      <c r="B51" s="316"/>
+      <c r="B51" s="320"/>
       <c r="C51" s="36" t="s">
         <v>271</v>
       </c>
@@ -8569,14 +8604,14 @@
       <c r="E51" s="75">
         <v>120000</v>
       </c>
-      <c r="F51" s="298"/>
+      <c r="F51" s="337"/>
       <c r="G51" s="12"/>
     </row>
     <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>19</v>
       </c>
-      <c r="B52" s="296"/>
+      <c r="B52" s="321"/>
       <c r="C52" s="36" t="s">
         <v>272</v>
       </c>
@@ -8586,7 +8621,7 @@
       <c r="E52" s="75">
         <v>282000</v>
       </c>
-      <c r="F52" s="299"/>
+      <c r="F52" s="338"/>
       <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -8612,7 +8647,7 @@
       <c r="A54" s="38">
         <v>21</v>
       </c>
-      <c r="B54" s="311" t="s">
+      <c r="B54" s="342" t="s">
         <v>131</v>
       </c>
       <c r="C54" s="36" t="s">
@@ -8624,7 +8659,7 @@
       <c r="E54" s="75">
         <v>71000</v>
       </c>
-      <c r="F54" s="300" t="s">
+      <c r="F54" s="305" t="s">
         <v>382</v>
       </c>
       <c r="G54" s="12"/>
@@ -8633,7 +8668,7 @@
       <c r="A55" s="38">
         <v>22</v>
       </c>
-      <c r="B55" s="312"/>
+      <c r="B55" s="344"/>
       <c r="C55" s="36" t="s">
         <v>134</v>
       </c>
@@ -8643,7 +8678,7 @@
       <c r="E55" s="71">
         <v>138000</v>
       </c>
-      <c r="F55" s="301"/>
+      <c r="F55" s="306"/>
       <c r="G55" s="12"/>
     </row>
     <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -8669,7 +8704,7 @@
       <c r="A57" s="38">
         <v>24</v>
       </c>
-      <c r="B57" s="310" t="s">
+      <c r="B57" s="360" t="s">
         <v>206</v>
       </c>
       <c r="C57" s="36" t="s">
@@ -8681,7 +8716,7 @@
       <c r="E57" s="75">
         <v>30000</v>
       </c>
-      <c r="F57" s="302" t="s">
+      <c r="F57" s="353" t="s">
         <v>384</v>
       </c>
       <c r="G57" s="13"/>
@@ -8690,7 +8725,7 @@
       <c r="A58" s="38">
         <v>25</v>
       </c>
-      <c r="B58" s="310"/>
+      <c r="B58" s="360"/>
       <c r="C58" s="36" t="s">
         <v>279</v>
       </c>
@@ -8700,16 +8735,16 @@
       <c r="E58" s="75">
         <v>20000</v>
       </c>
-      <c r="F58" s="303"/>
+      <c r="F58" s="354"/>
       <c r="G58" s="13"/>
     </row>
     <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="292" t="s">
+      <c r="A59" s="332" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="293"/>
-      <c r="C59" s="293"/>
-      <c r="D59" s="294"/>
+      <c r="B59" s="333"/>
+      <c r="C59" s="333"/>
+      <c r="D59" s="334"/>
       <c r="E59" s="69"/>
       <c r="F59" s="70"/>
       <c r="G59" s="12"/>
@@ -8718,7 +8753,7 @@
       <c r="A60" s="38">
         <v>26</v>
       </c>
-      <c r="B60" s="304" t="s">
+      <c r="B60" s="355" t="s">
         <v>261</v>
       </c>
       <c r="C60" s="76" t="s">
@@ -8737,7 +8772,7 @@
       <c r="A61" s="38">
         <v>27</v>
       </c>
-      <c r="B61" s="305"/>
+      <c r="B61" s="356"/>
       <c r="C61" s="76" t="s">
         <v>84</v>
       </c>
@@ -8754,7 +8789,7 @@
       <c r="A62" s="38">
         <v>28</v>
       </c>
-      <c r="B62" s="305"/>
+      <c r="B62" s="356"/>
       <c r="C62" s="76" t="s">
         <v>86</v>
       </c>
@@ -8771,7 +8806,7 @@
       <c r="A63" s="38">
         <v>29</v>
       </c>
-      <c r="B63" s="305"/>
+      <c r="B63" s="356"/>
       <c r="C63" s="76" t="s">
         <v>80</v>
       </c>
@@ -8788,7 +8823,7 @@
       <c r="A64" s="38">
         <v>30</v>
       </c>
-      <c r="B64" s="305"/>
+      <c r="B64" s="356"/>
       <c r="C64" s="76" t="s">
         <v>94</v>
       </c>
@@ -8805,7 +8840,7 @@
       <c r="A65" s="38">
         <v>31</v>
       </c>
-      <c r="B65" s="305"/>
+      <c r="B65" s="356"/>
       <c r="C65" s="76" t="s">
         <v>81</v>
       </c>
@@ -8822,7 +8857,7 @@
       <c r="A66" s="38">
         <v>32</v>
       </c>
-      <c r="B66" s="305"/>
+      <c r="B66" s="356"/>
       <c r="C66" s="76" t="s">
         <v>83</v>
       </c>
@@ -8841,7 +8876,7 @@
       <c r="A67" s="38">
         <v>33</v>
       </c>
-      <c r="B67" s="305"/>
+      <c r="B67" s="356"/>
       <c r="C67" s="80" t="s">
         <v>235</v>
       </c>
@@ -8858,7 +8893,7 @@
       <c r="A68" s="38">
         <v>34</v>
       </c>
-      <c r="B68" s="305"/>
+      <c r="B68" s="356"/>
       <c r="C68" s="76" t="s">
         <v>74</v>
       </c>
@@ -8877,7 +8912,7 @@
       <c r="A69" s="38">
         <v>35</v>
       </c>
-      <c r="B69" s="305"/>
+      <c r="B69" s="356"/>
       <c r="C69" s="76" t="s">
         <v>76</v>
       </c>
@@ -8894,7 +8929,7 @@
       <c r="A70" s="38">
         <v>36</v>
       </c>
-      <c r="B70" s="305"/>
+      <c r="B70" s="356"/>
       <c r="C70" s="76" t="s">
         <v>78</v>
       </c>
@@ -8911,7 +8946,7 @@
       <c r="A71" s="38">
         <v>37</v>
       </c>
-      <c r="B71" s="305"/>
+      <c r="B71" s="356"/>
       <c r="C71" s="76" t="s">
         <v>88</v>
       </c>
@@ -8928,7 +8963,7 @@
       <c r="A72" s="38">
         <v>38</v>
       </c>
-      <c r="B72" s="306"/>
+      <c r="B72" s="357"/>
       <c r="C72" s="76" t="s">
         <v>96</v>
       </c>
@@ -8945,19 +8980,19 @@
       <c r="A73" s="38">
         <v>39</v>
       </c>
-      <c r="B73" s="304" t="s">
+      <c r="B73" s="355" t="s">
         <v>91</v>
       </c>
       <c r="C73" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="D73" s="313" t="s">
+      <c r="D73" s="361" t="s">
         <v>398</v>
       </c>
       <c r="E73" s="78">
         <v>137000</v>
       </c>
-      <c r="F73" s="297" t="s">
+      <c r="F73" s="336" t="s">
         <v>381</v>
       </c>
       <c r="G73" s="13"/>
@@ -8966,43 +9001,43 @@
       <c r="A74" s="38">
         <v>40</v>
       </c>
-      <c r="B74" s="305"/>
+      <c r="B74" s="356"/>
       <c r="C74" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="D74" s="314"/>
+      <c r="D74" s="362"/>
       <c r="E74" s="78">
         <v>137000</v>
       </c>
-      <c r="F74" s="298"/>
+      <c r="F74" s="337"/>
       <c r="G74" s="13"/>
     </row>
     <row r="75" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A75" s="38">
         <v>41</v>
       </c>
-      <c r="B75" s="306"/>
+      <c r="B75" s="357"/>
       <c r="C75" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="D75" s="315"/>
+      <c r="D75" s="363"/>
       <c r="E75" s="78">
         <v>208000</v>
       </c>
-      <c r="F75" s="299"/>
+      <c r="F75" s="338"/>
       <c r="G75" s="13"/>
     </row>
     <row r="76" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>42</v>
       </c>
-      <c r="B76" s="304" t="s">
+      <c r="B76" s="355" t="s">
         <v>399</v>
       </c>
       <c r="C76" s="76" t="s">
         <v>400</v>
       </c>
-      <c r="D76" s="307" t="s">
+      <c r="D76" s="358" t="s">
         <v>402</v>
       </c>
       <c r="E76" s="78">
@@ -9015,11 +9050,11 @@
       <c r="A77" s="38">
         <v>43</v>
       </c>
-      <c r="B77" s="305"/>
+      <c r="B77" s="356"/>
       <c r="C77" s="76" t="s">
         <v>401</v>
       </c>
-      <c r="D77" s="308"/>
+      <c r="D77" s="359"/>
       <c r="E77" s="78">
         <v>323000</v>
       </c>
@@ -9030,7 +9065,7 @@
       <c r="A78" s="38">
         <v>44</v>
       </c>
-      <c r="B78" s="305"/>
+      <c r="B78" s="356"/>
       <c r="C78" s="76" t="s">
         <v>404</v>
       </c>
@@ -9047,7 +9082,7 @@
       <c r="A79" s="38">
         <v>45</v>
       </c>
-      <c r="B79" s="306"/>
+      <c r="B79" s="357"/>
       <c r="C79" s="76" t="s">
         <v>405</v>
       </c>
@@ -9061,12 +9096,12 @@
       <c r="G79" s="13"/>
     </row>
     <row r="80" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="292" t="s">
+      <c r="A80" s="332" t="s">
         <v>208</v>
       </c>
-      <c r="B80" s="293"/>
-      <c r="C80" s="293"/>
-      <c r="D80" s="294"/>
+      <c r="B80" s="333"/>
+      <c r="C80" s="333"/>
+      <c r="D80" s="334"/>
       <c r="E80" s="69"/>
       <c r="F80" s="70"/>
       <c r="G80" s="13"/>
@@ -9075,7 +9110,7 @@
       <c r="A81" s="38">
         <v>46</v>
       </c>
-      <c r="B81" s="309" t="s">
+      <c r="B81" s="339" t="s">
         <v>98</v>
       </c>
       <c r="C81" s="36" t="s">
@@ -9094,7 +9129,7 @@
       <c r="A82" s="38">
         <v>47</v>
       </c>
-      <c r="B82" s="309"/>
+      <c r="B82" s="339"/>
       <c r="C82" s="36" t="s">
         <v>101</v>
       </c>
@@ -9111,7 +9146,7 @@
       <c r="A83" s="38">
         <v>48</v>
       </c>
-      <c r="B83" s="309"/>
+      <c r="B83" s="339"/>
       <c r="C83" s="36" t="s">
         <v>103</v>
       </c>
@@ -9130,7 +9165,7 @@
       <c r="A84" s="38">
         <v>49</v>
       </c>
-      <c r="B84" s="309"/>
+      <c r="B84" s="339"/>
       <c r="C84" s="36" t="s">
         <v>106</v>
       </c>
@@ -9149,7 +9184,7 @@
       <c r="A85" s="38">
         <v>50</v>
       </c>
-      <c r="B85" s="309"/>
+      <c r="B85" s="339"/>
       <c r="C85" s="36" t="s">
         <v>407</v>
       </c>
@@ -9166,7 +9201,7 @@
       <c r="A86" s="38">
         <v>51</v>
       </c>
-      <c r="B86" s="309"/>
+      <c r="B86" s="339"/>
       <c r="C86" s="36" t="s">
         <v>108</v>
       </c>
@@ -9185,7 +9220,7 @@
       <c r="A87" s="38">
         <v>52</v>
       </c>
-      <c r="B87" s="309"/>
+      <c r="B87" s="339"/>
       <c r="C87" s="36" t="s">
         <v>111</v>
       </c>
@@ -9204,7 +9239,7 @@
       <c r="A88" s="38">
         <v>53</v>
       </c>
-      <c r="B88" s="309"/>
+      <c r="B88" s="339"/>
       <c r="C88" s="36" t="s">
         <v>114</v>
       </c>
@@ -9223,7 +9258,7 @@
       <c r="A89" s="38">
         <v>54</v>
       </c>
-      <c r="B89" s="309" t="s">
+      <c r="B89" s="339" t="s">
         <v>117</v>
       </c>
       <c r="C89" s="36" t="s">
@@ -9242,7 +9277,7 @@
       <c r="A90" s="38">
         <v>55</v>
       </c>
-      <c r="B90" s="309"/>
+      <c r="B90" s="339"/>
       <c r="C90" s="36" t="s">
         <v>120</v>
       </c>
@@ -9259,7 +9294,7 @@
       <c r="A91" s="38">
         <v>56</v>
       </c>
-      <c r="B91" s="311" t="s">
+      <c r="B91" s="342" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="36" t="s">
@@ -9278,7 +9313,7 @@
       <c r="A92" s="38">
         <v>57</v>
       </c>
-      <c r="B92" s="319"/>
+      <c r="B92" s="343"/>
       <c r="C92" s="36" t="s">
         <v>390</v>
       </c>
@@ -9295,7 +9330,7 @@
       <c r="A93" s="38">
         <v>58</v>
       </c>
-      <c r="B93" s="312"/>
+      <c r="B93" s="344"/>
       <c r="C93" s="36" t="s">
         <v>126</v>
       </c>
@@ -9309,12 +9344,12 @@
       <c r="G93" s="12"/>
     </row>
     <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="292" t="s">
+      <c r="A94" s="332" t="s">
         <v>262</v>
       </c>
-      <c r="B94" s="293"/>
-      <c r="C94" s="293"/>
-      <c r="D94" s="294"/>
+      <c r="B94" s="333"/>
+      <c r="C94" s="333"/>
+      <c r="D94" s="334"/>
       <c r="E94" s="83"/>
       <c r="F94" s="70"/>
       <c r="G94" s="12"/>
@@ -9323,7 +9358,7 @@
       <c r="A95" s="38">
         <v>59</v>
       </c>
-      <c r="B95" s="311" t="s">
+      <c r="B95" s="342" t="s">
         <v>241</v>
       </c>
       <c r="C95" s="36" t="s">
@@ -9342,7 +9377,7 @@
       <c r="A96" s="38">
         <v>60</v>
       </c>
-      <c r="B96" s="312"/>
+      <c r="B96" s="344"/>
       <c r="C96" s="36" t="s">
         <v>240</v>
       </c>
@@ -9359,7 +9394,7 @@
       <c r="A97" s="38">
         <v>61</v>
       </c>
-      <c r="B97" s="311" t="s">
+      <c r="B97" s="342" t="s">
         <v>244</v>
       </c>
       <c r="C97" s="36" t="s">
@@ -9376,7 +9411,7 @@
       <c r="A98" s="38">
         <v>62</v>
       </c>
-      <c r="B98" s="312"/>
+      <c r="B98" s="344"/>
       <c r="C98" s="36" t="s">
         <v>243</v>
       </c>
@@ -9410,7 +9445,7 @@
       <c r="A100" s="38">
         <v>64</v>
       </c>
-      <c r="B100" s="311" t="s">
+      <c r="B100" s="342" t="s">
         <v>259</v>
       </c>
       <c r="C100" s="36" t="s">
@@ -9427,7 +9462,7 @@
       <c r="A101" s="38">
         <v>65</v>
       </c>
-      <c r="B101" s="319"/>
+      <c r="B101" s="343"/>
       <c r="C101" s="36" t="s">
         <v>246</v>
       </c>
@@ -9442,7 +9477,7 @@
       <c r="A102" s="38">
         <v>66</v>
       </c>
-      <c r="B102" s="319"/>
+      <c r="B102" s="343"/>
       <c r="C102" s="36" t="s">
         <v>247</v>
       </c>
@@ -9457,7 +9492,7 @@
       <c r="A103" s="38">
         <v>67</v>
       </c>
-      <c r="B103" s="319"/>
+      <c r="B103" s="343"/>
       <c r="C103" s="36" t="s">
         <v>248</v>
       </c>
@@ -9472,7 +9507,7 @@
       <c r="A104" s="38">
         <v>68</v>
       </c>
-      <c r="B104" s="319"/>
+      <c r="B104" s="343"/>
       <c r="C104" s="36" t="s">
         <v>249</v>
       </c>
@@ -9487,7 +9522,7 @@
       <c r="A105" s="38">
         <v>69</v>
       </c>
-      <c r="B105" s="319"/>
+      <c r="B105" s="343"/>
       <c r="C105" s="36" t="s">
         <v>250</v>
       </c>
@@ -9502,7 +9537,7 @@
       <c r="A106" s="38">
         <v>70</v>
       </c>
-      <c r="B106" s="319"/>
+      <c r="B106" s="343"/>
       <c r="C106" s="36" t="s">
         <v>251</v>
       </c>
@@ -9517,7 +9552,7 @@
       <c r="A107" s="38">
         <v>71</v>
       </c>
-      <c r="B107" s="319"/>
+      <c r="B107" s="343"/>
       <c r="C107" s="36" t="s">
         <v>252</v>
       </c>
@@ -9532,7 +9567,7 @@
       <c r="A108" s="38">
         <v>72</v>
       </c>
-      <c r="B108" s="319"/>
+      <c r="B108" s="343"/>
       <c r="C108" s="36" t="s">
         <v>253</v>
       </c>
@@ -9547,7 +9582,7 @@
       <c r="A109" s="38">
         <v>73</v>
       </c>
-      <c r="B109" s="319"/>
+      <c r="B109" s="343"/>
       <c r="C109" s="36" t="s">
         <v>254</v>
       </c>
@@ -9562,7 +9597,7 @@
       <c r="A110" s="38">
         <v>74</v>
       </c>
-      <c r="B110" s="319"/>
+      <c r="B110" s="343"/>
       <c r="C110" s="36" t="s">
         <v>255</v>
       </c>
@@ -9577,7 +9612,7 @@
       <c r="A111" s="38">
         <v>75</v>
       </c>
-      <c r="B111" s="319"/>
+      <c r="B111" s="343"/>
       <c r="C111" s="36" t="s">
         <v>256</v>
       </c>
@@ -9592,7 +9627,7 @@
       <c r="A112" s="38">
         <v>76</v>
       </c>
-      <c r="B112" s="319"/>
+      <c r="B112" s="343"/>
       <c r="C112" s="36" t="s">
         <v>257</v>
       </c>
@@ -9607,7 +9642,7 @@
       <c r="A113" s="38">
         <v>77</v>
       </c>
-      <c r="B113" s="312"/>
+      <c r="B113" s="344"/>
       <c r="C113" s="36" t="s">
         <v>258</v>
       </c>
@@ -9619,12 +9654,12 @@
       <c r="G113" s="12"/>
     </row>
     <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="292" t="s">
+      <c r="A114" s="332" t="s">
         <v>227</v>
       </c>
-      <c r="B114" s="293"/>
-      <c r="C114" s="293"/>
-      <c r="D114" s="294"/>
+      <c r="B114" s="333"/>
+      <c r="C114" s="333"/>
+      <c r="D114" s="334"/>
       <c r="E114" s="69"/>
       <c r="F114" s="70"/>
       <c r="G114" s="12"/>
@@ -9668,12 +9703,12 @@
       <c r="G116" s="12"/>
     </row>
     <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="320" t="s">
+      <c r="A117" s="329" t="s">
         <v>263</v>
       </c>
-      <c r="B117" s="320"/>
-      <c r="C117" s="320"/>
-      <c r="D117" s="320"/>
+      <c r="B117" s="329"/>
+      <c r="C117" s="329"/>
+      <c r="D117" s="329"/>
       <c r="E117" s="84"/>
       <c r="F117" s="70"/>
       <c r="G117" s="12"/>
@@ -9682,7 +9717,7 @@
       <c r="A118" s="38">
         <v>80</v>
       </c>
-      <c r="B118" s="326" t="s">
+      <c r="B118" s="350" t="s">
         <v>205</v>
       </c>
       <c r="C118" s="37" t="s">
@@ -9701,7 +9736,7 @@
       <c r="A119" s="38">
         <v>81</v>
       </c>
-      <c r="B119" s="327"/>
+      <c r="B119" s="351"/>
       <c r="C119" s="37" t="s">
         <v>35</v>
       </c>
@@ -9718,7 +9753,7 @@
       <c r="A120" s="38">
         <v>82</v>
       </c>
-      <c r="B120" s="327"/>
+      <c r="B120" s="351"/>
       <c r="C120" s="37" t="s">
         <v>326</v>
       </c>
@@ -9732,10 +9767,10 @@
       <c r="G120" s="12"/>
     </row>
     <row r="121" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A121" s="321">
+      <c r="A121" s="345">
         <v>83</v>
       </c>
-      <c r="B121" s="327"/>
+      <c r="B121" s="351"/>
       <c r="C121" s="36" t="s">
         <v>409</v>
       </c>
@@ -9747,8 +9782,8 @@
       <c r="G121" s="12"/>
     </row>
     <row r="122" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="322"/>
-      <c r="B122" s="327"/>
+      <c r="A122" s="346"/>
+      <c r="B122" s="351"/>
       <c r="C122" s="36" t="s">
         <v>410</v>
       </c>
@@ -9760,8 +9795,8 @@
       <c r="G122" s="12"/>
     </row>
     <row r="123" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="323"/>
-      <c r="B123" s="327"/>
+      <c r="A123" s="347"/>
+      <c r="B123" s="351"/>
       <c r="C123" s="36" t="s">
         <v>411</v>
       </c>
@@ -9776,7 +9811,7 @@
       <c r="A124" s="38">
         <v>84</v>
       </c>
-      <c r="B124" s="327"/>
+      <c r="B124" s="351"/>
       <c r="C124" s="37" t="s">
         <v>412</v>
       </c>
@@ -9793,7 +9828,7 @@
       <c r="A125" s="38">
         <v>85</v>
       </c>
-      <c r="B125" s="327"/>
+      <c r="B125" s="351"/>
       <c r="C125" s="37" t="s">
         <v>139</v>
       </c>
@@ -9810,7 +9845,7 @@
       <c r="A126" s="38">
         <v>86</v>
       </c>
-      <c r="B126" s="328"/>
+      <c r="B126" s="352"/>
       <c r="C126" s="37" t="s">
         <v>140</v>
       </c>
@@ -9827,7 +9862,7 @@
       <c r="A127" s="38">
         <v>87</v>
       </c>
-      <c r="B127" s="295" t="s">
+      <c r="B127" s="319" t="s">
         <v>283</v>
       </c>
       <c r="C127" s="36" t="s">
@@ -9846,7 +9881,7 @@
       <c r="A128" s="38">
         <v>88</v>
       </c>
-      <c r="B128" s="316"/>
+      <c r="B128" s="320"/>
       <c r="C128" s="36" t="s">
         <v>144</v>
       </c>
@@ -9863,7 +9898,7 @@
       <c r="A129" s="38">
         <v>89</v>
       </c>
-      <c r="B129" s="316"/>
+      <c r="B129" s="320"/>
       <c r="C129" s="36" t="s">
         <v>394</v>
       </c>
@@ -9880,7 +9915,7 @@
       <c r="A130" s="38">
         <v>90</v>
       </c>
-      <c r="B130" s="316"/>
+      <c r="B130" s="320"/>
       <c r="C130" s="36" t="s">
         <v>396</v>
       </c>
@@ -9897,7 +9932,7 @@
       <c r="A131" s="38">
         <v>91</v>
       </c>
-      <c r="B131" s="316"/>
+      <c r="B131" s="320"/>
       <c r="C131" s="36" t="s">
         <v>371</v>
       </c>
@@ -9914,7 +9949,7 @@
       <c r="A132" s="38">
         <v>92</v>
       </c>
-      <c r="B132" s="296"/>
+      <c r="B132" s="321"/>
       <c r="C132" s="36" t="s">
         <v>146</v>
       </c>
@@ -9929,7 +9964,7 @@
       <c r="A133" s="38">
         <v>93</v>
       </c>
-      <c r="B133" s="316" t="s">
+      <c r="B133" s="320" t="s">
         <v>284</v>
       </c>
       <c r="C133" s="36" t="s">
@@ -9946,7 +9981,7 @@
       <c r="A134" s="38">
         <v>94</v>
       </c>
-      <c r="B134" s="316"/>
+      <c r="B134" s="320"/>
       <c r="C134" s="36" t="s">
         <v>332</v>
       </c>
@@ -9963,7 +9998,7 @@
       <c r="A135" s="38">
         <v>95</v>
       </c>
-      <c r="B135" s="316"/>
+      <c r="B135" s="320"/>
       <c r="C135" s="36" t="s">
         <v>152</v>
       </c>
@@ -9980,7 +10015,7 @@
       <c r="A136" s="38">
         <v>96</v>
       </c>
-      <c r="B136" s="316"/>
+      <c r="B136" s="320"/>
       <c r="C136" s="36" t="s">
         <v>154</v>
       </c>
@@ -9997,7 +10032,7 @@
       <c r="A137" s="38">
         <v>97</v>
       </c>
-      <c r="B137" s="316"/>
+      <c r="B137" s="320"/>
       <c r="C137" s="36" t="s">
         <v>156</v>
       </c>
@@ -10014,7 +10049,7 @@
       <c r="A138" s="38">
         <v>98</v>
       </c>
-      <c r="B138" s="316"/>
+      <c r="B138" s="320"/>
       <c r="C138" s="36" t="s">
         <v>158</v>
       </c>
@@ -10031,7 +10066,7 @@
       <c r="A139" s="38">
         <v>99</v>
       </c>
-      <c r="B139" s="316"/>
+      <c r="B139" s="320"/>
       <c r="C139" s="36" t="s">
         <v>159</v>
       </c>
@@ -10046,7 +10081,7 @@
       <c r="A140" s="38">
         <v>100</v>
       </c>
-      <c r="B140" s="336" t="s">
+      <c r="B140" s="298" t="s">
         <v>305</v>
       </c>
       <c r="C140" s="36" t="s">
@@ -10059,16 +10094,16 @@
         <v>3420000</v>
       </c>
       <c r="F140" s="41"/>
-      <c r="G140" s="317" t="s">
+      <c r="G140" s="340" t="s">
         <v>336</v>
       </c>
-      <c r="H140" s="318"/>
+      <c r="H140" s="341"/>
     </row>
     <row r="141" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A141" s="38">
         <v>101</v>
       </c>
-      <c r="B141" s="336"/>
+      <c r="B141" s="298"/>
       <c r="C141" s="36" t="s">
         <v>344</v>
       </c>
@@ -10085,7 +10120,7 @@
       <c r="A142" s="38">
         <v>102</v>
       </c>
-      <c r="B142" s="336"/>
+      <c r="B142" s="298"/>
       <c r="C142" s="36" t="s">
         <v>345</v>
       </c>
@@ -10096,16 +10131,16 @@
         <v>3420000</v>
       </c>
       <c r="F142" s="41"/>
-      <c r="G142" s="317" t="s">
+      <c r="G142" s="340" t="s">
         <v>336</v>
       </c>
-      <c r="H142" s="318"/>
+      <c r="H142" s="341"/>
     </row>
     <row r="143" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A143" s="38">
         <v>103</v>
       </c>
-      <c r="B143" s="336"/>
+      <c r="B143" s="298"/>
       <c r="C143" s="36" t="s">
         <v>346</v>
       </c>
@@ -10122,7 +10157,7 @@
       <c r="A144" s="38">
         <v>104</v>
       </c>
-      <c r="B144" s="336"/>
+      <c r="B144" s="298"/>
       <c r="C144" s="36" t="s">
         <v>347</v>
       </c>
@@ -10139,7 +10174,7 @@
       <c r="A145" s="38">
         <v>105</v>
       </c>
-      <c r="B145" s="336"/>
+      <c r="B145" s="298"/>
       <c r="C145" s="118" t="s">
         <v>374</v>
       </c>
@@ -10156,7 +10191,7 @@
       <c r="A146" s="38">
         <v>106</v>
       </c>
-      <c r="B146" s="336"/>
+      <c r="B146" s="298"/>
       <c r="C146" s="36" t="s">
         <v>348</v>
       </c>
@@ -10173,7 +10208,7 @@
       <c r="A147" s="38">
         <v>107</v>
       </c>
-      <c r="B147" s="336"/>
+      <c r="B147" s="298"/>
       <c r="C147" s="36" t="s">
         <v>349</v>
       </c>
@@ -10190,7 +10225,7 @@
       <c r="A148" s="38">
         <v>108</v>
       </c>
-      <c r="B148" s="336"/>
+      <c r="B148" s="298"/>
       <c r="C148" s="36" t="s">
         <v>350</v>
       </c>
@@ -10207,7 +10242,7 @@
       <c r="A149" s="38">
         <v>109</v>
       </c>
-      <c r="B149" s="336"/>
+      <c r="B149" s="298"/>
       <c r="C149" s="118" t="s">
         <v>373</v>
       </c>
@@ -10224,7 +10259,7 @@
       <c r="A150" s="38">
         <v>110</v>
       </c>
-      <c r="B150" s="336"/>
+      <c r="B150" s="298"/>
       <c r="C150" s="36" t="s">
         <v>351</v>
       </c>
@@ -10243,7 +10278,7 @@
       <c r="A151" s="38">
         <v>111</v>
       </c>
-      <c r="B151" s="336"/>
+      <c r="B151" s="298"/>
       <c r="C151" s="36" t="s">
         <v>352</v>
       </c>
@@ -10260,7 +10295,7 @@
       <c r="A152" s="38">
         <v>112</v>
       </c>
-      <c r="B152" s="336"/>
+      <c r="B152" s="298"/>
       <c r="C152" s="36" t="s">
         <v>353</v>
       </c>
@@ -10277,7 +10312,7 @@
       <c r="A153" s="38">
         <v>113</v>
       </c>
-      <c r="B153" s="336"/>
+      <c r="B153" s="298"/>
       <c r="C153" s="36" t="s">
         <v>354</v>
       </c>
@@ -10294,7 +10329,7 @@
       <c r="A154" s="38">
         <v>114</v>
       </c>
-      <c r="B154" s="336"/>
+      <c r="B154" s="298"/>
       <c r="C154" s="36" t="s">
         <v>355</v>
       </c>
@@ -10311,7 +10346,7 @@
       <c r="A155" s="38">
         <v>115</v>
       </c>
-      <c r="B155" s="336"/>
+      <c r="B155" s="298"/>
       <c r="C155" s="36" t="s">
         <v>356</v>
       </c>
@@ -10328,7 +10363,7 @@
       <c r="A156" s="38">
         <v>116</v>
       </c>
-      <c r="B156" s="336"/>
+      <c r="B156" s="298"/>
       <c r="C156" s="36" t="s">
         <v>357</v>
       </c>
@@ -10345,7 +10380,7 @@
       <c r="A157" s="38">
         <v>117</v>
       </c>
-      <c r="B157" s="336"/>
+      <c r="B157" s="298"/>
       <c r="C157" s="36" t="s">
         <v>358</v>
       </c>
@@ -10362,7 +10397,7 @@
       <c r="A158" s="38">
         <v>118</v>
       </c>
-      <c r="B158" s="336"/>
+      <c r="B158" s="298"/>
       <c r="C158" s="36" t="s">
         <v>359</v>
       </c>
@@ -10379,7 +10414,7 @@
       <c r="A159" s="38">
         <v>119</v>
       </c>
-      <c r="B159" s="336"/>
+      <c r="B159" s="298"/>
       <c r="C159" s="36" t="s">
         <v>360</v>
       </c>
@@ -10396,7 +10431,7 @@
       <c r="A160" s="38">
         <v>120</v>
       </c>
-      <c r="B160" s="336"/>
+      <c r="B160" s="298"/>
       <c r="C160" s="36" t="s">
         <v>361</v>
       </c>
@@ -10413,7 +10448,7 @@
       <c r="A161" s="38">
         <v>121</v>
       </c>
-      <c r="B161" s="336"/>
+      <c r="B161" s="298"/>
       <c r="C161" s="36" t="s">
         <v>362</v>
       </c>
@@ -10430,7 +10465,7 @@
       <c r="A162" s="38">
         <v>122</v>
       </c>
-      <c r="B162" s="336"/>
+      <c r="B162" s="298"/>
       <c r="C162" s="36" t="s">
         <v>363</v>
       </c>
@@ -10447,7 +10482,7 @@
       <c r="A163" s="38">
         <v>123</v>
       </c>
-      <c r="B163" s="336"/>
+      <c r="B163" s="298"/>
       <c r="C163" s="36" t="s">
         <v>364</v>
       </c>
@@ -10464,7 +10499,7 @@
       <c r="A164" s="38">
         <v>124</v>
       </c>
-      <c r="B164" s="336"/>
+      <c r="B164" s="298"/>
       <c r="C164" s="36" t="s">
         <v>365</v>
       </c>
@@ -10479,7 +10514,7 @@
       <c r="A165" s="38">
         <v>125</v>
       </c>
-      <c r="B165" s="336"/>
+      <c r="B165" s="298"/>
       <c r="C165" s="36" t="s">
         <v>366</v>
       </c>
@@ -10494,7 +10529,7 @@
       <c r="A166" s="38">
         <v>126</v>
       </c>
-      <c r="B166" s="336"/>
+      <c r="B166" s="298"/>
       <c r="C166" s="36" t="s">
         <v>367</v>
       </c>
@@ -10511,7 +10546,7 @@
       <c r="A167" s="38">
         <v>127</v>
       </c>
-      <c r="B167" s="336"/>
+      <c r="B167" s="298"/>
       <c r="C167" s="36" t="s">
         <v>368</v>
       </c>
@@ -10528,7 +10563,7 @@
       <c r="A168" s="38">
         <v>128</v>
       </c>
-      <c r="B168" s="336"/>
+      <c r="B168" s="298"/>
       <c r="C168" s="36" t="s">
         <v>369</v>
       </c>
@@ -10545,7 +10580,7 @@
       <c r="A169" s="38">
         <v>129</v>
       </c>
-      <c r="B169" s="336"/>
+      <c r="B169" s="298"/>
       <c r="C169" s="36" t="s">
         <v>370</v>
       </c>
@@ -10559,12 +10594,12 @@
       <c r="G169" s="12"/>
     </row>
     <row r="170" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="320" t="s">
+      <c r="A170" s="329" t="s">
         <v>207</v>
       </c>
-      <c r="B170" s="320"/>
-      <c r="C170" s="320"/>
-      <c r="D170" s="320"/>
+      <c r="B170" s="329"/>
+      <c r="C170" s="329"/>
+      <c r="D170" s="329"/>
       <c r="E170" s="84"/>
       <c r="F170" s="70"/>
       <c r="G170" s="12"/>
@@ -10625,7 +10660,7 @@
       <c r="A174" s="38">
         <v>133</v>
       </c>
-      <c r="B174" s="295" t="s">
+      <c r="B174" s="319" t="s">
         <v>204</v>
       </c>
       <c r="C174" s="36" t="s">
@@ -10643,7 +10678,7 @@
       <c r="A175" s="38">
         <v>134</v>
       </c>
-      <c r="B175" s="296"/>
+      <c r="B175" s="321"/>
       <c r="C175" s="36" t="s">
         <v>225</v>
       </c>
@@ -10656,12 +10691,12 @@
       <c r="F175" s="41"/>
     </row>
     <row r="176" spans="1:8" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="292" t="s">
+      <c r="A176" s="332" t="s">
         <v>164</v>
       </c>
-      <c r="B176" s="293"/>
-      <c r="C176" s="293"/>
-      <c r="D176" s="294"/>
+      <c r="B176" s="333"/>
+      <c r="C176" s="333"/>
+      <c r="D176" s="334"/>
       <c r="E176" s="65"/>
       <c r="F176" s="65"/>
     </row>
@@ -10679,7 +10714,7 @@
       <c r="E177" s="90">
         <v>71000</v>
       </c>
-      <c r="F177" s="324" t="s">
+      <c r="F177" s="348" t="s">
         <v>385</v>
       </c>
     </row>
@@ -10697,15 +10732,15 @@
       <c r="E178" s="90">
         <v>86000</v>
       </c>
-      <c r="F178" s="325"/>
+      <c r="F178" s="349"/>
     </row>
     <row r="179" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="320" t="s">
+      <c r="A179" s="329" t="s">
         <v>169</v>
       </c>
-      <c r="B179" s="320"/>
-      <c r="C179" s="320"/>
-      <c r="D179" s="320"/>
+      <c r="B179" s="329"/>
+      <c r="C179" s="329"/>
+      <c r="D179" s="329"/>
       <c r="E179" s="84"/>
       <c r="F179" s="70"/>
       <c r="G179" s="12"/>
@@ -10851,12 +10886,12 @@
       <c r="G187" s="12"/>
     </row>
     <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A188" s="320" t="s">
+      <c r="A188" s="329" t="s">
         <v>264</v>
       </c>
-      <c r="B188" s="320"/>
-      <c r="C188" s="320"/>
-      <c r="D188" s="320"/>
+      <c r="B188" s="329"/>
+      <c r="C188" s="329"/>
+      <c r="D188" s="329"/>
       <c r="E188" s="84"/>
       <c r="F188" s="70"/>
       <c r="G188" s="12"/>
@@ -10879,12 +10914,12 @@
       <c r="G189" s="12"/>
     </row>
     <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="320" t="s">
+      <c r="A190" s="329" t="s">
         <v>234</v>
       </c>
-      <c r="B190" s="320"/>
-      <c r="C190" s="320"/>
-      <c r="D190" s="320"/>
+      <c r="B190" s="329"/>
+      <c r="C190" s="329"/>
+      <c r="D190" s="329"/>
       <c r="E190" s="84"/>
       <c r="F190" s="70"/>
       <c r="G190" s="12"/>
@@ -11060,12 +11095,12 @@
       <c r="G200" s="12"/>
     </row>
     <row r="201" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="292" t="s">
+      <c r="A201" s="332" t="s">
         <v>323</v>
       </c>
-      <c r="B201" s="293"/>
-      <c r="C201" s="293"/>
-      <c r="D201" s="294"/>
+      <c r="B201" s="333"/>
+      <c r="C201" s="333"/>
+      <c r="D201" s="334"/>
       <c r="E201" s="69"/>
       <c r="F201" s="70"/>
       <c r="G201" s="12"/>
@@ -11154,12 +11189,12 @@
       <c r="G206" s="12"/>
     </row>
     <row r="207" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="292" t="s">
+      <c r="A207" s="332" t="s">
         <v>222</v>
       </c>
-      <c r="B207" s="293"/>
-      <c r="C207" s="293"/>
-      <c r="D207" s="294"/>
+      <c r="B207" s="333"/>
+      <c r="C207" s="333"/>
+      <c r="D207" s="334"/>
       <c r="E207" s="69"/>
       <c r="F207" s="70"/>
       <c r="G207" s="12"/>
@@ -11216,12 +11251,12 @@
       <c r="G210" s="12"/>
     </row>
     <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="292" t="s">
+      <c r="A211" s="332" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="293"/>
-      <c r="C211" s="293"/>
-      <c r="D211" s="294"/>
+      <c r="B211" s="333"/>
+      <c r="C211" s="333"/>
+      <c r="D211" s="334"/>
       <c r="E211" s="98"/>
       <c r="F211" s="70"/>
       <c r="G211" s="12"/>
@@ -11235,7 +11270,7 @@
         <v>212</v>
       </c>
       <c r="D212" s="36"/>
-      <c r="E212" s="332">
+      <c r="E212" s="322">
         <v>183000</v>
       </c>
       <c r="F212" s="41"/>
@@ -11250,7 +11285,7 @@
         <v>213</v>
       </c>
       <c r="D213" s="36"/>
-      <c r="E213" s="333"/>
+      <c r="E213" s="323"/>
       <c r="F213" s="41"/>
       <c r="G213" s="12"/>
     </row>
@@ -11263,7 +11298,7 @@
         <v>214</v>
       </c>
       <c r="D214" s="36"/>
-      <c r="E214" s="333"/>
+      <c r="E214" s="323"/>
       <c r="F214" s="41"/>
       <c r="G214" s="12"/>
     </row>
@@ -11276,17 +11311,17 @@
         <v>215</v>
       </c>
       <c r="D215" s="36"/>
-      <c r="E215" s="334"/>
+      <c r="E215" s="324"/>
       <c r="F215" s="41"/>
       <c r="G215" s="12"/>
     </row>
     <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="292" t="s">
+      <c r="A216" s="332" t="s">
         <v>415</v>
       </c>
-      <c r="B216" s="293"/>
-      <c r="C216" s="293"/>
-      <c r="D216" s="294"/>
+      <c r="B216" s="333"/>
+      <c r="C216" s="333"/>
+      <c r="D216" s="334"/>
       <c r="E216" s="98"/>
       <c r="F216" s="70"/>
       <c r="G216" s="12"/>
@@ -11371,33 +11406,33 @@
     </row>
     <row r="223" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A223" s="104"/>
-      <c r="B223" s="329" t="s">
+      <c r="B223" s="328" t="s">
         <v>267</v>
       </c>
-      <c r="C223" s="329"/>
-      <c r="D223" s="329"/>
-      <c r="E223" s="329"/>
-      <c r="F223" s="329"/>
+      <c r="C223" s="328"/>
+      <c r="D223" s="328"/>
+      <c r="E223" s="328"/>
+      <c r="F223" s="328"/>
     </row>
     <row r="224" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A224" s="104"/>
-      <c r="B224" s="329" t="s">
+      <c r="B224" s="328" t="s">
         <v>420</v>
       </c>
-      <c r="C224" s="329"/>
-      <c r="D224" s="329"/>
-      <c r="E224" s="329"/>
-      <c r="F224" s="329"/>
+      <c r="C224" s="328"/>
+      <c r="D224" s="328"/>
+      <c r="E224" s="328"/>
+      <c r="F224" s="328"/>
     </row>
     <row r="225" spans="1:6" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A225" s="105"/>
-      <c r="B225" s="329" t="s">
+      <c r="B225" s="328" t="s">
         <v>29</v>
       </c>
-      <c r="C225" s="329"/>
-      <c r="D225" s="329"/>
-      <c r="E225" s="329"/>
-      <c r="F225" s="329"/>
+      <c r="C225" s="328"/>
+      <c r="D225" s="328"/>
+      <c r="E225" s="328"/>
+      <c r="F225" s="328"/>
     </row>
     <row r="226" spans="1:6" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A226" s="106"/>
@@ -11411,13 +11446,13 @@
     </row>
     <row r="227" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A227" s="103"/>
-      <c r="B227" s="329" t="s">
+      <c r="B227" s="328" t="s">
         <v>31</v>
       </c>
-      <c r="C227" s="329"/>
-      <c r="D227" s="329"/>
-      <c r="E227" s="329"/>
-      <c r="F227" s="329"/>
+      <c r="C227" s="328"/>
+      <c r="D227" s="328"/>
+      <c r="E227" s="328"/>
+      <c r="F227" s="328"/>
     </row>
     <row r="228" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A228" s="103"/>
@@ -11481,6 +11516,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="A176:D176"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="B60:B72"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="B81:B88"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="B133:B139"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A121:A123"/>
+    <mergeCell ref="F177:F178"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="B100:B113"/>
+    <mergeCell ref="A170:D170"/>
+    <mergeCell ref="B118:B126"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="B227:F227"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="F180:F182"/>
+    <mergeCell ref="A190:D190"/>
+    <mergeCell ref="A222:D222"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="E212:E215"/>
+    <mergeCell ref="A207:D207"/>
+    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="A201:D201"/>
     <mergeCell ref="B140:B169"/>
     <mergeCell ref="D1:F5"/>
     <mergeCell ref="A7:F7"/>
@@ -11497,59 +11585,6 @@
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="E14:E19"/>
     <mergeCell ref="F14:F19"/>
-    <mergeCell ref="B227:F227"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="F180:F182"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A222:D222"/>
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="E212:E215"/>
-    <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="G142:H142"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A121:A123"/>
-    <mergeCell ref="F177:F178"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="B100:B113"/>
-    <mergeCell ref="A170:D170"/>
-    <mergeCell ref="B118:B126"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A176:D176"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="B60:B72"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="B81:B88"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="B133:B139"/>
   </mergeCells>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="65" orientation="portrait" r:id="rId1"/>
@@ -11572,7 +11607,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:DW84"/>
+  <dimension ref="A1:DX84"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="129" customWidth="1"/>
@@ -11596,38 +11631,39 @@
     <col min="125" max="125" width="36.140625" style="15" customWidth="1"/>
     <col min="126" max="126" width="9.140625" style="15"/>
     <col min="127" max="127" width="79.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="128" max="16384" width="9.140625" style="15"/>
+    <col min="128" max="128" width="13.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="129" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:127" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="289" t="s">
+    <row r="1" spans="1:128" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="295" t="s">
         <v>260</v>
       </c>
-      <c r="B1" s="290" t="s">
+      <c r="B1" s="296" t="s">
         <v>654</v>
       </c>
-      <c r="C1" s="289" t="s">
+      <c r="C1" s="295" t="s">
         <v>421</v>
       </c>
-      <c r="D1" s="289" t="s">
+      <c r="D1" s="295" t="s">
         <v>422</v>
       </c>
-      <c r="E1" s="290" t="s">
+      <c r="E1" s="296" t="s">
         <v>735</v>
       </c>
-      <c r="F1" s="289" t="s">
+      <c r="F1" s="295" t="s">
         <v>423</v>
       </c>
-      <c r="G1" s="362" t="s">
+      <c r="G1" s="368" t="s">
         <v>514</v>
       </c>
-      <c r="H1" s="362" t="s">
+      <c r="H1" s="368" t="s">
         <v>424</v>
       </c>
-      <c r="I1" s="289" t="s">
+      <c r="I1" s="295" t="s">
         <v>425</v>
       </c>
-      <c r="J1" s="289" t="s">
+      <c r="J1" s="295" t="s">
         <v>426</v>
       </c>
       <c r="K1" s="125">
@@ -11840,11 +11876,11 @@
       <c r="CB1" s="126">
         <v>82</v>
       </c>
-      <c r="CC1" s="360">
+      <c r="CC1" s="366">
         <v>83</v>
       </c>
-      <c r="CD1" s="360"/>
-      <c r="CE1" s="360"/>
+      <c r="CD1" s="366"/>
+      <c r="CE1" s="366"/>
       <c r="CF1" s="126">
         <v>84</v>
       </c>
@@ -11962,21 +11998,21 @@
       <c r="DR1" s="126">
         <v>164</v>
       </c>
-      <c r="DS1" s="359" t="s">
+      <c r="DS1" s="365" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="2" spans="1:127" s="129" customFormat="1" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="289"/>
-      <c r="B2" s="291"/>
-      <c r="C2" s="289"/>
-      <c r="D2" s="289"/>
-      <c r="E2" s="291"/>
-      <c r="F2" s="289"/>
-      <c r="G2" s="362"/>
-      <c r="H2" s="362"/>
-      <c r="I2" s="289"/>
-      <c r="J2" s="289"/>
+    <row r="2" spans="1:128" s="129" customFormat="1" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="295"/>
+      <c r="B2" s="297"/>
+      <c r="C2" s="295"/>
+      <c r="D2" s="295"/>
+      <c r="E2" s="297"/>
+      <c r="F2" s="295"/>
+      <c r="G2" s="368"/>
+      <c r="H2" s="368"/>
+      <c r="I2" s="295"/>
+      <c r="J2" s="295"/>
       <c r="K2" s="128" t="s">
         <v>1</v>
       </c>
@@ -12313,12 +12349,15 @@
       <c r="DR2" s="128" t="s">
         <v>416</v>
       </c>
-      <c r="DS2" s="359"/>
+      <c r="DS2" s="365"/>
       <c r="DW2" s="210" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="3" spans="1:127" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX2" s="129" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="3" spans="1:128" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="149" t="s">
         <v>430</v>
       </c>
@@ -12346,10 +12385,10 @@
       <c r="O3" s="131">
         <v>27000</v>
       </c>
-      <c r="P3" s="358">
+      <c r="P3" s="364">
         <v>60000</v>
       </c>
-      <c r="Q3" s="358"/>
+      <c r="Q3" s="364"/>
       <c r="R3" s="132">
         <v>41000</v>
       </c>
@@ -12663,9 +12702,9 @@
       <c r="DR3" s="131">
         <v>205000</v>
       </c>
-      <c r="DS3" s="359"/>
-    </row>
-    <row r="4" spans="1:127" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DS3" s="365"/>
+    </row>
+    <row r="4" spans="1:128" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="153">
         <v>1</v>
       </c>
@@ -12834,8 +12873,11 @@
         <f>3000000-DS4</f>
         <v>2436000</v>
       </c>
-    </row>
-    <row r="5" spans="1:127" s="136" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX4" s="288">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="5" spans="1:128" s="136" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="209">
         <v>2</v>
       </c>
@@ -13030,8 +13072,11 @@
         <f>2000000-DS5</f>
         <v>-2246000</v>
       </c>
-    </row>
-    <row r="6" spans="1:127" s="167" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX5" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="6" spans="1:128" s="167" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="153">
         <v>3</v>
       </c>
@@ -13219,7 +13264,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="7" spans="1:127" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:128" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="153">
         <v>4</v>
       </c>
@@ -13426,8 +13471,11 @@
         <f t="shared" si="1"/>
         <v>-743000</v>
       </c>
-    </row>
-    <row r="8" spans="1:127" s="249" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX7" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="8" spans="1:128" s="249" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="239">
         <v>5</v>
       </c>
@@ -13601,10 +13649,13 @@
         <v>1898000</v>
       </c>
       <c r="DW8" s="249" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="9" spans="1:127" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>753</v>
+      </c>
+      <c r="DX8" s="289">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="9" spans="1:128" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="153">
         <v>6</v>
       </c>
@@ -13788,7 +13839,7 @@
         <v>-4000</v>
       </c>
     </row>
-    <row r="10" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="153">
         <v>7</v>
       </c>
@@ -13983,8 +14034,11 @@
         <f t="shared" ref="DT10:DT16" si="2">3000000-DS10</f>
         <v>-396000</v>
       </c>
-    </row>
-    <row r="11" spans="1:127" s="136" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX10" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="11" spans="1:128" s="136" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="209">
         <v>8</v>
       </c>
@@ -14184,8 +14238,11 @@
       <c r="DU11" s="136" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="12" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX11" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="12" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="153">
         <v>9</v>
       </c>
@@ -14386,8 +14443,11 @@
         <f t="shared" si="2"/>
         <v>-562000</v>
       </c>
-    </row>
-    <row r="13" spans="1:127" s="249" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX12" s="288">
+        <v>45801</v>
+      </c>
+    </row>
+    <row r="13" spans="1:128" s="249" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="239">
         <v>10</v>
       </c>
@@ -14587,10 +14647,13 @@
         <v>-577000</v>
       </c>
       <c r="DW13" s="249" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="14" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>754</v>
+      </c>
+      <c r="DX13" s="289">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="14" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="153">
         <v>11</v>
       </c>
@@ -14782,7 +14845,7 @@
         <v>-631000</v>
       </c>
     </row>
-    <row r="15" spans="1:127" s="262" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:128" s="262" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="250">
         <v>12</v>
       </c>
@@ -14987,10 +15050,13 @@
         <v>649</v>
       </c>
       <c r="DW15" s="273" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="16" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+      <c r="DX15" s="290">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="16" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="153">
         <v>13</v>
       </c>
@@ -15193,8 +15259,11 @@
         <f t="shared" si="2"/>
         <v>-318000</v>
       </c>
-    </row>
-    <row r="17" spans="1:127" s="272" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX16" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="17" spans="1:128" s="272" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="263">
         <v>14</v>
       </c>
@@ -15372,10 +15441,13 @@
         <v>-103000</v>
       </c>
       <c r="DW17" s="272" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="18" spans="1:127" s="201" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+      <c r="DX17" s="291">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="18" spans="1:128" s="201" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="190">
         <v>15</v>
       </c>
@@ -15571,8 +15643,11 @@
       <c r="DU18" s="201" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="19" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX18" s="292">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="19" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="153">
         <v>16</v>
       </c>
@@ -15765,8 +15840,11 @@
         <f t="shared" si="3"/>
         <v>-163000</v>
       </c>
-    </row>
-    <row r="20" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX19" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="20" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="153">
         <v>17</v>
       </c>
@@ -15956,7 +16034,7 @@
         <v>434000</v>
       </c>
     </row>
-    <row r="21" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="153">
         <v>18</v>
       </c>
@@ -16134,7 +16212,7 @@
         <v>-331000</v>
       </c>
     </row>
-    <row r="22" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="153">
         <v>19</v>
       </c>
@@ -16307,8 +16385,11 @@
         <f t="shared" si="4"/>
         <v>-3000</v>
       </c>
-    </row>
-    <row r="23" spans="1:127" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX22" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="23" spans="1:128" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="190">
         <v>20</v>
       </c>
@@ -16511,8 +16592,11 @@
       <c r="DW23" s="201" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="24" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX23" s="292">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="24" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="153">
         <v>21</v>
       </c>
@@ -16699,8 +16783,11 @@
         <f t="shared" ref="DT24:DT25" si="5">2000000-DS24</f>
         <v>57000</v>
       </c>
-    </row>
-    <row r="25" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX24" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="25" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="153">
         <v>22</v>
       </c>
@@ -16888,7 +16975,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="26" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="153">
         <v>23</v>
       </c>
@@ -17067,8 +17154,11 @@
         <f>3000000-DS26</f>
         <v>-1485000</v>
       </c>
-    </row>
-    <row r="27" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX26" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="27" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="153">
         <v>24</v>
       </c>
@@ -17265,8 +17355,11 @@
         <f>2000000-DS27</f>
         <v>-717000</v>
       </c>
-    </row>
-    <row r="28" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX27" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="28" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="153">
         <v>25</v>
       </c>
@@ -17469,8 +17562,11 @@
         <f>3000000-DS28</f>
         <v>-1024000</v>
       </c>
-    </row>
-    <row r="29" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX28" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="29" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="153">
         <v>26</v>
       </c>
@@ -17644,7 +17740,7 @@
         <v>-2025000</v>
       </c>
     </row>
-    <row r="30" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="153">
         <v>27</v>
       </c>
@@ -17827,8 +17923,11 @@
         <f t="shared" ref="DT30:DT37" si="6">3000000-DS30</f>
         <v>356000</v>
       </c>
-    </row>
-    <row r="31" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX30" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="31" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="153">
         <v>28</v>
       </c>
@@ -18013,8 +18112,11 @@
         <f t="shared" si="6"/>
         <v>764000</v>
       </c>
-    </row>
-    <row r="32" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX31" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="32" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="153">
         <v>29</v>
       </c>
@@ -18183,8 +18285,11 @@
         <f t="shared" si="6"/>
         <v>2436000</v>
       </c>
-    </row>
-    <row r="33" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX32" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="33" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="153">
         <v>30</v>
       </c>
@@ -18369,8 +18474,11 @@
         <f t="shared" si="6"/>
         <v>1175000</v>
       </c>
-    </row>
-    <row r="34" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX33" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="34" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="153">
         <v>31</v>
       </c>
@@ -18559,8 +18667,11 @@
         <f t="shared" si="6"/>
         <v>-400000</v>
       </c>
-    </row>
-    <row r="35" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX34" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="35" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="153">
         <v>32</v>
       </c>
@@ -18743,8 +18854,11 @@
         <f t="shared" si="6"/>
         <v>1303000</v>
       </c>
-    </row>
-    <row r="36" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX35" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="36" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="153">
         <v>33</v>
       </c>
@@ -18927,8 +19041,11 @@
         <f t="shared" si="6"/>
         <v>1303000</v>
       </c>
-    </row>
-    <row r="37" spans="1:127" s="286" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX36" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="37" spans="1:128" s="286" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="275">
         <v>34</v>
       </c>
@@ -19120,10 +19237,13 @@
         <v>659000</v>
       </c>
       <c r="DW37" s="286" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="38" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>751</v>
+      </c>
+      <c r="DX37" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="38" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="153">
         <v>35</v>
       </c>
@@ -19366,8 +19486,11 @@
         <f>2000000-DS38</f>
         <v>-4175000</v>
       </c>
-    </row>
-    <row r="39" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX38" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="39" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="153">
         <v>36</v>
       </c>
@@ -19552,8 +19675,11 @@
         <f t="shared" ref="DT39:DT40" si="7">3000000-DS39</f>
         <v>-589000</v>
       </c>
-    </row>
-    <row r="40" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX39" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="40" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="153">
         <v>37</v>
       </c>
@@ -19726,8 +19852,11 @@
         <f t="shared" si="7"/>
         <v>284000</v>
       </c>
-    </row>
-    <row r="41" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX40" s="288">
+        <v>45801</v>
+      </c>
+    </row>
+    <row r="41" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="153">
         <v>38</v>
       </c>
@@ -19920,8 +20049,11 @@
         <f>2000000-DS41</f>
         <v>-153000</v>
       </c>
-    </row>
-    <row r="42" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX41" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="42" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="153">
         <v>39</v>
       </c>
@@ -20108,8 +20240,11 @@
         <f>3000000-DS42</f>
         <v>-500000</v>
       </c>
-    </row>
-    <row r="43" spans="1:127" s="136" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX42" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="43" spans="1:128" s="136" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="153">
         <v>40</v>
       </c>
@@ -20306,8 +20441,11 @@
         <f>2000000-DS43</f>
         <v>-910000</v>
       </c>
-    </row>
-    <row r="44" spans="1:127" s="238" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX43" s="288">
+        <v>45791</v>
+      </c>
+    </row>
+    <row r="44" spans="1:128" s="238" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="227">
         <v>41</v>
       </c>
@@ -20517,10 +20655,13 @@
         <v>-595000</v>
       </c>
       <c r="DW44" s="238" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="45" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+      <c r="DX44" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="45" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="153">
         <v>42</v>
       </c>
@@ -20711,8 +20852,11 @@
         <f t="shared" ref="DT45:DT46" si="8">2000000-DS45</f>
         <v>-1085000</v>
       </c>
-    </row>
-    <row r="46" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX45" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="46" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="153">
         <v>43</v>
       </c>
@@ -20911,8 +21055,11 @@
         <f t="shared" si="8"/>
         <v>-1455000</v>
       </c>
-    </row>
-    <row r="47" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX46" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="47" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="153">
         <v>44</v>
       </c>
@@ -21105,8 +21252,11 @@
         <f t="shared" ref="DT47:DT51" si="9">3000000-DS47</f>
         <v>-470000</v>
       </c>
-    </row>
-    <row r="48" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX47" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="48" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="153">
         <v>45</v>
       </c>
@@ -21309,8 +21459,11 @@
         <f t="shared" si="9"/>
         <v>-595000</v>
       </c>
-    </row>
-    <row r="49" spans="1:127" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX48" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="49" spans="1:128" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="190">
         <v>46</v>
       </c>
@@ -21522,8 +21675,11 @@
       <c r="DU49" s="201" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="50" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX49" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="50" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="153">
         <v>47</v>
       </c>
@@ -21720,8 +21876,11 @@
         <f t="shared" si="9"/>
         <v>-559000</v>
       </c>
-    </row>
-    <row r="51" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX50" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="51" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="153">
         <v>48</v>
       </c>
@@ -21890,8 +22049,11 @@
         <f t="shared" si="9"/>
         <v>2436000</v>
       </c>
-    </row>
-    <row r="52" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX51" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="52" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="153">
         <v>49</v>
       </c>
@@ -22070,8 +22232,11 @@
         <f>2000000-DS52</f>
         <v>-89000</v>
       </c>
-    </row>
-    <row r="53" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX52" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="53" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="153">
         <v>50</v>
       </c>
@@ -22260,8 +22425,11 @@
         <f t="shared" ref="DT53:DT57" si="10">3000000-DS53</f>
         <v>-402000</v>
       </c>
-    </row>
-    <row r="54" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX53" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="54" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="153">
         <v>51</v>
       </c>
@@ -22456,8 +22624,11 @@
         <f t="shared" si="10"/>
         <v>-419000</v>
       </c>
-    </row>
-    <row r="55" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX54" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="55" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="153">
         <v>52</v>
       </c>
@@ -22662,8 +22833,11 @@
         <f t="shared" si="10"/>
         <v>-180000</v>
       </c>
-    </row>
-    <row r="56" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX55" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="56" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="153">
         <v>53</v>
       </c>
@@ -22860,8 +23034,11 @@
         <f t="shared" si="10"/>
         <v>-946000</v>
       </c>
-    </row>
-    <row r="57" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX56" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="57" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="153">
         <v>54</v>
       </c>
@@ -23060,8 +23237,11 @@
         <f t="shared" si="10"/>
         <v>-440000</v>
       </c>
-    </row>
-    <row r="58" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX57" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="58" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="153">
         <v>55</v>
       </c>
@@ -23240,8 +23420,11 @@
         <f t="shared" ref="DT58:DT60" si="11">2000000-DS58</f>
         <v>-300000</v>
       </c>
-    </row>
-    <row r="59" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX58" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="59" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="153">
         <v>56</v>
       </c>
@@ -23426,8 +23609,11 @@
         <f t="shared" si="11"/>
         <v>-14000</v>
       </c>
-    </row>
-    <row r="60" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX59" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="60" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="153">
         <v>57</v>
       </c>
@@ -23629,7 +23815,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="61" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="153">
         <v>58</v>
       </c>
@@ -23818,8 +24004,11 @@
         <f t="shared" ref="DT61:DT65" si="12">3000000-DS61</f>
         <v>-127000</v>
       </c>
-    </row>
-    <row r="62" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX61" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="62" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="153">
         <v>59</v>
       </c>
@@ -24004,8 +24193,11 @@
         <f t="shared" si="12"/>
         <v>-654000</v>
       </c>
-    </row>
-    <row r="63" spans="1:127" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX62" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="63" spans="1:128" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="190">
         <v>60</v>
       </c>
@@ -24215,8 +24407,11 @@
       <c r="DW63" s="201" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="64" spans="1:127" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX63" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="64" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="153">
         <v>61</v>
       </c>
@@ -24421,8 +24616,11 @@
         <f t="shared" si="12"/>
         <v>-339000</v>
       </c>
-    </row>
-    <row r="65" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX64" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="65" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="153">
         <v>62</v>
       </c>
@@ -24629,8 +24827,11 @@
         <f t="shared" si="12"/>
         <v>-1012000</v>
       </c>
-    </row>
-    <row r="66" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX65" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="66" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="153">
         <v>63</v>
       </c>
@@ -24811,8 +25012,14 @@
         <f>2000000-DS66</f>
         <v>-3185000</v>
       </c>
-    </row>
-    <row r="67" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DW66" s="136" t="s">
+        <v>757</v>
+      </c>
+      <c r="DX66" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="67" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="153">
         <v>64</v>
       </c>
@@ -25034,7 +25241,7 @@
         <v>-528000</v>
       </c>
     </row>
-    <row r="68" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="153">
         <v>65</v>
       </c>
@@ -25223,8 +25430,11 @@
         <f>2000000-DS68</f>
         <v>-88000</v>
       </c>
-    </row>
-    <row r="69" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX68" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="69" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="153">
         <v>66</v>
       </c>
@@ -25428,7 +25638,7 @@
         <v>-771000</v>
       </c>
     </row>
-    <row r="70" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="153">
         <v>67</v>
       </c>
@@ -25631,8 +25841,11 @@
         <f t="shared" si="14"/>
         <v>-583000</v>
       </c>
-    </row>
-    <row r="71" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX70" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="71" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="153">
         <v>68</v>
       </c>
@@ -25807,8 +26020,11 @@
         <f>2000000-DS71</f>
         <v>1095000</v>
       </c>
-    </row>
-    <row r="72" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX71" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="72" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="153">
         <v>69</v>
       </c>
@@ -25987,8 +26203,11 @@
         <f t="shared" ref="DT72:DT76" si="15">3000000-DS72</f>
         <v>1024000</v>
       </c>
-    </row>
-    <row r="73" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX72" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="73" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="153">
         <v>70</v>
       </c>
@@ -26185,8 +26404,11 @@
         <f t="shared" si="15"/>
         <v>514000</v>
       </c>
-    </row>
-    <row r="74" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX73" s="288">
+        <v>45794</v>
+      </c>
+    </row>
+    <row r="74" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="153">
         <v>71</v>
       </c>
@@ -26333,8 +26555,11 @@
         <f t="shared" si="15"/>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="75" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX74" s="288">
+        <v>45730</v>
+      </c>
+    </row>
+    <row r="75" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="153">
         <v>72</v>
       </c>
@@ -26481,8 +26706,11 @@
         <f t="shared" si="15"/>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="76" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX75" s="288">
+        <v>45793</v>
+      </c>
+    </row>
+    <row r="76" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="153">
         <v>73</v>
       </c>
@@ -26629,8 +26857,11 @@
         <f t="shared" si="15"/>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="77" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX76" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="77" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="153">
         <v>74</v>
       </c>
@@ -26778,7 +27009,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="78" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="153">
         <v>75</v>
       </c>
@@ -26925,8 +27156,11 @@
         <f t="shared" ref="DT78:DT81" si="16">3000000-DS78</f>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="79" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX78" s="288">
+        <v>45791</v>
+      </c>
+    </row>
+    <row r="79" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="153">
         <v>76</v>
       </c>
@@ -27073,8 +27307,11 @@
         <f t="shared" si="16"/>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="80" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX79" s="288">
+        <v>45793</v>
+      </c>
+    </row>
+    <row r="80" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="153">
         <v>77</v>
       </c>
@@ -27221,8 +27458,11 @@
         <f t="shared" si="16"/>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="81" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX80" s="288">
+        <v>45793</v>
+      </c>
+    </row>
+    <row r="81" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="153">
         <v>78</v>
       </c>
@@ -27369,8 +27609,11 @@
         <f t="shared" si="16"/>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="82" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX81" s="288">
+        <v>45793</v>
+      </c>
+    </row>
+    <row r="82" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="153">
         <v>79</v>
       </c>
@@ -27517,8 +27760,11 @@
         <f>2000000-DS82</f>
         <v>2000000</v>
       </c>
-    </row>
-    <row r="83" spans="1:124" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DX82" s="288">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="83" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="153">
         <v>80</v>
       </c>
@@ -27665,20 +27911,23 @@
         <f>3000000-DS83</f>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="84" spans="1:124" s="137" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="287" t="s">
+      <c r="DX83" s="288">
+        <v>45793</v>
+      </c>
+    </row>
+    <row r="84" spans="1:128" s="137" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="293" t="s">
         <v>414</v>
       </c>
-      <c r="B84" s="288"/>
-      <c r="C84" s="288"/>
-      <c r="D84" s="288"/>
-      <c r="E84" s="288"/>
-      <c r="F84" s="288"/>
-      <c r="G84" s="288"/>
-      <c r="H84" s="288"/>
-      <c r="I84" s="288"/>
-      <c r="J84" s="361"/>
+      <c r="B84" s="294"/>
+      <c r="C84" s="294"/>
+      <c r="D84" s="294"/>
+      <c r="E84" s="294"/>
+      <c r="F84" s="294"/>
+      <c r="G84" s="294"/>
+      <c r="H84" s="294"/>
+      <c r="I84" s="294"/>
+      <c r="J84" s="367"/>
       <c r="K84" s="138">
         <f>COUNTA(K4:K83)</f>
         <v>70</v>
@@ -28180,6 +28429,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7243669-21FB-4D0A-A56C-939AA9CB053E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43DB772-A7B7-4AF5-B575-B861E13F3981}">
   <dimension ref="A3:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -28196,17 +28454,17 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="363" t="s">
-        <v>746</v>
-      </c>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="G3" s="363"/>
-      <c r="H3" s="363"/>
-      <c r="I3" s="363"/>
+      <c r="A3" s="369" t="s">
+        <v>745</v>
+      </c>
+      <c r="B3" s="369"/>
+      <c r="C3" s="369"/>
+      <c r="D3" s="369"/>
+      <c r="E3" s="369"/>
+      <c r="F3" s="369"/>
+      <c r="G3" s="369"/>
+      <c r="H3" s="369"/>
+      <c r="I3" s="369"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="221" t="s">
@@ -28234,7 +28492,7 @@
         <v>425</v>
       </c>
       <c r="I4" s="221" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="136" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -28263,7 +28521,7 @@
         <v>556</v>
       </c>
       <c r="I5" s="157" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="224" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -28292,7 +28550,7 @@
         <v>560</v>
       </c>
       <c r="I6" s="222" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -28321,7 +28579,7 @@
         <v>582</v>
       </c>
       <c r="I7" s="225" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -28330,4 +28588,1440 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D9F8ED-8F98-4628-A2C6-06CCD6FEFC96}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F81"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="221" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="287" t="s">
+        <v>654</v>
+      </c>
+      <c r="C1" s="221" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1" s="221" t="s">
+        <v>422</v>
+      </c>
+      <c r="E1" s="287" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="153">
+        <v>1</v>
+      </c>
+      <c r="B2" s="153" t="s">
+        <v>655</v>
+      </c>
+      <c r="C2" s="154" t="s">
+        <v>614</v>
+      </c>
+      <c r="D2" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E2" s="153">
+        <v>1972</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="209">
+        <v>2</v>
+      </c>
+      <c r="B3" s="153" t="s">
+        <v>656</v>
+      </c>
+      <c r="C3" s="208" t="s">
+        <v>431</v>
+      </c>
+      <c r="D3" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E3" s="153">
+        <v>1983</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="157">
+        <v>3</v>
+      </c>
+      <c r="B4" s="157" t="s">
+        <v>657</v>
+      </c>
+      <c r="C4" s="220" t="s">
+        <v>434</v>
+      </c>
+      <c r="D4" s="157" t="s">
+        <v>432</v>
+      </c>
+      <c r="E4" s="157">
+        <v>1979</v>
+      </c>
+      <c r="F4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="153">
+        <v>4</v>
+      </c>
+      <c r="B5" s="153" t="s">
+        <v>658</v>
+      </c>
+      <c r="C5" s="163" t="s">
+        <v>435</v>
+      </c>
+      <c r="D5" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E5" s="153">
+        <v>1979</v>
+      </c>
+      <c r="F5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="239">
+        <v>5</v>
+      </c>
+      <c r="B6" s="239" t="s">
+        <v>659</v>
+      </c>
+      <c r="C6" s="240" t="s">
+        <v>436</v>
+      </c>
+      <c r="D6" s="239" t="s">
+        <v>437</v>
+      </c>
+      <c r="E6" s="239">
+        <v>1987</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="157">
+        <v>6</v>
+      </c>
+      <c r="B7" s="157" t="s">
+        <v>660</v>
+      </c>
+      <c r="C7" s="220" t="s">
+        <v>438</v>
+      </c>
+      <c r="D7" s="157" t="s">
+        <v>432</v>
+      </c>
+      <c r="E7" s="157">
+        <v>1990</v>
+      </c>
+      <c r="F7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="153">
+        <v>7</v>
+      </c>
+      <c r="B8" s="153" t="s">
+        <v>661</v>
+      </c>
+      <c r="C8" s="163" t="s">
+        <v>439</v>
+      </c>
+      <c r="D8" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E8" s="153">
+        <v>1987</v>
+      </c>
+      <c r="F8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="209">
+        <v>8</v>
+      </c>
+      <c r="B9" s="153" t="s">
+        <v>662</v>
+      </c>
+      <c r="C9" s="208" t="s">
+        <v>440</v>
+      </c>
+      <c r="D9" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E9" s="153">
+        <v>1985</v>
+      </c>
+      <c r="F9">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="153">
+        <v>9</v>
+      </c>
+      <c r="B10" s="153" t="s">
+        <v>663</v>
+      </c>
+      <c r="C10" s="163" t="s">
+        <v>441</v>
+      </c>
+      <c r="D10" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E10" s="153">
+        <v>1985</v>
+      </c>
+      <c r="F10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="239">
+        <v>10</v>
+      </c>
+      <c r="B11" s="239" t="s">
+        <v>664</v>
+      </c>
+      <c r="C11" s="240" t="s">
+        <v>442</v>
+      </c>
+      <c r="D11" s="239" t="s">
+        <v>437</v>
+      </c>
+      <c r="E11" s="239">
+        <v>1997</v>
+      </c>
+      <c r="F11">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="157">
+        <v>11</v>
+      </c>
+      <c r="B12" s="157" t="s">
+        <v>665</v>
+      </c>
+      <c r="C12" s="220" t="s">
+        <v>443</v>
+      </c>
+      <c r="D12" s="157" t="s">
+        <v>437</v>
+      </c>
+      <c r="E12" s="157">
+        <v>1982</v>
+      </c>
+      <c r="F12">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="250">
+        <v>12</v>
+      </c>
+      <c r="B13" s="250" t="s">
+        <v>666</v>
+      </c>
+      <c r="C13" s="251" t="s">
+        <v>444</v>
+      </c>
+      <c r="D13" s="250" t="s">
+        <v>437</v>
+      </c>
+      <c r="E13" s="250">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="153">
+        <v>13</v>
+      </c>
+      <c r="B14" s="153" t="s">
+        <v>667</v>
+      </c>
+      <c r="C14" s="163" t="s">
+        <v>445</v>
+      </c>
+      <c r="D14" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E14" s="153">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="263">
+        <v>14</v>
+      </c>
+      <c r="B15" s="263" t="s">
+        <v>668</v>
+      </c>
+      <c r="C15" s="264" t="s">
+        <v>446</v>
+      </c>
+      <c r="D15" s="263" t="s">
+        <v>432</v>
+      </c>
+      <c r="E15" s="263">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="190">
+        <v>15</v>
+      </c>
+      <c r="B16" s="190" t="s">
+        <v>669</v>
+      </c>
+      <c r="C16" s="191" t="s">
+        <v>447</v>
+      </c>
+      <c r="D16" s="190" t="s">
+        <v>437</v>
+      </c>
+      <c r="E16" s="190">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="153">
+        <v>16</v>
+      </c>
+      <c r="B17" s="153" t="s">
+        <v>670</v>
+      </c>
+      <c r="C17" s="163" t="s">
+        <v>448</v>
+      </c>
+      <c r="D17" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E17" s="153">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="157">
+        <v>17</v>
+      </c>
+      <c r="B18" s="157" t="s">
+        <v>671</v>
+      </c>
+      <c r="C18" s="220" t="s">
+        <v>449</v>
+      </c>
+      <c r="D18" s="157" t="s">
+        <v>432</v>
+      </c>
+      <c r="E18" s="157">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="157">
+        <v>18</v>
+      </c>
+      <c r="B19" s="157" t="s">
+        <v>672</v>
+      </c>
+      <c r="C19" s="220" t="s">
+        <v>450</v>
+      </c>
+      <c r="D19" s="157" t="s">
+        <v>432</v>
+      </c>
+      <c r="E19" s="157">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="153">
+        <v>19</v>
+      </c>
+      <c r="B20" s="153" t="s">
+        <v>673</v>
+      </c>
+      <c r="C20" s="163" t="s">
+        <v>451</v>
+      </c>
+      <c r="D20" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E20" s="153">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="190">
+        <v>20</v>
+      </c>
+      <c r="B21" s="190" t="s">
+        <v>674</v>
+      </c>
+      <c r="C21" s="191" t="s">
+        <v>452</v>
+      </c>
+      <c r="D21" s="190" t="s">
+        <v>437</v>
+      </c>
+      <c r="E21" s="190">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="153">
+        <v>21</v>
+      </c>
+      <c r="B22" s="153" t="s">
+        <v>675</v>
+      </c>
+      <c r="C22" s="163" t="s">
+        <v>453</v>
+      </c>
+      <c r="D22" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E22" s="153">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="157">
+        <v>22</v>
+      </c>
+      <c r="B23" s="157" t="s">
+        <v>676</v>
+      </c>
+      <c r="C23" s="220" t="s">
+        <v>454</v>
+      </c>
+      <c r="D23" s="157" t="s">
+        <v>432</v>
+      </c>
+      <c r="E23" s="157">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="153">
+        <v>23</v>
+      </c>
+      <c r="B24" s="153" t="s">
+        <v>677</v>
+      </c>
+      <c r="C24" s="163" t="s">
+        <v>455</v>
+      </c>
+      <c r="D24" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E24" s="153">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="153">
+        <v>24</v>
+      </c>
+      <c r="B25" s="153" t="s">
+        <v>678</v>
+      </c>
+      <c r="C25" s="163" t="s">
+        <v>456</v>
+      </c>
+      <c r="D25" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E25" s="153">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="153">
+        <v>25</v>
+      </c>
+      <c r="B26" s="153" t="s">
+        <v>679</v>
+      </c>
+      <c r="C26" s="163" t="s">
+        <v>457</v>
+      </c>
+      <c r="D26" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E26" s="153">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="157">
+        <v>26</v>
+      </c>
+      <c r="B27" s="157" t="s">
+        <v>680</v>
+      </c>
+      <c r="C27" s="220" t="s">
+        <v>458</v>
+      </c>
+      <c r="D27" s="157" t="s">
+        <v>432</v>
+      </c>
+      <c r="E27" s="157">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="153">
+        <v>27</v>
+      </c>
+      <c r="B28" s="153" t="s">
+        <v>681</v>
+      </c>
+      <c r="C28" s="163" t="s">
+        <v>459</v>
+      </c>
+      <c r="D28" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E28" s="153">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="153">
+        <v>28</v>
+      </c>
+      <c r="B29" s="153" t="s">
+        <v>682</v>
+      </c>
+      <c r="C29" s="163" t="s">
+        <v>460</v>
+      </c>
+      <c r="D29" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E29" s="153">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="153">
+        <v>29</v>
+      </c>
+      <c r="B30" s="153" t="s">
+        <v>683</v>
+      </c>
+      <c r="C30" s="163" t="s">
+        <v>461</v>
+      </c>
+      <c r="D30" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E30" s="153">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="153">
+        <v>30</v>
+      </c>
+      <c r="B31" s="153" t="s">
+        <v>684</v>
+      </c>
+      <c r="C31" s="163" t="s">
+        <v>462</v>
+      </c>
+      <c r="D31" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E31" s="153">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="153">
+        <v>31</v>
+      </c>
+      <c r="B32" s="153" t="s">
+        <v>685</v>
+      </c>
+      <c r="C32" s="163" t="s">
+        <v>463</v>
+      </c>
+      <c r="D32" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E32" s="153">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="31.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="153">
+        <v>32</v>
+      </c>
+      <c r="B33" s="153" t="s">
+        <v>686</v>
+      </c>
+      <c r="C33" s="163" t="s">
+        <v>464</v>
+      </c>
+      <c r="D33" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E33" s="153">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="153">
+        <v>33</v>
+      </c>
+      <c r="B34" s="153" t="s">
+        <v>687</v>
+      </c>
+      <c r="C34" s="163" t="s">
+        <v>465</v>
+      </c>
+      <c r="D34" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E34" s="153">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="275">
+        <v>34</v>
+      </c>
+      <c r="B35" s="275" t="s">
+        <v>688</v>
+      </c>
+      <c r="C35" s="276" t="s">
+        <v>466</v>
+      </c>
+      <c r="D35" s="275" t="s">
+        <v>437</v>
+      </c>
+      <c r="E35" s="275">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="153">
+        <v>35</v>
+      </c>
+      <c r="B36" s="153" t="s">
+        <v>689</v>
+      </c>
+      <c r="C36" s="163" t="s">
+        <v>467</v>
+      </c>
+      <c r="D36" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E36" s="153">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="153">
+        <v>36</v>
+      </c>
+      <c r="B37" s="153" t="s">
+        <v>690</v>
+      </c>
+      <c r="C37" s="163" t="s">
+        <v>468</v>
+      </c>
+      <c r="D37" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E37" s="153">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="153">
+        <v>37</v>
+      </c>
+      <c r="B38" s="153" t="s">
+        <v>691</v>
+      </c>
+      <c r="C38" s="163" t="s">
+        <v>469</v>
+      </c>
+      <c r="D38" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E38" s="153">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="153">
+        <v>38</v>
+      </c>
+      <c r="B39" s="153" t="s">
+        <v>692</v>
+      </c>
+      <c r="C39" s="163" t="s">
+        <v>470</v>
+      </c>
+      <c r="D39" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E39" s="153">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="153">
+        <v>39</v>
+      </c>
+      <c r="B40" s="153" t="s">
+        <v>693</v>
+      </c>
+      <c r="C40" s="163" t="s">
+        <v>471</v>
+      </c>
+      <c r="D40" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E40" s="153">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="153">
+        <v>40</v>
+      </c>
+      <c r="B41" s="153" t="s">
+        <v>694</v>
+      </c>
+      <c r="C41" s="163" t="s">
+        <v>472</v>
+      </c>
+      <c r="D41" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E41" s="153">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="227">
+        <v>41</v>
+      </c>
+      <c r="B42" s="227" t="s">
+        <v>695</v>
+      </c>
+      <c r="C42" s="228" t="s">
+        <v>473</v>
+      </c>
+      <c r="D42" s="227" t="s">
+        <v>437</v>
+      </c>
+      <c r="E42" s="227">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="153">
+        <v>42</v>
+      </c>
+      <c r="B43" s="153" t="s">
+        <v>696</v>
+      </c>
+      <c r="C43" s="163" t="s">
+        <v>474</v>
+      </c>
+      <c r="D43" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E43" s="153">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="153">
+        <v>43</v>
+      </c>
+      <c r="B44" s="153" t="s">
+        <v>697</v>
+      </c>
+      <c r="C44" s="163" t="s">
+        <v>475</v>
+      </c>
+      <c r="D44" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E44" s="153">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="153">
+        <v>44</v>
+      </c>
+      <c r="B45" s="153" t="s">
+        <v>698</v>
+      </c>
+      <c r="C45" s="163" t="s">
+        <v>476</v>
+      </c>
+      <c r="D45" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E45" s="153">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="153">
+        <v>45</v>
+      </c>
+      <c r="B46" s="153" t="s">
+        <v>699</v>
+      </c>
+      <c r="C46" s="163" t="s">
+        <v>477</v>
+      </c>
+      <c r="D46" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E46" s="153">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="190">
+        <v>46</v>
+      </c>
+      <c r="B47" s="190" t="s">
+        <v>700</v>
+      </c>
+      <c r="C47" s="191" t="s">
+        <v>478</v>
+      </c>
+      <c r="D47" s="190" t="s">
+        <v>437</v>
+      </c>
+      <c r="E47" s="190">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="153">
+        <v>47</v>
+      </c>
+      <c r="B48" s="153" t="s">
+        <v>701</v>
+      </c>
+      <c r="C48" s="163" t="s">
+        <v>479</v>
+      </c>
+      <c r="D48" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E48" s="153">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="153">
+        <v>48</v>
+      </c>
+      <c r="B49" s="153" t="s">
+        <v>702</v>
+      </c>
+      <c r="C49" s="163" t="s">
+        <v>480</v>
+      </c>
+      <c r="D49" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E49" s="153">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="153">
+        <v>49</v>
+      </c>
+      <c r="B50" s="153" t="s">
+        <v>703</v>
+      </c>
+      <c r="C50" s="171" t="s">
+        <v>481</v>
+      </c>
+      <c r="D50" s="173" t="s">
+        <v>432</v>
+      </c>
+      <c r="E50" s="153">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="153">
+        <v>50</v>
+      </c>
+      <c r="B51" s="153" t="s">
+        <v>704</v>
+      </c>
+      <c r="C51" s="163" t="s">
+        <v>482</v>
+      </c>
+      <c r="D51" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E51" s="153">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="153">
+        <v>51</v>
+      </c>
+      <c r="B52" s="153" t="s">
+        <v>705</v>
+      </c>
+      <c r="C52" s="163" t="s">
+        <v>483</v>
+      </c>
+      <c r="D52" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E52" s="153">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="153">
+        <v>52</v>
+      </c>
+      <c r="B53" s="153" t="s">
+        <v>706</v>
+      </c>
+      <c r="C53" s="183" t="s">
+        <v>484</v>
+      </c>
+      <c r="D53" s="184" t="s">
+        <v>437</v>
+      </c>
+      <c r="E53" s="153">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="153">
+        <v>53</v>
+      </c>
+      <c r="B54" s="153" t="s">
+        <v>707</v>
+      </c>
+      <c r="C54" s="182" t="s">
+        <v>485</v>
+      </c>
+      <c r="D54" s="181" t="s">
+        <v>437</v>
+      </c>
+      <c r="E54" s="153">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="153">
+        <v>54</v>
+      </c>
+      <c r="B55" s="153" t="s">
+        <v>708</v>
+      </c>
+      <c r="C55" s="163" t="s">
+        <v>486</v>
+      </c>
+      <c r="D55" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E55" s="153">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="153">
+        <v>55</v>
+      </c>
+      <c r="B56" s="153" t="s">
+        <v>709</v>
+      </c>
+      <c r="C56" s="163" t="s">
+        <v>487</v>
+      </c>
+      <c r="D56" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E56" s="153">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="153">
+        <v>56</v>
+      </c>
+      <c r="B57" s="153" t="s">
+        <v>710</v>
+      </c>
+      <c r="C57" s="163" t="s">
+        <v>488</v>
+      </c>
+      <c r="D57" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E57" s="153">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="157">
+        <v>57</v>
+      </c>
+      <c r="B58" s="157" t="s">
+        <v>711</v>
+      </c>
+      <c r="C58" s="220" t="s">
+        <v>489</v>
+      </c>
+      <c r="D58" s="157" t="s">
+        <v>432</v>
+      </c>
+      <c r="E58" s="157">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="153">
+        <v>58</v>
+      </c>
+      <c r="B59" s="153" t="s">
+        <v>712</v>
+      </c>
+      <c r="C59" s="163" t="s">
+        <v>490</v>
+      </c>
+      <c r="D59" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E59" s="153">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="153">
+        <v>59</v>
+      </c>
+      <c r="B60" s="153" t="s">
+        <v>713</v>
+      </c>
+      <c r="C60" s="163" t="s">
+        <v>491</v>
+      </c>
+      <c r="D60" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E60" s="153">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="190">
+        <v>60</v>
+      </c>
+      <c r="B61" s="190" t="s">
+        <v>714</v>
+      </c>
+      <c r="C61" s="191" t="s">
+        <v>492</v>
+      </c>
+      <c r="D61" s="190" t="s">
+        <v>437</v>
+      </c>
+      <c r="E61" s="190">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="153">
+        <v>61</v>
+      </c>
+      <c r="B62" s="153" t="s">
+        <v>715</v>
+      </c>
+      <c r="C62" s="163" t="s">
+        <v>493</v>
+      </c>
+      <c r="D62" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E62" s="153">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="153">
+        <v>62</v>
+      </c>
+      <c r="B63" s="153" t="s">
+        <v>716</v>
+      </c>
+      <c r="C63" s="163" t="s">
+        <v>494</v>
+      </c>
+      <c r="D63" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E63" s="153">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="153">
+        <v>63</v>
+      </c>
+      <c r="B64" s="153" t="s">
+        <v>717</v>
+      </c>
+      <c r="C64" s="163" t="s">
+        <v>495</v>
+      </c>
+      <c r="D64" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E64" s="153">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="157">
+        <v>64</v>
+      </c>
+      <c r="B65" s="157" t="s">
+        <v>718</v>
+      </c>
+      <c r="C65" s="220" t="s">
+        <v>496</v>
+      </c>
+      <c r="D65" s="157" t="s">
+        <v>437</v>
+      </c>
+      <c r="E65" s="157">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="153">
+        <v>65</v>
+      </c>
+      <c r="B66" s="153" t="s">
+        <v>719</v>
+      </c>
+      <c r="C66" s="163" t="s">
+        <v>497</v>
+      </c>
+      <c r="D66" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E66" s="153">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="157">
+        <v>66</v>
+      </c>
+      <c r="B67" s="157" t="s">
+        <v>720</v>
+      </c>
+      <c r="C67" s="220" t="s">
+        <v>498</v>
+      </c>
+      <c r="D67" s="157" t="s">
+        <v>437</v>
+      </c>
+      <c r="E67" s="157">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="153">
+        <v>67</v>
+      </c>
+      <c r="B68" s="153" t="s">
+        <v>721</v>
+      </c>
+      <c r="C68" s="163" t="s">
+        <v>499</v>
+      </c>
+      <c r="D68" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E68" s="153">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="153">
+        <v>68</v>
+      </c>
+      <c r="B69" s="153" t="s">
+        <v>722</v>
+      </c>
+      <c r="C69" s="163" t="s">
+        <v>500</v>
+      </c>
+      <c r="D69" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E69" s="153">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="153">
+        <v>69</v>
+      </c>
+      <c r="B70" s="153" t="s">
+        <v>723</v>
+      </c>
+      <c r="C70" s="163" t="s">
+        <v>501</v>
+      </c>
+      <c r="D70" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E70" s="153">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="153">
+        <v>70</v>
+      </c>
+      <c r="B71" s="153" t="s">
+        <v>724</v>
+      </c>
+      <c r="C71" s="163" t="s">
+        <v>502</v>
+      </c>
+      <c r="D71" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E71" s="153">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="153">
+        <v>71</v>
+      </c>
+      <c r="B72" s="153" t="s">
+        <v>725</v>
+      </c>
+      <c r="C72" s="160" t="s">
+        <v>503</v>
+      </c>
+      <c r="D72" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E72" s="153">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="153">
+        <v>72</v>
+      </c>
+      <c r="B73" s="153" t="s">
+        <v>726</v>
+      </c>
+      <c r="C73" s="160" t="s">
+        <v>505</v>
+      </c>
+      <c r="D73" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E73" s="153">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="153">
+        <v>73</v>
+      </c>
+      <c r="B74" s="153" t="s">
+        <v>727</v>
+      </c>
+      <c r="C74" s="160" t="s">
+        <v>506</v>
+      </c>
+      <c r="D74" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E74" s="153">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="157">
+        <v>74</v>
+      </c>
+      <c r="B75" s="157" t="s">
+        <v>728</v>
+      </c>
+      <c r="C75" s="160" t="s">
+        <v>507</v>
+      </c>
+      <c r="D75" s="157" t="s">
+        <v>432</v>
+      </c>
+      <c r="E75" s="157">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="153">
+        <v>75</v>
+      </c>
+      <c r="B76" s="153" t="s">
+        <v>729</v>
+      </c>
+      <c r="C76" s="160" t="s">
+        <v>508</v>
+      </c>
+      <c r="D76" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E76" s="153">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="153">
+        <v>76</v>
+      </c>
+      <c r="B77" s="153" t="s">
+        <v>730</v>
+      </c>
+      <c r="C77" s="160" t="s">
+        <v>509</v>
+      </c>
+      <c r="D77" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E77" s="153">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="153">
+        <v>77</v>
+      </c>
+      <c r="B78" s="153" t="s">
+        <v>731</v>
+      </c>
+      <c r="C78" s="160" t="s">
+        <v>510</v>
+      </c>
+      <c r="D78" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E78" s="153">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="153">
+        <v>78</v>
+      </c>
+      <c r="B79" s="153" t="s">
+        <v>732</v>
+      </c>
+      <c r="C79" s="160" t="s">
+        <v>511</v>
+      </c>
+      <c r="D79" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E79" s="153">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="153">
+        <v>79</v>
+      </c>
+      <c r="B80" s="153" t="s">
+        <v>733</v>
+      </c>
+      <c r="C80" s="160" t="s">
+        <v>512</v>
+      </c>
+      <c r="D80" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="E80" s="153">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="153">
+        <v>80</v>
+      </c>
+      <c r="B81" s="153" t="s">
+        <v>734</v>
+      </c>
+      <c r="C81" s="160" t="s">
+        <v>513</v>
+      </c>
+      <c r="D81" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="E81" s="153">
+        <v>1958</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F81" xr:uid="{91D9F8ED-8F98-4628-A2C6-06CCD6FEFC96}">
+    <filterColumn colId="0">
+      <colorFilter dxfId="2"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A1:A1048576 F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Hoàng/2025/T5/BIDV QUẢNG NAM (62-2025)/DANH MỤC BIDV QUẢNG NAM - điều chỉnh DM FINAL.xlsx
+++ b/Hoàng/2025/T5/BIDV QUẢNG NAM (62-2025)/DANH MỤC BIDV QUẢNG NAM - điều chỉnh DM FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\BIDV QUẢNG NAM (62-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FD75CD-1687-4CCB-B556-D5245D1CD8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB60D29-8740-405D-85A4-7DA7891282A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3073,7 +3073,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="371">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3850,6 +3850,138 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3871,12 +4003,6 @@
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3913,24 +4039,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3940,114 +4048,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="24" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4065,6 +4065,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4074,7 +4077,47 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -7808,7 +7851,7 @@
     <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7835,43 +7878,43 @@
       <c r="A1" s="22"/>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
-      <c r="D1" s="299" t="s">
+      <c r="D1" s="343" t="s">
         <v>313</v>
       </c>
-      <c r="E1" s="299"/>
-      <c r="F1" s="299"/>
+      <c r="E1" s="343"/>
+      <c r="F1" s="343"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
-      <c r="D2" s="300"/>
-      <c r="E2" s="300"/>
-      <c r="F2" s="300"/>
+      <c r="D2" s="344"/>
+      <c r="E2" s="344"/>
+      <c r="F2" s="344"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="300"/>
-      <c r="E3" s="300"/>
-      <c r="F3" s="300"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
+      <c r="F3" s="344"/>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="300"/>
-      <c r="E4" s="300"/>
-      <c r="F4" s="300"/>
+      <c r="D4" s="344"/>
+      <c r="E4" s="344"/>
+      <c r="F4" s="344"/>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="300"/>
-      <c r="E5" s="300"/>
-      <c r="F5" s="300"/>
+      <c r="D5" s="344"/>
+      <c r="E5" s="344"/>
+      <c r="F5" s="344"/>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
@@ -7882,14 +7925,14 @@
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="301" t="s">
+      <c r="A7" s="345" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="301"/>
-      <c r="C7" s="301"/>
-      <c r="D7" s="301"/>
-      <c r="E7" s="301"/>
-      <c r="F7" s="301"/>
+      <c r="B7" s="345"/>
+      <c r="C7" s="345"/>
+      <c r="D7" s="345"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -7911,27 +7954,27 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
-      <c r="B9" s="309" t="s">
+      <c r="B9" s="351" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="309"/>
-      <c r="D9" s="309"/>
-      <c r="E9" s="309"/>
-      <c r="F9" s="309"/>
+      <c r="C9" s="351"/>
+      <c r="D9" s="351"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="310" t="s">
+      <c r="A10" s="352" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="311"/>
-      <c r="C10" s="311"/>
-      <c r="D10" s="311"/>
-      <c r="E10" s="311"/>
-      <c r="F10" s="312"/>
+      <c r="B10" s="353"/>
+      <c r="C10" s="353"/>
+      <c r="D10" s="353"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="354"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -7939,12 +7982,12 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="313"/>
-      <c r="B11" s="314"/>
-      <c r="C11" s="314"/>
-      <c r="D11" s="314"/>
-      <c r="E11" s="314"/>
-      <c r="F11" s="315"/>
+      <c r="A11" s="355"/>
+      <c r="B11" s="356"/>
+      <c r="C11" s="356"/>
+      <c r="D11" s="356"/>
+      <c r="E11" s="356"/>
+      <c r="F11" s="357"/>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
@@ -7963,10 +8006,10 @@
       <c r="A13" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="B13" s="307" t="s">
+      <c r="B13" s="349" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="307"/>
+      <c r="C13" s="349"/>
       <c r="D13" s="33" t="s">
         <v>4</v>
       </c>
@@ -7979,77 +8022,77 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="316">
+      <c r="A14" s="358">
         <v>1</v>
       </c>
-      <c r="B14" s="319" t="s">
+      <c r="B14" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="316" t="s">
+      <c r="C14" s="358" t="s">
         <v>328</v>
       </c>
       <c r="D14" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="322">
+      <c r="E14" s="338">
         <v>200000</v>
       </c>
-      <c r="F14" s="325"/>
+      <c r="F14" s="361"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="317"/>
-      <c r="B15" s="320"/>
-      <c r="C15" s="317"/>
+      <c r="A15" s="359"/>
+      <c r="B15" s="322"/>
+      <c r="C15" s="359"/>
       <c r="D15" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="323"/>
-      <c r="F15" s="326"/>
+      <c r="E15" s="339"/>
+      <c r="F15" s="362"/>
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="317"/>
-      <c r="B16" s="320"/>
-      <c r="C16" s="317"/>
+      <c r="A16" s="359"/>
+      <c r="B16" s="322"/>
+      <c r="C16" s="359"/>
       <c r="D16" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="323"/>
-      <c r="F16" s="326"/>
+      <c r="E16" s="339"/>
+      <c r="F16" s="362"/>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A17" s="317"/>
-      <c r="B17" s="320"/>
-      <c r="C17" s="317"/>
+      <c r="A17" s="359"/>
+      <c r="B17" s="322"/>
+      <c r="C17" s="359"/>
       <c r="D17" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="323"/>
-      <c r="F17" s="326"/>
+      <c r="E17" s="339"/>
+      <c r="F17" s="362"/>
       <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A18" s="317"/>
-      <c r="B18" s="320"/>
-      <c r="C18" s="317"/>
+      <c r="A18" s="359"/>
+      <c r="B18" s="322"/>
+      <c r="C18" s="359"/>
       <c r="D18" s="36" t="s">
         <v>413</v>
       </c>
-      <c r="E18" s="323"/>
-      <c r="F18" s="326"/>
+      <c r="E18" s="339"/>
+      <c r="F18" s="362"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="318"/>
-      <c r="B19" s="321"/>
-      <c r="C19" s="318"/>
+      <c r="A19" s="360"/>
+      <c r="B19" s="302"/>
+      <c r="C19" s="360"/>
       <c r="D19" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="324"/>
-      <c r="F19" s="327"/>
+      <c r="E19" s="340"/>
+      <c r="F19" s="363"/>
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -8132,7 +8175,7 @@
       <c r="A24" s="38">
         <v>6</v>
       </c>
-      <c r="B24" s="298" t="s">
+      <c r="B24" s="342" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="42" t="s">
@@ -8141,10 +8184,10 @@
       <c r="D24" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="304">
+      <c r="E24" s="348">
         <v>60000</v>
       </c>
-      <c r="F24" s="305" t="s">
+      <c r="F24" s="306" t="s">
         <v>383</v>
       </c>
       <c r="G24" s="12"/>
@@ -8153,15 +8196,15 @@
       <c r="A25" s="38">
         <v>7</v>
       </c>
-      <c r="B25" s="298"/>
+      <c r="B25" s="342"/>
       <c r="C25" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="304"/>
-      <c r="F25" s="306"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="307"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -8201,12 +8244,12 @@
       <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="302" t="s">
+      <c r="A28" s="346" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="308"/>
-      <c r="C28" s="308"/>
-      <c r="D28" s="303"/>
+      <c r="B28" s="350"/>
+      <c r="C28" s="350"/>
+      <c r="D28" s="347"/>
       <c r="E28" s="34">
         <f>SUM(E14:E27)</f>
         <v>564000</v>
@@ -8247,10 +8290,10 @@
       <c r="A32" s="63" t="s">
         <v>260</v>
       </c>
-      <c r="B32" s="302" t="s">
+      <c r="B32" s="346" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="303"/>
+      <c r="C32" s="347"/>
       <c r="D32" s="63" t="s">
         <v>4</v>
       </c>
@@ -8353,7 +8396,7 @@
       <c r="A38" s="38">
         <v>5</v>
       </c>
-      <c r="B38" s="319" t="s">
+      <c r="B38" s="301" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="42" t="s">
@@ -8374,7 +8417,7 @@
       <c r="A39" s="38">
         <v>6</v>
       </c>
-      <c r="B39" s="321"/>
+      <c r="B39" s="302"/>
       <c r="C39" s="42" t="s">
         <v>275</v>
       </c>
@@ -8393,7 +8436,7 @@
       <c r="A40" s="38">
         <v>7</v>
       </c>
-      <c r="B40" s="339" t="s">
+      <c r="B40" s="315" t="s">
         <v>61</v>
       </c>
       <c r="C40" s="42" t="s">
@@ -8405,7 +8448,7 @@
       <c r="E40" s="72">
         <v>41000</v>
       </c>
-      <c r="F40" s="336" t="s">
+      <c r="F40" s="303" t="s">
         <v>379</v>
       </c>
       <c r="G40" s="12"/>
@@ -8414,7 +8457,7 @@
       <c r="A41" s="38">
         <v>8</v>
       </c>
-      <c r="B41" s="339"/>
+      <c r="B41" s="315"/>
       <c r="C41" s="42" t="s">
         <v>64</v>
       </c>
@@ -8424,14 +8467,14 @@
       <c r="E41" s="72">
         <v>59000</v>
       </c>
-      <c r="F41" s="337"/>
+      <c r="F41" s="304"/>
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>9</v>
       </c>
-      <c r="B42" s="339"/>
+      <c r="B42" s="315"/>
       <c r="C42" s="42" t="s">
         <v>66</v>
       </c>
@@ -8441,14 +8484,14 @@
       <c r="E42" s="72">
         <v>59000</v>
       </c>
-      <c r="F42" s="337"/>
+      <c r="F42" s="304"/>
       <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>10</v>
       </c>
-      <c r="B43" s="339"/>
+      <c r="B43" s="315"/>
       <c r="C43" s="42" t="s">
         <v>68</v>
       </c>
@@ -8458,14 +8501,14 @@
       <c r="E43" s="72">
         <v>47000</v>
       </c>
-      <c r="F43" s="337"/>
+      <c r="F43" s="304"/>
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>11</v>
       </c>
-      <c r="B44" s="339"/>
+      <c r="B44" s="315"/>
       <c r="C44" s="42" t="s">
         <v>70</v>
       </c>
@@ -8475,7 +8518,7 @@
       <c r="E44" s="72">
         <v>41000</v>
       </c>
-      <c r="F44" s="338"/>
+      <c r="F44" s="305"/>
       <c r="G44" s="12"/>
     </row>
     <row r="45" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -8501,7 +8544,7 @@
       <c r="A46" s="38">
         <v>13</v>
       </c>
-      <c r="B46" s="319" t="s">
+      <c r="B46" s="301" t="s">
         <v>278</v>
       </c>
       <c r="C46" s="36" t="s">
@@ -8513,7 +8556,7 @@
       <c r="E46" s="75">
         <v>62000</v>
       </c>
-      <c r="F46" s="336" t="s">
+      <c r="F46" s="303" t="s">
         <v>380</v>
       </c>
       <c r="G46" s="12"/>
@@ -8522,7 +8565,7 @@
       <c r="A47" s="38">
         <v>14</v>
       </c>
-      <c r="B47" s="320"/>
+      <c r="B47" s="322"/>
       <c r="C47" s="36" t="s">
         <v>197</v>
       </c>
@@ -8532,14 +8575,14 @@
       <c r="E47" s="75">
         <v>165000</v>
       </c>
-      <c r="F47" s="337"/>
+      <c r="F47" s="304"/>
       <c r="G47" s="12"/>
     </row>
     <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>15</v>
       </c>
-      <c r="B48" s="321"/>
+      <c r="B48" s="302"/>
       <c r="C48" s="36" t="s">
         <v>202</v>
       </c>
@@ -8549,14 +8592,14 @@
       <c r="E48" s="75">
         <v>116000</v>
       </c>
-      <c r="F48" s="338"/>
+      <c r="F48" s="305"/>
       <c r="G48" s="12"/>
     </row>
     <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>16</v>
       </c>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="301" t="s">
         <v>273</v>
       </c>
       <c r="C49" s="36" t="s">
@@ -8575,7 +8618,7 @@
       <c r="A50" s="38">
         <v>17</v>
       </c>
-      <c r="B50" s="320"/>
+      <c r="B50" s="322"/>
       <c r="C50" s="36" t="s">
         <v>270</v>
       </c>
@@ -8585,7 +8628,7 @@
       <c r="E50" s="75">
         <v>130000</v>
       </c>
-      <c r="F50" s="336" t="s">
+      <c r="F50" s="303" t="s">
         <v>380</v>
       </c>
       <c r="G50" s="12"/>
@@ -8594,7 +8637,7 @@
       <c r="A51" s="38">
         <v>18</v>
       </c>
-      <c r="B51" s="320"/>
+      <c r="B51" s="322"/>
       <c r="C51" s="36" t="s">
         <v>271</v>
       </c>
@@ -8604,14 +8647,14 @@
       <c r="E51" s="75">
         <v>120000</v>
       </c>
-      <c r="F51" s="337"/>
+      <c r="F51" s="304"/>
       <c r="G51" s="12"/>
     </row>
     <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>19</v>
       </c>
-      <c r="B52" s="321"/>
+      <c r="B52" s="302"/>
       <c r="C52" s="36" t="s">
         <v>272</v>
       </c>
@@ -8621,7 +8664,7 @@
       <c r="E52" s="75">
         <v>282000</v>
       </c>
-      <c r="F52" s="338"/>
+      <c r="F52" s="305"/>
       <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -8647,7 +8690,7 @@
       <c r="A54" s="38">
         <v>21</v>
       </c>
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="317" t="s">
         <v>131</v>
       </c>
       <c r="C54" s="36" t="s">
@@ -8659,7 +8702,7 @@
       <c r="E54" s="75">
         <v>71000</v>
       </c>
-      <c r="F54" s="305" t="s">
+      <c r="F54" s="306" t="s">
         <v>382</v>
       </c>
       <c r="G54" s="12"/>
@@ -8668,7 +8711,7 @@
       <c r="A55" s="38">
         <v>22</v>
       </c>
-      <c r="B55" s="344"/>
+      <c r="B55" s="318"/>
       <c r="C55" s="36" t="s">
         <v>134</v>
       </c>
@@ -8678,7 +8721,7 @@
       <c r="E55" s="71">
         <v>138000</v>
       </c>
-      <c r="F55" s="306"/>
+      <c r="F55" s="307"/>
       <c r="G55" s="12"/>
     </row>
     <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -8704,7 +8747,7 @@
       <c r="A57" s="38">
         <v>24</v>
       </c>
-      <c r="B57" s="360" t="s">
+      <c r="B57" s="316" t="s">
         <v>206</v>
       </c>
       <c r="C57" s="36" t="s">
@@ -8716,7 +8759,7 @@
       <c r="E57" s="75">
         <v>30000</v>
       </c>
-      <c r="F57" s="353" t="s">
+      <c r="F57" s="308" t="s">
         <v>384</v>
       </c>
       <c r="G57" s="13"/>
@@ -8725,7 +8768,7 @@
       <c r="A58" s="38">
         <v>25</v>
       </c>
-      <c r="B58" s="360"/>
+      <c r="B58" s="316"/>
       <c r="C58" s="36" t="s">
         <v>279</v>
       </c>
@@ -8735,16 +8778,16 @@
       <c r="E58" s="75">
         <v>20000</v>
       </c>
-      <c r="F58" s="354"/>
+      <c r="F58" s="309"/>
       <c r="G58" s="13"/>
     </row>
     <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="332" t="s">
+      <c r="A59" s="298" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="333"/>
-      <c r="C59" s="333"/>
-      <c r="D59" s="334"/>
+      <c r="B59" s="299"/>
+      <c r="C59" s="299"/>
+      <c r="D59" s="300"/>
       <c r="E59" s="69"/>
       <c r="F59" s="70"/>
       <c r="G59" s="12"/>
@@ -8753,7 +8796,7 @@
       <c r="A60" s="38">
         <v>26</v>
       </c>
-      <c r="B60" s="355" t="s">
+      <c r="B60" s="310" t="s">
         <v>261</v>
       </c>
       <c r="C60" s="76" t="s">
@@ -8772,7 +8815,7 @@
       <c r="A61" s="38">
         <v>27</v>
       </c>
-      <c r="B61" s="356"/>
+      <c r="B61" s="311"/>
       <c r="C61" s="76" t="s">
         <v>84</v>
       </c>
@@ -8789,7 +8832,7 @@
       <c r="A62" s="38">
         <v>28</v>
       </c>
-      <c r="B62" s="356"/>
+      <c r="B62" s="311"/>
       <c r="C62" s="76" t="s">
         <v>86</v>
       </c>
@@ -8806,7 +8849,7 @@
       <c r="A63" s="38">
         <v>29</v>
       </c>
-      <c r="B63" s="356"/>
+      <c r="B63" s="311"/>
       <c r="C63" s="76" t="s">
         <v>80</v>
       </c>
@@ -8823,7 +8866,7 @@
       <c r="A64" s="38">
         <v>30</v>
       </c>
-      <c r="B64" s="356"/>
+      <c r="B64" s="311"/>
       <c r="C64" s="76" t="s">
         <v>94</v>
       </c>
@@ -8840,7 +8883,7 @@
       <c r="A65" s="38">
         <v>31</v>
       </c>
-      <c r="B65" s="356"/>
+      <c r="B65" s="311"/>
       <c r="C65" s="76" t="s">
         <v>81</v>
       </c>
@@ -8857,7 +8900,7 @@
       <c r="A66" s="38">
         <v>32</v>
       </c>
-      <c r="B66" s="356"/>
+      <c r="B66" s="311"/>
       <c r="C66" s="76" t="s">
         <v>83</v>
       </c>
@@ -8876,7 +8919,7 @@
       <c r="A67" s="38">
         <v>33</v>
       </c>
-      <c r="B67" s="356"/>
+      <c r="B67" s="311"/>
       <c r="C67" s="80" t="s">
         <v>235</v>
       </c>
@@ -8893,7 +8936,7 @@
       <c r="A68" s="38">
         <v>34</v>
       </c>
-      <c r="B68" s="356"/>
+      <c r="B68" s="311"/>
       <c r="C68" s="76" t="s">
         <v>74</v>
       </c>
@@ -8912,7 +8955,7 @@
       <c r="A69" s="38">
         <v>35</v>
       </c>
-      <c r="B69" s="356"/>
+      <c r="B69" s="311"/>
       <c r="C69" s="76" t="s">
         <v>76</v>
       </c>
@@ -8929,7 +8972,7 @@
       <c r="A70" s="38">
         <v>36</v>
       </c>
-      <c r="B70" s="356"/>
+      <c r="B70" s="311"/>
       <c r="C70" s="76" t="s">
         <v>78</v>
       </c>
@@ -8946,7 +8989,7 @@
       <c r="A71" s="38">
         <v>37</v>
       </c>
-      <c r="B71" s="356"/>
+      <c r="B71" s="311"/>
       <c r="C71" s="76" t="s">
         <v>88</v>
       </c>
@@ -8963,7 +9006,7 @@
       <c r="A72" s="38">
         <v>38</v>
       </c>
-      <c r="B72" s="357"/>
+      <c r="B72" s="312"/>
       <c r="C72" s="76" t="s">
         <v>96</v>
       </c>
@@ -8980,19 +9023,19 @@
       <c r="A73" s="38">
         <v>39</v>
       </c>
-      <c r="B73" s="355" t="s">
+      <c r="B73" s="310" t="s">
         <v>91</v>
       </c>
       <c r="C73" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="D73" s="361" t="s">
+      <c r="D73" s="319" t="s">
         <v>398</v>
       </c>
       <c r="E73" s="78">
         <v>137000</v>
       </c>
-      <c r="F73" s="336" t="s">
+      <c r="F73" s="303" t="s">
         <v>381</v>
       </c>
       <c r="G73" s="13"/>
@@ -9001,43 +9044,43 @@
       <c r="A74" s="38">
         <v>40</v>
       </c>
-      <c r="B74" s="356"/>
+      <c r="B74" s="311"/>
       <c r="C74" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="D74" s="362"/>
+      <c r="D74" s="320"/>
       <c r="E74" s="78">
         <v>137000</v>
       </c>
-      <c r="F74" s="337"/>
+      <c r="F74" s="304"/>
       <c r="G74" s="13"/>
     </row>
     <row r="75" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A75" s="38">
         <v>41</v>
       </c>
-      <c r="B75" s="357"/>
+      <c r="B75" s="312"/>
       <c r="C75" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="D75" s="363"/>
+      <c r="D75" s="321"/>
       <c r="E75" s="78">
         <v>208000</v>
       </c>
-      <c r="F75" s="338"/>
+      <c r="F75" s="305"/>
       <c r="G75" s="13"/>
     </row>
     <row r="76" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>42</v>
       </c>
-      <c r="B76" s="355" t="s">
+      <c r="B76" s="310" t="s">
         <v>399</v>
       </c>
       <c r="C76" s="76" t="s">
         <v>400</v>
       </c>
-      <c r="D76" s="358" t="s">
+      <c r="D76" s="313" t="s">
         <v>402</v>
       </c>
       <c r="E76" s="78">
@@ -9050,11 +9093,11 @@
       <c r="A77" s="38">
         <v>43</v>
       </c>
-      <c r="B77" s="356"/>
+      <c r="B77" s="311"/>
       <c r="C77" s="76" t="s">
         <v>401</v>
       </c>
-      <c r="D77" s="359"/>
+      <c r="D77" s="314"/>
       <c r="E77" s="78">
         <v>323000</v>
       </c>
@@ -9065,7 +9108,7 @@
       <c r="A78" s="38">
         <v>44</v>
       </c>
-      <c r="B78" s="356"/>
+      <c r="B78" s="311"/>
       <c r="C78" s="76" t="s">
         <v>404</v>
       </c>
@@ -9082,7 +9125,7 @@
       <c r="A79" s="38">
         <v>45</v>
       </c>
-      <c r="B79" s="357"/>
+      <c r="B79" s="312"/>
       <c r="C79" s="76" t="s">
         <v>405</v>
       </c>
@@ -9096,12 +9139,12 @@
       <c r="G79" s="13"/>
     </row>
     <row r="80" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="332" t="s">
+      <c r="A80" s="298" t="s">
         <v>208</v>
       </c>
-      <c r="B80" s="333"/>
-      <c r="C80" s="333"/>
-      <c r="D80" s="334"/>
+      <c r="B80" s="299"/>
+      <c r="C80" s="299"/>
+      <c r="D80" s="300"/>
       <c r="E80" s="69"/>
       <c r="F80" s="70"/>
       <c r="G80" s="13"/>
@@ -9110,7 +9153,7 @@
       <c r="A81" s="38">
         <v>46</v>
       </c>
-      <c r="B81" s="339" t="s">
+      <c r="B81" s="315" t="s">
         <v>98</v>
       </c>
       <c r="C81" s="36" t="s">
@@ -9129,7 +9172,7 @@
       <c r="A82" s="38">
         <v>47</v>
       </c>
-      <c r="B82" s="339"/>
+      <c r="B82" s="315"/>
       <c r="C82" s="36" t="s">
         <v>101</v>
       </c>
@@ -9146,7 +9189,7 @@
       <c r="A83" s="38">
         <v>48</v>
       </c>
-      <c r="B83" s="339"/>
+      <c r="B83" s="315"/>
       <c r="C83" s="36" t="s">
         <v>103</v>
       </c>
@@ -9165,7 +9208,7 @@
       <c r="A84" s="38">
         <v>49</v>
       </c>
-      <c r="B84" s="339"/>
+      <c r="B84" s="315"/>
       <c r="C84" s="36" t="s">
         <v>106</v>
       </c>
@@ -9184,7 +9227,7 @@
       <c r="A85" s="38">
         <v>50</v>
       </c>
-      <c r="B85" s="339"/>
+      <c r="B85" s="315"/>
       <c r="C85" s="36" t="s">
         <v>407</v>
       </c>
@@ -9201,7 +9244,7 @@
       <c r="A86" s="38">
         <v>51</v>
       </c>
-      <c r="B86" s="339"/>
+      <c r="B86" s="315"/>
       <c r="C86" s="36" t="s">
         <v>108</v>
       </c>
@@ -9220,7 +9263,7 @@
       <c r="A87" s="38">
         <v>52</v>
       </c>
-      <c r="B87" s="339"/>
+      <c r="B87" s="315"/>
       <c r="C87" s="36" t="s">
         <v>111</v>
       </c>
@@ -9239,7 +9282,7 @@
       <c r="A88" s="38">
         <v>53</v>
       </c>
-      <c r="B88" s="339"/>
+      <c r="B88" s="315"/>
       <c r="C88" s="36" t="s">
         <v>114</v>
       </c>
@@ -9258,7 +9301,7 @@
       <c r="A89" s="38">
         <v>54</v>
       </c>
-      <c r="B89" s="339" t="s">
+      <c r="B89" s="315" t="s">
         <v>117</v>
       </c>
       <c r="C89" s="36" t="s">
@@ -9277,7 +9320,7 @@
       <c r="A90" s="38">
         <v>55</v>
       </c>
-      <c r="B90" s="339"/>
+      <c r="B90" s="315"/>
       <c r="C90" s="36" t="s">
         <v>120</v>
       </c>
@@ -9294,7 +9337,7 @@
       <c r="A91" s="38">
         <v>56</v>
       </c>
-      <c r="B91" s="342" t="s">
+      <c r="B91" s="317" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="36" t="s">
@@ -9313,7 +9356,7 @@
       <c r="A92" s="38">
         <v>57</v>
       </c>
-      <c r="B92" s="343"/>
+      <c r="B92" s="325"/>
       <c r="C92" s="36" t="s">
         <v>390</v>
       </c>
@@ -9330,7 +9373,7 @@
       <c r="A93" s="38">
         <v>58</v>
       </c>
-      <c r="B93" s="344"/>
+      <c r="B93" s="318"/>
       <c r="C93" s="36" t="s">
         <v>126</v>
       </c>
@@ -9344,12 +9387,12 @@
       <c r="G93" s="12"/>
     </row>
     <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="332" t="s">
+      <c r="A94" s="298" t="s">
         <v>262</v>
       </c>
-      <c r="B94" s="333"/>
-      <c r="C94" s="333"/>
-      <c r="D94" s="334"/>
+      <c r="B94" s="299"/>
+      <c r="C94" s="299"/>
+      <c r="D94" s="300"/>
       <c r="E94" s="83"/>
       <c r="F94" s="70"/>
       <c r="G94" s="12"/>
@@ -9358,7 +9401,7 @@
       <c r="A95" s="38">
         <v>59</v>
       </c>
-      <c r="B95" s="342" t="s">
+      <c r="B95" s="317" t="s">
         <v>241</v>
       </c>
       <c r="C95" s="36" t="s">
@@ -9377,7 +9420,7 @@
       <c r="A96" s="38">
         <v>60</v>
       </c>
-      <c r="B96" s="344"/>
+      <c r="B96" s="318"/>
       <c r="C96" s="36" t="s">
         <v>240</v>
       </c>
@@ -9394,7 +9437,7 @@
       <c r="A97" s="38">
         <v>61</v>
       </c>
-      <c r="B97" s="342" t="s">
+      <c r="B97" s="317" t="s">
         <v>244</v>
       </c>
       <c r="C97" s="36" t="s">
@@ -9411,7 +9454,7 @@
       <c r="A98" s="38">
         <v>62</v>
       </c>
-      <c r="B98" s="344"/>
+      <c r="B98" s="318"/>
       <c r="C98" s="36" t="s">
         <v>243</v>
       </c>
@@ -9445,7 +9488,7 @@
       <c r="A100" s="38">
         <v>64</v>
       </c>
-      <c r="B100" s="342" t="s">
+      <c r="B100" s="317" t="s">
         <v>259</v>
       </c>
       <c r="C100" s="36" t="s">
@@ -9462,7 +9505,7 @@
       <c r="A101" s="38">
         <v>65</v>
       </c>
-      <c r="B101" s="343"/>
+      <c r="B101" s="325"/>
       <c r="C101" s="36" t="s">
         <v>246</v>
       </c>
@@ -9477,7 +9520,7 @@
       <c r="A102" s="38">
         <v>66</v>
       </c>
-      <c r="B102" s="343"/>
+      <c r="B102" s="325"/>
       <c r="C102" s="36" t="s">
         <v>247</v>
       </c>
@@ -9492,7 +9535,7 @@
       <c r="A103" s="38">
         <v>67</v>
       </c>
-      <c r="B103" s="343"/>
+      <c r="B103" s="325"/>
       <c r="C103" s="36" t="s">
         <v>248</v>
       </c>
@@ -9507,7 +9550,7 @@
       <c r="A104" s="38">
         <v>68</v>
       </c>
-      <c r="B104" s="343"/>
+      <c r="B104" s="325"/>
       <c r="C104" s="36" t="s">
         <v>249</v>
       </c>
@@ -9522,7 +9565,7 @@
       <c r="A105" s="38">
         <v>69</v>
       </c>
-      <c r="B105" s="343"/>
+      <c r="B105" s="325"/>
       <c r="C105" s="36" t="s">
         <v>250</v>
       </c>
@@ -9537,7 +9580,7 @@
       <c r="A106" s="38">
         <v>70</v>
       </c>
-      <c r="B106" s="343"/>
+      <c r="B106" s="325"/>
       <c r="C106" s="36" t="s">
         <v>251</v>
       </c>
@@ -9552,7 +9595,7 @@
       <c r="A107" s="38">
         <v>71</v>
       </c>
-      <c r="B107" s="343"/>
+      <c r="B107" s="325"/>
       <c r="C107" s="36" t="s">
         <v>252</v>
       </c>
@@ -9567,7 +9610,7 @@
       <c r="A108" s="38">
         <v>72</v>
       </c>
-      <c r="B108" s="343"/>
+      <c r="B108" s="325"/>
       <c r="C108" s="36" t="s">
         <v>253</v>
       </c>
@@ -9582,7 +9625,7 @@
       <c r="A109" s="38">
         <v>73</v>
       </c>
-      <c r="B109" s="343"/>
+      <c r="B109" s="325"/>
       <c r="C109" s="36" t="s">
         <v>254</v>
       </c>
@@ -9597,7 +9640,7 @@
       <c r="A110" s="38">
         <v>74</v>
       </c>
-      <c r="B110" s="343"/>
+      <c r="B110" s="325"/>
       <c r="C110" s="36" t="s">
         <v>255</v>
       </c>
@@ -9612,7 +9655,7 @@
       <c r="A111" s="38">
         <v>75</v>
       </c>
-      <c r="B111" s="343"/>
+      <c r="B111" s="325"/>
       <c r="C111" s="36" t="s">
         <v>256</v>
       </c>
@@ -9627,7 +9670,7 @@
       <c r="A112" s="38">
         <v>76</v>
       </c>
-      <c r="B112" s="343"/>
+      <c r="B112" s="325"/>
       <c r="C112" s="36" t="s">
         <v>257</v>
       </c>
@@ -9642,7 +9685,7 @@
       <c r="A113" s="38">
         <v>77</v>
       </c>
-      <c r="B113" s="344"/>
+      <c r="B113" s="318"/>
       <c r="C113" s="36" t="s">
         <v>258</v>
       </c>
@@ -9654,12 +9697,12 @@
       <c r="G113" s="12"/>
     </row>
     <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="332" t="s">
+      <c r="A114" s="298" t="s">
         <v>227</v>
       </c>
-      <c r="B114" s="333"/>
-      <c r="C114" s="333"/>
-      <c r="D114" s="334"/>
+      <c r="B114" s="299"/>
+      <c r="C114" s="299"/>
+      <c r="D114" s="300"/>
       <c r="E114" s="69"/>
       <c r="F114" s="70"/>
       <c r="G114" s="12"/>
@@ -9703,12 +9746,12 @@
       <c r="G116" s="12"/>
     </row>
     <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="329" t="s">
+      <c r="A117" s="326" t="s">
         <v>263</v>
       </c>
-      <c r="B117" s="329"/>
-      <c r="C117" s="329"/>
-      <c r="D117" s="329"/>
+      <c r="B117" s="326"/>
+      <c r="C117" s="326"/>
+      <c r="D117" s="326"/>
       <c r="E117" s="84"/>
       <c r="F117" s="70"/>
       <c r="G117" s="12"/>
@@ -9717,7 +9760,7 @@
       <c r="A118" s="38">
         <v>80</v>
       </c>
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="332" t="s">
         <v>205</v>
       </c>
       <c r="C118" s="37" t="s">
@@ -9736,7 +9779,7 @@
       <c r="A119" s="38">
         <v>81</v>
       </c>
-      <c r="B119" s="351"/>
+      <c r="B119" s="333"/>
       <c r="C119" s="37" t="s">
         <v>35</v>
       </c>
@@ -9753,7 +9796,7 @@
       <c r="A120" s="38">
         <v>82</v>
       </c>
-      <c r="B120" s="351"/>
+      <c r="B120" s="333"/>
       <c r="C120" s="37" t="s">
         <v>326</v>
       </c>
@@ -9767,10 +9810,10 @@
       <c r="G120" s="12"/>
     </row>
     <row r="121" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A121" s="345">
+      <c r="A121" s="327">
         <v>83</v>
       </c>
-      <c r="B121" s="351"/>
+      <c r="B121" s="333"/>
       <c r="C121" s="36" t="s">
         <v>409</v>
       </c>
@@ -9782,8 +9825,8 @@
       <c r="G121" s="12"/>
     </row>
     <row r="122" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="346"/>
-      <c r="B122" s="351"/>
+      <c r="A122" s="328"/>
+      <c r="B122" s="333"/>
       <c r="C122" s="36" t="s">
         <v>410</v>
       </c>
@@ -9795,8 +9838,8 @@
       <c r="G122" s="12"/>
     </row>
     <row r="123" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="347"/>
-      <c r="B123" s="351"/>
+      <c r="A123" s="329"/>
+      <c r="B123" s="333"/>
       <c r="C123" s="36" t="s">
         <v>411</v>
       </c>
@@ -9811,7 +9854,7 @@
       <c r="A124" s="38">
         <v>84</v>
       </c>
-      <c r="B124" s="351"/>
+      <c r="B124" s="333"/>
       <c r="C124" s="37" t="s">
         <v>412</v>
       </c>
@@ -9828,7 +9871,7 @@
       <c r="A125" s="38">
         <v>85</v>
       </c>
-      <c r="B125" s="351"/>
+      <c r="B125" s="333"/>
       <c r="C125" s="37" t="s">
         <v>139</v>
       </c>
@@ -9845,7 +9888,7 @@
       <c r="A126" s="38">
         <v>86</v>
       </c>
-      <c r="B126" s="352"/>
+      <c r="B126" s="334"/>
       <c r="C126" s="37" t="s">
         <v>140</v>
       </c>
@@ -9862,7 +9905,7 @@
       <c r="A127" s="38">
         <v>87</v>
       </c>
-      <c r="B127" s="319" t="s">
+      <c r="B127" s="301" t="s">
         <v>283</v>
       </c>
       <c r="C127" s="36" t="s">
@@ -9881,7 +9924,7 @@
       <c r="A128" s="38">
         <v>88</v>
       </c>
-      <c r="B128" s="320"/>
+      <c r="B128" s="322"/>
       <c r="C128" s="36" t="s">
         <v>144</v>
       </c>
@@ -9898,7 +9941,7 @@
       <c r="A129" s="38">
         <v>89</v>
       </c>
-      <c r="B129" s="320"/>
+      <c r="B129" s="322"/>
       <c r="C129" s="36" t="s">
         <v>394</v>
       </c>
@@ -9915,7 +9958,7 @@
       <c r="A130" s="38">
         <v>90</v>
       </c>
-      <c r="B130" s="320"/>
+      <c r="B130" s="322"/>
       <c r="C130" s="36" t="s">
         <v>396</v>
       </c>
@@ -9932,7 +9975,7 @@
       <c r="A131" s="38">
         <v>91</v>
       </c>
-      <c r="B131" s="320"/>
+      <c r="B131" s="322"/>
       <c r="C131" s="36" t="s">
         <v>371</v>
       </c>
@@ -9949,7 +9992,7 @@
       <c r="A132" s="38">
         <v>92</v>
       </c>
-      <c r="B132" s="321"/>
+      <c r="B132" s="302"/>
       <c r="C132" s="36" t="s">
         <v>146</v>
       </c>
@@ -9964,7 +10007,7 @@
       <c r="A133" s="38">
         <v>93</v>
       </c>
-      <c r="B133" s="320" t="s">
+      <c r="B133" s="322" t="s">
         <v>284</v>
       </c>
       <c r="C133" s="36" t="s">
@@ -9981,7 +10024,7 @@
       <c r="A134" s="38">
         <v>94</v>
       </c>
-      <c r="B134" s="320"/>
+      <c r="B134" s="322"/>
       <c r="C134" s="36" t="s">
         <v>332</v>
       </c>
@@ -9998,7 +10041,7 @@
       <c r="A135" s="38">
         <v>95</v>
       </c>
-      <c r="B135" s="320"/>
+      <c r="B135" s="322"/>
       <c r="C135" s="36" t="s">
         <v>152</v>
       </c>
@@ -10015,7 +10058,7 @@
       <c r="A136" s="38">
         <v>96</v>
       </c>
-      <c r="B136" s="320"/>
+      <c r="B136" s="322"/>
       <c r="C136" s="36" t="s">
         <v>154</v>
       </c>
@@ -10032,7 +10075,7 @@
       <c r="A137" s="38">
         <v>97</v>
       </c>
-      <c r="B137" s="320"/>
+      <c r="B137" s="322"/>
       <c r="C137" s="36" t="s">
         <v>156</v>
       </c>
@@ -10049,7 +10092,7 @@
       <c r="A138" s="38">
         <v>98</v>
       </c>
-      <c r="B138" s="320"/>
+      <c r="B138" s="322"/>
       <c r="C138" s="36" t="s">
         <v>158</v>
       </c>
@@ -10066,7 +10109,7 @@
       <c r="A139" s="38">
         <v>99</v>
       </c>
-      <c r="B139" s="320"/>
+      <c r="B139" s="322"/>
       <c r="C139" s="36" t="s">
         <v>159</v>
       </c>
@@ -10081,7 +10124,7 @@
       <c r="A140" s="38">
         <v>100</v>
       </c>
-      <c r="B140" s="298" t="s">
+      <c r="B140" s="342" t="s">
         <v>305</v>
       </c>
       <c r="C140" s="36" t="s">
@@ -10094,16 +10137,16 @@
         <v>3420000</v>
       </c>
       <c r="F140" s="41"/>
-      <c r="G140" s="340" t="s">
+      <c r="G140" s="323" t="s">
         <v>336</v>
       </c>
-      <c r="H140" s="341"/>
+      <c r="H140" s="324"/>
     </row>
     <row r="141" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A141" s="38">
         <v>101</v>
       </c>
-      <c r="B141" s="298"/>
+      <c r="B141" s="342"/>
       <c r="C141" s="36" t="s">
         <v>344</v>
       </c>
@@ -10120,7 +10163,7 @@
       <c r="A142" s="38">
         <v>102</v>
       </c>
-      <c r="B142" s="298"/>
+      <c r="B142" s="342"/>
       <c r="C142" s="36" t="s">
         <v>345</v>
       </c>
@@ -10131,16 +10174,16 @@
         <v>3420000</v>
       </c>
       <c r="F142" s="41"/>
-      <c r="G142" s="340" t="s">
+      <c r="G142" s="323" t="s">
         <v>336</v>
       </c>
-      <c r="H142" s="341"/>
+      <c r="H142" s="324"/>
     </row>
     <row r="143" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A143" s="38">
         <v>103</v>
       </c>
-      <c r="B143" s="298"/>
+      <c r="B143" s="342"/>
       <c r="C143" s="36" t="s">
         <v>346</v>
       </c>
@@ -10157,7 +10200,7 @@
       <c r="A144" s="38">
         <v>104</v>
       </c>
-      <c r="B144" s="298"/>
+      <c r="B144" s="342"/>
       <c r="C144" s="36" t="s">
         <v>347</v>
       </c>
@@ -10174,7 +10217,7 @@
       <c r="A145" s="38">
         <v>105</v>
       </c>
-      <c r="B145" s="298"/>
+      <c r="B145" s="342"/>
       <c r="C145" s="118" t="s">
         <v>374</v>
       </c>
@@ -10191,7 +10234,7 @@
       <c r="A146" s="38">
         <v>106</v>
       </c>
-      <c r="B146" s="298"/>
+      <c r="B146" s="342"/>
       <c r="C146" s="36" t="s">
         <v>348</v>
       </c>
@@ -10208,7 +10251,7 @@
       <c r="A147" s="38">
         <v>107</v>
       </c>
-      <c r="B147" s="298"/>
+      <c r="B147" s="342"/>
       <c r="C147" s="36" t="s">
         <v>349</v>
       </c>
@@ -10225,7 +10268,7 @@
       <c r="A148" s="38">
         <v>108</v>
       </c>
-      <c r="B148" s="298"/>
+      <c r="B148" s="342"/>
       <c r="C148" s="36" t="s">
         <v>350</v>
       </c>
@@ -10242,7 +10285,7 @@
       <c r="A149" s="38">
         <v>109</v>
       </c>
-      <c r="B149" s="298"/>
+      <c r="B149" s="342"/>
       <c r="C149" s="118" t="s">
         <v>373</v>
       </c>
@@ -10259,7 +10302,7 @@
       <c r="A150" s="38">
         <v>110</v>
       </c>
-      <c r="B150" s="298"/>
+      <c r="B150" s="342"/>
       <c r="C150" s="36" t="s">
         <v>351</v>
       </c>
@@ -10278,7 +10321,7 @@
       <c r="A151" s="38">
         <v>111</v>
       </c>
-      <c r="B151" s="298"/>
+      <c r="B151" s="342"/>
       <c r="C151" s="36" t="s">
         <v>352</v>
       </c>
@@ -10295,7 +10338,7 @@
       <c r="A152" s="38">
         <v>112</v>
       </c>
-      <c r="B152" s="298"/>
+      <c r="B152" s="342"/>
       <c r="C152" s="36" t="s">
         <v>353</v>
       </c>
@@ -10312,7 +10355,7 @@
       <c r="A153" s="38">
         <v>113</v>
       </c>
-      <c r="B153" s="298"/>
+      <c r="B153" s="342"/>
       <c r="C153" s="36" t="s">
         <v>354</v>
       </c>
@@ -10329,7 +10372,7 @@
       <c r="A154" s="38">
         <v>114</v>
       </c>
-      <c r="B154" s="298"/>
+      <c r="B154" s="342"/>
       <c r="C154" s="36" t="s">
         <v>355</v>
       </c>
@@ -10346,7 +10389,7 @@
       <c r="A155" s="38">
         <v>115</v>
       </c>
-      <c r="B155" s="298"/>
+      <c r="B155" s="342"/>
       <c r="C155" s="36" t="s">
         <v>356</v>
       </c>
@@ -10363,7 +10406,7 @@
       <c r="A156" s="38">
         <v>116</v>
       </c>
-      <c r="B156" s="298"/>
+      <c r="B156" s="342"/>
       <c r="C156" s="36" t="s">
         <v>357</v>
       </c>
@@ -10380,7 +10423,7 @@
       <c r="A157" s="38">
         <v>117</v>
       </c>
-      <c r="B157" s="298"/>
+      <c r="B157" s="342"/>
       <c r="C157" s="36" t="s">
         <v>358</v>
       </c>
@@ -10397,7 +10440,7 @@
       <c r="A158" s="38">
         <v>118</v>
       </c>
-      <c r="B158" s="298"/>
+      <c r="B158" s="342"/>
       <c r="C158" s="36" t="s">
         <v>359</v>
       </c>
@@ -10414,7 +10457,7 @@
       <c r="A159" s="38">
         <v>119</v>
       </c>
-      <c r="B159" s="298"/>
+      <c r="B159" s="342"/>
       <c r="C159" s="36" t="s">
         <v>360</v>
       </c>
@@ -10431,7 +10474,7 @@
       <c r="A160" s="38">
         <v>120</v>
       </c>
-      <c r="B160" s="298"/>
+      <c r="B160" s="342"/>
       <c r="C160" s="36" t="s">
         <v>361</v>
       </c>
@@ -10448,7 +10491,7 @@
       <c r="A161" s="38">
         <v>121</v>
       </c>
-      <c r="B161" s="298"/>
+      <c r="B161" s="342"/>
       <c r="C161" s="36" t="s">
         <v>362</v>
       </c>
@@ -10465,7 +10508,7 @@
       <c r="A162" s="38">
         <v>122</v>
       </c>
-      <c r="B162" s="298"/>
+      <c r="B162" s="342"/>
       <c r="C162" s="36" t="s">
         <v>363</v>
       </c>
@@ -10482,7 +10525,7 @@
       <c r="A163" s="38">
         <v>123</v>
       </c>
-      <c r="B163" s="298"/>
+      <c r="B163" s="342"/>
       <c r="C163" s="36" t="s">
         <v>364</v>
       </c>
@@ -10499,7 +10542,7 @@
       <c r="A164" s="38">
         <v>124</v>
       </c>
-      <c r="B164" s="298"/>
+      <c r="B164" s="342"/>
       <c r="C164" s="36" t="s">
         <v>365</v>
       </c>
@@ -10514,7 +10557,7 @@
       <c r="A165" s="38">
         <v>125</v>
       </c>
-      <c r="B165" s="298"/>
+      <c r="B165" s="342"/>
       <c r="C165" s="36" t="s">
         <v>366</v>
       </c>
@@ -10529,7 +10572,7 @@
       <c r="A166" s="38">
         <v>126</v>
       </c>
-      <c r="B166" s="298"/>
+      <c r="B166" s="342"/>
       <c r="C166" s="36" t="s">
         <v>367</v>
       </c>
@@ -10546,7 +10589,7 @@
       <c r="A167" s="38">
         <v>127</v>
       </c>
-      <c r="B167" s="298"/>
+      <c r="B167" s="342"/>
       <c r="C167" s="36" t="s">
         <v>368</v>
       </c>
@@ -10563,7 +10606,7 @@
       <c r="A168" s="38">
         <v>128</v>
       </c>
-      <c r="B168" s="298"/>
+      <c r="B168" s="342"/>
       <c r="C168" s="36" t="s">
         <v>369</v>
       </c>
@@ -10580,7 +10623,7 @@
       <c r="A169" s="38">
         <v>129</v>
       </c>
-      <c r="B169" s="298"/>
+      <c r="B169" s="342"/>
       <c r="C169" s="36" t="s">
         <v>370</v>
       </c>
@@ -10594,12 +10637,12 @@
       <c r="G169" s="12"/>
     </row>
     <row r="170" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="329" t="s">
+      <c r="A170" s="326" t="s">
         <v>207</v>
       </c>
-      <c r="B170" s="329"/>
-      <c r="C170" s="329"/>
-      <c r="D170" s="329"/>
+      <c r="B170" s="326"/>
+      <c r="C170" s="326"/>
+      <c r="D170" s="326"/>
       <c r="E170" s="84"/>
       <c r="F170" s="70"/>
       <c r="G170" s="12"/>
@@ -10660,7 +10703,7 @@
       <c r="A174" s="38">
         <v>133</v>
       </c>
-      <c r="B174" s="319" t="s">
+      <c r="B174" s="301" t="s">
         <v>204</v>
       </c>
       <c r="C174" s="36" t="s">
@@ -10678,7 +10721,7 @@
       <c r="A175" s="38">
         <v>134</v>
       </c>
-      <c r="B175" s="321"/>
+      <c r="B175" s="302"/>
       <c r="C175" s="36" t="s">
         <v>225</v>
       </c>
@@ -10691,12 +10734,12 @@
       <c r="F175" s="41"/>
     </row>
     <row r="176" spans="1:8" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="332" t="s">
+      <c r="A176" s="298" t="s">
         <v>164</v>
       </c>
-      <c r="B176" s="333"/>
-      <c r="C176" s="333"/>
-      <c r="D176" s="334"/>
+      <c r="B176" s="299"/>
+      <c r="C176" s="299"/>
+      <c r="D176" s="300"/>
       <c r="E176" s="65"/>
       <c r="F176" s="65"/>
     </row>
@@ -10714,7 +10757,7 @@
       <c r="E177" s="90">
         <v>71000</v>
       </c>
-      <c r="F177" s="348" t="s">
+      <c r="F177" s="330" t="s">
         <v>385</v>
       </c>
     </row>
@@ -10732,15 +10775,15 @@
       <c r="E178" s="90">
         <v>86000</v>
       </c>
-      <c r="F178" s="349"/>
+      <c r="F178" s="331"/>
     </row>
     <row r="179" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="329" t="s">
+      <c r="A179" s="326" t="s">
         <v>169</v>
       </c>
-      <c r="B179" s="329"/>
-      <c r="C179" s="329"/>
-      <c r="D179" s="329"/>
+      <c r="B179" s="326"/>
+      <c r="C179" s="326"/>
+      <c r="D179" s="326"/>
       <c r="E179" s="84"/>
       <c r="F179" s="70"/>
       <c r="G179" s="12"/>
@@ -10759,7 +10802,7 @@
       <c r="E180" s="116">
         <v>1968000</v>
       </c>
-      <c r="F180" s="330" t="s">
+      <c r="F180" s="336" t="s">
         <v>327</v>
       </c>
       <c r="G180" s="12"/>
@@ -10778,7 +10821,7 @@
       <c r="E181" s="116">
         <v>2952000</v>
       </c>
-      <c r="F181" s="330"/>
+      <c r="F181" s="336"/>
       <c r="G181" s="12"/>
     </row>
     <row r="182" spans="1:7" ht="66" x14ac:dyDescent="0.25">
@@ -10795,7 +10838,7 @@
       <c r="E182" s="116">
         <v>4100000</v>
       </c>
-      <c r="F182" s="330"/>
+      <c r="F182" s="336"/>
       <c r="G182" s="12"/>
     </row>
     <row r="183" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -10886,12 +10929,12 @@
       <c r="G187" s="12"/>
     </row>
     <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A188" s="329" t="s">
+      <c r="A188" s="326" t="s">
         <v>264</v>
       </c>
-      <c r="B188" s="329"/>
-      <c r="C188" s="329"/>
-      <c r="D188" s="329"/>
+      <c r="B188" s="326"/>
+      <c r="C188" s="326"/>
+      <c r="D188" s="326"/>
       <c r="E188" s="84"/>
       <c r="F188" s="70"/>
       <c r="G188" s="12"/>
@@ -10914,12 +10957,12 @@
       <c r="G189" s="12"/>
     </row>
     <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="329" t="s">
+      <c r="A190" s="326" t="s">
         <v>234</v>
       </c>
-      <c r="B190" s="329"/>
-      <c r="C190" s="329"/>
-      <c r="D190" s="329"/>
+      <c r="B190" s="326"/>
+      <c r="C190" s="326"/>
+      <c r="D190" s="326"/>
       <c r="E190" s="84"/>
       <c r="F190" s="70"/>
       <c r="G190" s="12"/>
@@ -11095,12 +11138,12 @@
       <c r="G200" s="12"/>
     </row>
     <row r="201" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="332" t="s">
+      <c r="A201" s="298" t="s">
         <v>323</v>
       </c>
-      <c r="B201" s="333"/>
-      <c r="C201" s="333"/>
-      <c r="D201" s="334"/>
+      <c r="B201" s="299"/>
+      <c r="C201" s="299"/>
+      <c r="D201" s="300"/>
       <c r="E201" s="69"/>
       <c r="F201" s="70"/>
       <c r="G201" s="12"/>
@@ -11189,12 +11232,12 @@
       <c r="G206" s="12"/>
     </row>
     <row r="207" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="332" t="s">
+      <c r="A207" s="298" t="s">
         <v>222</v>
       </c>
-      <c r="B207" s="333"/>
-      <c r="C207" s="333"/>
-      <c r="D207" s="334"/>
+      <c r="B207" s="299"/>
+      <c r="C207" s="299"/>
+      <c r="D207" s="300"/>
       <c r="E207" s="69"/>
       <c r="F207" s="70"/>
       <c r="G207" s="12"/>
@@ -11251,12 +11294,12 @@
       <c r="G210" s="12"/>
     </row>
     <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="332" t="s">
+      <c r="A211" s="298" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="333"/>
-      <c r="C211" s="333"/>
-      <c r="D211" s="334"/>
+      <c r="B211" s="299"/>
+      <c r="C211" s="299"/>
+      <c r="D211" s="300"/>
       <c r="E211" s="98"/>
       <c r="F211" s="70"/>
       <c r="G211" s="12"/>
@@ -11270,7 +11313,7 @@
         <v>212</v>
       </c>
       <c r="D212" s="36"/>
-      <c r="E212" s="322">
+      <c r="E212" s="338">
         <v>183000</v>
       </c>
       <c r="F212" s="41"/>
@@ -11285,7 +11328,7 @@
         <v>213</v>
       </c>
       <c r="D213" s="36"/>
-      <c r="E213" s="323"/>
+      <c r="E213" s="339"/>
       <c r="F213" s="41"/>
       <c r="G213" s="12"/>
     </row>
@@ -11298,7 +11341,7 @@
         <v>214</v>
       </c>
       <c r="D214" s="36"/>
-      <c r="E214" s="323"/>
+      <c r="E214" s="339"/>
       <c r="F214" s="41"/>
       <c r="G214" s="12"/>
     </row>
@@ -11311,17 +11354,17 @@
         <v>215</v>
       </c>
       <c r="D215" s="36"/>
-      <c r="E215" s="324"/>
+      <c r="E215" s="340"/>
       <c r="F215" s="41"/>
       <c r="G215" s="12"/>
     </row>
     <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="332" t="s">
+      <c r="A216" s="298" t="s">
         <v>415</v>
       </c>
-      <c r="B216" s="333"/>
-      <c r="C216" s="333"/>
-      <c r="D216" s="334"/>
+      <c r="B216" s="299"/>
+      <c r="C216" s="299"/>
+      <c r="D216" s="300"/>
       <c r="E216" s="98"/>
       <c r="F216" s="70"/>
       <c r="G216" s="12"/>
@@ -11395,64 +11438,64 @@
       <c r="F221" s="102"/>
     </row>
     <row r="222" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="331" t="s">
+      <c r="A222" s="337" t="s">
         <v>28</v>
       </c>
-      <c r="B222" s="331"/>
-      <c r="C222" s="331"/>
-      <c r="D222" s="331"/>
+      <c r="B222" s="337"/>
+      <c r="C222" s="337"/>
+      <c r="D222" s="337"/>
       <c r="E222" s="26"/>
       <c r="F222" s="103"/>
     </row>
     <row r="223" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A223" s="104"/>
-      <c r="B223" s="328" t="s">
+      <c r="B223" s="335" t="s">
         <v>267</v>
       </c>
-      <c r="C223" s="328"/>
-      <c r="D223" s="328"/>
-      <c r="E223" s="328"/>
-      <c r="F223" s="328"/>
+      <c r="C223" s="335"/>
+      <c r="D223" s="335"/>
+      <c r="E223" s="335"/>
+      <c r="F223" s="335"/>
     </row>
     <row r="224" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A224" s="104"/>
-      <c r="B224" s="328" t="s">
+      <c r="B224" s="335" t="s">
         <v>420</v>
       </c>
-      <c r="C224" s="328"/>
-      <c r="D224" s="328"/>
-      <c r="E224" s="328"/>
-      <c r="F224" s="328"/>
+      <c r="C224" s="335"/>
+      <c r="D224" s="335"/>
+      <c r="E224" s="335"/>
+      <c r="F224" s="335"/>
     </row>
     <row r="225" spans="1:6" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A225" s="105"/>
-      <c r="B225" s="328" t="s">
+      <c r="B225" s="335" t="s">
         <v>29</v>
       </c>
-      <c r="C225" s="328"/>
-      <c r="D225" s="328"/>
-      <c r="E225" s="328"/>
-      <c r="F225" s="328"/>
+      <c r="C225" s="335"/>
+      <c r="D225" s="335"/>
+      <c r="E225" s="335"/>
+      <c r="F225" s="335"/>
     </row>
     <row r="226" spans="1:6" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A226" s="106"/>
-      <c r="B226" s="335" t="s">
+      <c r="B226" s="341" t="s">
         <v>30</v>
       </c>
-      <c r="C226" s="335"/>
-      <c r="D226" s="335"/>
-      <c r="E226" s="335"/>
-      <c r="F226" s="335"/>
+      <c r="C226" s="341"/>
+      <c r="D226" s="341"/>
+      <c r="E226" s="341"/>
+      <c r="F226" s="341"/>
     </row>
     <row r="227" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A227" s="103"/>
-      <c r="B227" s="328" t="s">
+      <c r="B227" s="335" t="s">
         <v>31</v>
       </c>
-      <c r="C227" s="328"/>
-      <c r="D227" s="328"/>
-      <c r="E227" s="328"/>
-      <c r="F227" s="328"/>
+      <c r="C227" s="335"/>
+      <c r="D227" s="335"/>
+      <c r="E227" s="335"/>
+      <c r="F227" s="335"/>
     </row>
     <row r="228" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A228" s="103"/>
@@ -11516,6 +11559,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="B140:B169"/>
+    <mergeCell ref="D1:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A10:F11"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="F14:F19"/>
+    <mergeCell ref="B227:F227"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="F180:F182"/>
+    <mergeCell ref="A190:D190"/>
+    <mergeCell ref="A222:D222"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="E212:E215"/>
+    <mergeCell ref="A207:D207"/>
+    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="A201:D201"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A121:A123"/>
+    <mergeCell ref="F177:F178"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="B100:B113"/>
+    <mergeCell ref="A170:D170"/>
+    <mergeCell ref="B118:B126"/>
+    <mergeCell ref="A114:D114"/>
     <mergeCell ref="A176:D176"/>
     <mergeCell ref="B174:B175"/>
     <mergeCell ref="F73:F75"/>
@@ -11532,59 +11628,6 @@
     <mergeCell ref="A59:D59"/>
     <mergeCell ref="D73:D75"/>
     <mergeCell ref="B133:B139"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="G142:H142"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A121:A123"/>
-    <mergeCell ref="F177:F178"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="B100:B113"/>
-    <mergeCell ref="A170:D170"/>
-    <mergeCell ref="B118:B126"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="B227:F227"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="F180:F182"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A222:D222"/>
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="E212:E215"/>
-    <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="B140:B169"/>
-    <mergeCell ref="D1:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A10:F11"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="F14:F19"/>
   </mergeCells>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="65" orientation="portrait" r:id="rId1"/>
@@ -11607,7 +11650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:DX84"/>
+  <dimension ref="A1:DZ84"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="129" customWidth="1"/>
@@ -11635,7 +11678,7 @@
     <col min="129" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:128" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:130" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="295" t="s">
         <v>260</v>
       </c>
@@ -12002,7 +12045,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="2" spans="1:128" s="129" customFormat="1" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:130" s="129" customFormat="1" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="295"/>
       <c r="B2" s="297"/>
       <c r="C2" s="295"/>
@@ -12357,7 +12400,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="3" spans="1:128" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:130" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="149" t="s">
         <v>430</v>
       </c>
@@ -12704,8 +12747,8 @@
       </c>
       <c r="DS3" s="365"/>
     </row>
-    <row r="4" spans="1:128" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="153">
+    <row r="4" spans="1:130" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="370">
         <v>1</v>
       </c>
       <c r="B4" s="153" t="s">
@@ -12876,9 +12919,12 @@
       <c r="DX4" s="288">
         <v>45802</v>
       </c>
-    </row>
-    <row r="5" spans="1:128" s="136" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="209">
+      <c r="DZ4" s="136">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:130" s="136" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="370">
         <v>2</v>
       </c>
       <c r="B5" s="153" t="s">
@@ -13075,9 +13121,12 @@
       <c r="DX5" s="288">
         <v>45787</v>
       </c>
-    </row>
-    <row r="6" spans="1:128" s="167" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="153">
+      <c r="DZ5" s="136">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:130" s="167" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="370">
         <v>3</v>
       </c>
       <c r="B6" s="153" t="s">
@@ -13263,9 +13312,12 @@
       <c r="DV6" s="166" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="7" spans="1:128" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="153">
+      <c r="DZ6" s="167">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:130" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="370">
         <v>4</v>
       </c>
       <c r="B7" s="153" t="s">
@@ -13474,9 +13526,12 @@
       <c r="DX7" s="288">
         <v>45787</v>
       </c>
-    </row>
-    <row r="8" spans="1:128" s="249" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="239">
+      <c r="DZ7" s="136">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:130" s="249" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="370">
         <v>5</v>
       </c>
       <c r="B8" s="239" t="s">
@@ -13654,9 +13709,12 @@
       <c r="DX8" s="289">
         <v>45787</v>
       </c>
-    </row>
-    <row r="9" spans="1:128" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="153">
+      <c r="DZ8" s="249">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:130" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="370">
         <v>6</v>
       </c>
       <c r="B9" s="153" t="s">
@@ -13838,9 +13896,12 @@
         <f>2000000-DS9</f>
         <v>-4000</v>
       </c>
-    </row>
-    <row r="10" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="153">
+      <c r="DZ9" s="136">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:130" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="370">
         <v>7</v>
       </c>
       <c r="B10" s="153" t="s">
@@ -14037,9 +14098,12 @@
       <c r="DX10" s="288">
         <v>45787</v>
       </c>
-    </row>
-    <row r="11" spans="1:128" s="136" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="209">
+      <c r="DZ10" s="136">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:130" s="136" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="370">
         <v>8</v>
       </c>
       <c r="B11" s="153" t="s">
@@ -14241,9 +14305,12 @@
       <c r="DX11" s="288">
         <v>45787</v>
       </c>
-    </row>
-    <row r="12" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="153">
+      <c r="DZ11" s="136">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:130" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="370">
         <v>9</v>
       </c>
       <c r="B12" s="153" t="s">
@@ -14446,9 +14513,12 @@
       <c r="DX12" s="288">
         <v>45801</v>
       </c>
-    </row>
-    <row r="13" spans="1:128" s="249" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="239">
+      <c r="DZ12" s="136">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:130" s="249" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="370">
         <v>10</v>
       </c>
       <c r="B13" s="239" t="s">
@@ -14653,8 +14723,8 @@
         <v>45794</v>
       </c>
     </row>
-    <row r="14" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="153">
+    <row r="14" spans="1:130" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="370">
         <v>11</v>
       </c>
       <c r="B14" s="153" t="s">
@@ -14845,8 +14915,8 @@
         <v>-631000</v>
       </c>
     </row>
-    <row r="15" spans="1:128" s="262" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="250">
+    <row r="15" spans="1:130" s="262" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="370">
         <v>12</v>
       </c>
       <c r="B15" s="250" t="s">
@@ -15056,8 +15126,8 @@
         <v>45787</v>
       </c>
     </row>
-    <row r="16" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="153">
+    <row r="16" spans="1:130" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="370">
         <v>13</v>
       </c>
       <c r="B16" s="153" t="s">
@@ -15264,7 +15334,7 @@
       </c>
     </row>
     <row r="17" spans="1:128" s="272" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="263">
+      <c r="A17" s="370">
         <v>14</v>
       </c>
       <c r="B17" s="263" t="s">
@@ -15448,7 +15518,7 @@
       </c>
     </row>
     <row r="18" spans="1:128" s="201" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="190">
+      <c r="A18" s="370">
         <v>15</v>
       </c>
       <c r="B18" s="190" t="s">
@@ -15648,7 +15718,7 @@
       </c>
     </row>
     <row r="19" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="153">
+      <c r="A19" s="370">
         <v>16</v>
       </c>
       <c r="B19" s="153" t="s">
@@ -15845,7 +15915,7 @@
       </c>
     </row>
     <row r="20" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="153">
+      <c r="A20" s="370">
         <v>17</v>
       </c>
       <c r="B20" s="153" t="s">
@@ -16035,7 +16105,7 @@
       </c>
     </row>
     <row r="21" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="153">
+      <c r="A21" s="370">
         <v>18</v>
       </c>
       <c r="B21" s="153" t="s">
@@ -16213,7 +16283,7 @@
       </c>
     </row>
     <row r="22" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="153">
+      <c r="A22" s="370">
         <v>19</v>
       </c>
       <c r="B22" s="153" t="s">
@@ -16390,7 +16460,7 @@
       </c>
     </row>
     <row r="23" spans="1:128" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="190">
+      <c r="A23" s="370">
         <v>20</v>
       </c>
       <c r="B23" s="190" t="s">
@@ -16597,7 +16667,7 @@
       </c>
     </row>
     <row r="24" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="153">
+      <c r="A24" s="370">
         <v>21</v>
       </c>
       <c r="B24" s="153" t="s">
@@ -16788,7 +16858,7 @@
       </c>
     </row>
     <row r="25" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="153">
+      <c r="A25" s="370">
         <v>22</v>
       </c>
       <c r="B25" s="153" t="s">
@@ -16976,7 +17046,7 @@
       </c>
     </row>
     <row r="26" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="153">
+      <c r="A26" s="370">
         <v>23</v>
       </c>
       <c r="B26" s="153" t="s">
@@ -17159,7 +17229,7 @@
       </c>
     </row>
     <row r="27" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="153">
+      <c r="A27" s="370">
         <v>24</v>
       </c>
       <c r="B27" s="153" t="s">
@@ -17360,7 +17430,7 @@
       </c>
     </row>
     <row r="28" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="153">
+      <c r="A28" s="370">
         <v>25</v>
       </c>
       <c r="B28" s="153" t="s">
@@ -17567,7 +17637,7 @@
       </c>
     </row>
     <row r="29" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="153">
+      <c r="A29" s="370">
         <v>26</v>
       </c>
       <c r="B29" s="153" t="s">
@@ -17741,7 +17811,7 @@
       </c>
     </row>
     <row r="30" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="153">
+      <c r="A30" s="370">
         <v>27</v>
       </c>
       <c r="B30" s="153" t="s">
@@ -17928,7 +17998,7 @@
       </c>
     </row>
     <row r="31" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="153">
+      <c r="A31" s="370">
         <v>28</v>
       </c>
       <c r="B31" s="153" t="s">
@@ -18117,7 +18187,7 @@
       </c>
     </row>
     <row r="32" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="153">
+      <c r="A32" s="370">
         <v>29</v>
       </c>
       <c r="B32" s="153" t="s">
@@ -18290,7 +18360,7 @@
       </c>
     </row>
     <row r="33" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="153">
+      <c r="A33" s="370">
         <v>30</v>
       </c>
       <c r="B33" s="153" t="s">
@@ -18479,7 +18549,7 @@
       </c>
     </row>
     <row r="34" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="153">
+      <c r="A34" s="370">
         <v>31</v>
       </c>
       <c r="B34" s="153" t="s">
@@ -18672,7 +18742,7 @@
       </c>
     </row>
     <row r="35" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="153">
+      <c r="A35" s="370">
         <v>32</v>
       </c>
       <c r="B35" s="153" t="s">
@@ -18859,7 +18929,7 @@
       </c>
     </row>
     <row r="36" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="153">
+      <c r="A36" s="370">
         <v>33</v>
       </c>
       <c r="B36" s="153" t="s">
@@ -19046,7 +19116,7 @@
       </c>
     </row>
     <row r="37" spans="1:128" s="286" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="275">
+      <c r="A37" s="370">
         <v>34</v>
       </c>
       <c r="B37" s="275" t="s">
@@ -19244,7 +19314,7 @@
       </c>
     </row>
     <row r="38" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="153">
+      <c r="A38" s="370">
         <v>35</v>
       </c>
       <c r="B38" s="153" t="s">
@@ -19491,7 +19561,7 @@
       </c>
     </row>
     <row r="39" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="153">
+      <c r="A39" s="370">
         <v>36</v>
       </c>
       <c r="B39" s="153" t="s">
@@ -19680,7 +19750,7 @@
       </c>
     </row>
     <row r="40" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="153">
+      <c r="A40" s="370">
         <v>37</v>
       </c>
       <c r="B40" s="153" t="s">
@@ -19857,7 +19927,7 @@
       </c>
     </row>
     <row r="41" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="153">
+      <c r="A41" s="370">
         <v>38</v>
       </c>
       <c r="B41" s="153" t="s">
@@ -20054,7 +20124,7 @@
       </c>
     </row>
     <row r="42" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="153">
+      <c r="A42" s="370">
         <v>39</v>
       </c>
       <c r="B42" s="153" t="s">
@@ -20245,7 +20315,7 @@
       </c>
     </row>
     <row r="43" spans="1:128" s="136" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="153">
+      <c r="A43" s="370">
         <v>40</v>
       </c>
       <c r="B43" s="153" t="s">
@@ -20446,7 +20516,7 @@
       </c>
     </row>
     <row r="44" spans="1:128" s="238" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="227">
+      <c r="A44" s="370">
         <v>41</v>
       </c>
       <c r="B44" s="227" t="s">
@@ -20662,7 +20732,7 @@
       </c>
     </row>
     <row r="45" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="153">
+      <c r="A45" s="370">
         <v>42</v>
       </c>
       <c r="B45" s="153" t="s">
@@ -20857,7 +20927,7 @@
       </c>
     </row>
     <row r="46" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="153">
+      <c r="A46" s="370">
         <v>43</v>
       </c>
       <c r="B46" s="153" t="s">
@@ -21060,7 +21130,7 @@
       </c>
     </row>
     <row r="47" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="153">
+      <c r="A47" s="370">
         <v>44</v>
       </c>
       <c r="B47" s="153" t="s">
@@ -21257,7 +21327,7 @@
       </c>
     </row>
     <row r="48" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="153">
+      <c r="A48" s="370">
         <v>45</v>
       </c>
       <c r="B48" s="153" t="s">
@@ -21464,7 +21534,7 @@
       </c>
     </row>
     <row r="49" spans="1:128" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="190">
+      <c r="A49" s="370">
         <v>46</v>
       </c>
       <c r="B49" s="190" t="s">
@@ -21680,7 +21750,7 @@
       </c>
     </row>
     <row r="50" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="153">
+      <c r="A50" s="370">
         <v>47</v>
       </c>
       <c r="B50" s="153" t="s">
@@ -21881,7 +21951,7 @@
       </c>
     </row>
     <row r="51" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="153">
+      <c r="A51" s="370">
         <v>48</v>
       </c>
       <c r="B51" s="153" t="s">
@@ -22054,7 +22124,7 @@
       </c>
     </row>
     <row r="52" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="153">
+      <c r="A52" s="370">
         <v>49</v>
       </c>
       <c r="B52" s="153" t="s">
@@ -22237,7 +22307,7 @@
       </c>
     </row>
     <row r="53" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="153">
+      <c r="A53" s="370">
         <v>50</v>
       </c>
       <c r="B53" s="153" t="s">
@@ -22430,7 +22500,7 @@
       </c>
     </row>
     <row r="54" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="153">
+      <c r="A54" s="370">
         <v>51</v>
       </c>
       <c r="B54" s="153" t="s">
@@ -22629,7 +22699,7 @@
       </c>
     </row>
     <row r="55" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="153">
+      <c r="A55" s="370">
         <v>52</v>
       </c>
       <c r="B55" s="153" t="s">
@@ -22838,7 +22908,7 @@
       </c>
     </row>
     <row r="56" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="153">
+      <c r="A56" s="370">
         <v>53</v>
       </c>
       <c r="B56" s="153" t="s">
@@ -23039,7 +23109,7 @@
       </c>
     </row>
     <row r="57" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="153">
+      <c r="A57" s="370">
         <v>54</v>
       </c>
       <c r="B57" s="153" t="s">
@@ -23242,7 +23312,7 @@
       </c>
     </row>
     <row r="58" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="153">
+      <c r="A58" s="370">
         <v>55</v>
       </c>
       <c r="B58" s="153" t="s">
@@ -23425,7 +23495,7 @@
       </c>
     </row>
     <row r="59" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="153">
+      <c r="A59" s="370">
         <v>56</v>
       </c>
       <c r="B59" s="153" t="s">
@@ -23614,7 +23684,7 @@
       </c>
     </row>
     <row r="60" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="153">
+      <c r="A60" s="370">
         <v>57</v>
       </c>
       <c r="B60" s="153" t="s">
@@ -23816,7 +23886,7 @@
       </c>
     </row>
     <row r="61" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="153">
+      <c r="A61" s="370">
         <v>58</v>
       </c>
       <c r="B61" s="153" t="s">
@@ -24009,7 +24079,7 @@
       </c>
     </row>
     <row r="62" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="153">
+      <c r="A62" s="370">
         <v>59</v>
       </c>
       <c r="B62" s="153" t="s">
@@ -24198,7 +24268,7 @@
       </c>
     </row>
     <row r="63" spans="1:128" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="190">
+      <c r="A63" s="370">
         <v>60</v>
       </c>
       <c r="B63" s="190" t="s">
@@ -24412,7 +24482,7 @@
       </c>
     </row>
     <row r="64" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="153">
+      <c r="A64" s="370">
         <v>61</v>
       </c>
       <c r="B64" s="153" t="s">
@@ -24621,7 +24691,7 @@
       </c>
     </row>
     <row r="65" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="153">
+      <c r="A65" s="370">
         <v>62</v>
       </c>
       <c r="B65" s="153" t="s">
@@ -24832,7 +24902,7 @@
       </c>
     </row>
     <row r="66" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="153">
+      <c r="A66" s="370">
         <v>63</v>
       </c>
       <c r="B66" s="153" t="s">
@@ -25020,7 +25090,7 @@
       </c>
     </row>
     <row r="67" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="153">
+      <c r="A67" s="370">
         <v>64</v>
       </c>
       <c r="B67" s="153" t="s">
@@ -25242,7 +25312,7 @@
       </c>
     </row>
     <row r="68" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="153">
+      <c r="A68" s="370">
         <v>65</v>
       </c>
       <c r="B68" s="153" t="s">
@@ -25435,7 +25505,7 @@
       </c>
     </row>
     <row r="69" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="153">
+      <c r="A69" s="370">
         <v>66</v>
       </c>
       <c r="B69" s="153" t="s">
@@ -25639,7 +25709,7 @@
       </c>
     </row>
     <row r="70" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="153">
+      <c r="A70" s="370">
         <v>67</v>
       </c>
       <c r="B70" s="153" t="s">
@@ -25846,7 +25916,7 @@
       </c>
     </row>
     <row r="71" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="153">
+      <c r="A71" s="370">
         <v>68</v>
       </c>
       <c r="B71" s="153" t="s">
@@ -26025,7 +26095,7 @@
       </c>
     </row>
     <row r="72" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="153">
+      <c r="A72" s="370">
         <v>69</v>
       </c>
       <c r="B72" s="153" t="s">
@@ -26208,7 +26278,7 @@
       </c>
     </row>
     <row r="73" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="153">
+      <c r="A73" s="370">
         <v>70</v>
       </c>
       <c r="B73" s="153" t="s">
@@ -26409,7 +26479,7 @@
       </c>
     </row>
     <row r="74" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="153">
+      <c r="A74" s="370">
         <v>71</v>
       </c>
       <c r="B74" s="153" t="s">
@@ -26560,7 +26630,7 @@
       </c>
     </row>
     <row r="75" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="153">
+      <c r="A75" s="370">
         <v>72</v>
       </c>
       <c r="B75" s="153" t="s">
@@ -26711,7 +26781,7 @@
       </c>
     </row>
     <row r="76" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="153">
+      <c r="A76" s="370">
         <v>73</v>
       </c>
       <c r="B76" s="153" t="s">
@@ -26862,7 +26932,7 @@
       </c>
     </row>
     <row r="77" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="153">
+      <c r="A77" s="370">
         <v>74</v>
       </c>
       <c r="B77" s="153" t="s">
@@ -27010,7 +27080,7 @@
       </c>
     </row>
     <row r="78" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="153">
+      <c r="A78" s="370">
         <v>75</v>
       </c>
       <c r="B78" s="153" t="s">
@@ -27161,7 +27231,7 @@
       </c>
     </row>
     <row r="79" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="153">
+      <c r="A79" s="370">
         <v>76</v>
       </c>
       <c r="B79" s="153" t="s">
@@ -27312,7 +27382,7 @@
       </c>
     </row>
     <row r="80" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="153">
+      <c r="A80" s="370">
         <v>77</v>
       </c>
       <c r="B80" s="153" t="s">
@@ -27463,7 +27533,7 @@
       </c>
     </row>
     <row r="81" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="153">
+      <c r="A81" s="370">
         <v>78</v>
       </c>
       <c r="B81" s="153" t="s">
@@ -27614,7 +27684,7 @@
       </c>
     </row>
     <row r="82" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="153">
+      <c r="A82" s="370">
         <v>79</v>
       </c>
       <c r="B82" s="153" t="s">
@@ -27765,7 +27835,7 @@
       </c>
     </row>
     <row r="83" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="153">
+      <c r="A83" s="370">
         <v>80</v>
       </c>
       <c r="B83" s="153" t="s">
@@ -28402,6 +28472,9 @@
     <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="29" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A1048576 DZ1:DZ1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="J8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
     <hyperlink ref="J13" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
@@ -30016,11 +30089,11 @@
   </sheetData>
   <autoFilter ref="A1:F81" xr:uid="{91D9F8ED-8F98-4628-A2C6-06CCD6FEFC96}">
     <filterColumn colId="0">
-      <colorFilter dxfId="2"/>
+      <colorFilter dxfId="6"/>
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="A1:A1048576 F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Hoàng/2025/T5/BIDV QUẢNG NAM (62-2025)/DANH MỤC BIDV QUẢNG NAM - điều chỉnh DM FINAL.xlsx
+++ b/Hoàng/2025/T5/BIDV QUẢNG NAM (62-2025)/DANH MỤC BIDV QUẢNG NAM - điều chỉnh DM FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\BIDV QUẢNG NAM (62-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB60D29-8740-405D-85A4-7DA7891282A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA8B553-8DE4-4F9D-8977-E256C32E761D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3073,7 +3073,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="371">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3850,6 +3850,108 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3859,11 +3961,8 @@
     <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3874,11 +3973,47 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3901,18 +4036,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3922,132 +4048,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="24" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4065,9 +4065,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4077,37 +4074,7 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -7851,7 +7818,7 @@
     <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7878,43 +7845,43 @@
       <c r="A1" s="22"/>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
-      <c r="D1" s="343" t="s">
+      <c r="D1" s="299" t="s">
         <v>313</v>
       </c>
-      <c r="E1" s="343"/>
-      <c r="F1" s="343"/>
+      <c r="E1" s="299"/>
+      <c r="F1" s="299"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
-      <c r="D2" s="344"/>
-      <c r="E2" s="344"/>
-      <c r="F2" s="344"/>
+      <c r="D2" s="300"/>
+      <c r="E2" s="300"/>
+      <c r="F2" s="300"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="344"/>
-      <c r="E3" s="344"/>
-      <c r="F3" s="344"/>
+      <c r="D3" s="300"/>
+      <c r="E3" s="300"/>
+      <c r="F3" s="300"/>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
+      <c r="D4" s="300"/>
+      <c r="E4" s="300"/>
+      <c r="F4" s="300"/>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="344"/>
-      <c r="E5" s="344"/>
-      <c r="F5" s="344"/>
+      <c r="D5" s="300"/>
+      <c r="E5" s="300"/>
+      <c r="F5" s="300"/>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
@@ -7925,14 +7892,14 @@
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="345" t="s">
+      <c r="A7" s="301" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="345"/>
-      <c r="C7" s="345"/>
-      <c r="D7" s="345"/>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="B7" s="301"/>
+      <c r="C7" s="301"/>
+      <c r="D7" s="301"/>
+      <c r="E7" s="301"/>
+      <c r="F7" s="301"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -7954,27 +7921,27 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
-      <c r="B9" s="351" t="s">
+      <c r="B9" s="309" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="351"/>
-      <c r="D9" s="351"/>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="C9" s="309"/>
+      <c r="D9" s="309"/>
+      <c r="E9" s="309"/>
+      <c r="F9" s="309"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="352" t="s">
+      <c r="A10" s="310" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="353"/>
-      <c r="C10" s="353"/>
-      <c r="D10" s="353"/>
-      <c r="E10" s="353"/>
-      <c r="F10" s="354"/>
+      <c r="B10" s="311"/>
+      <c r="C10" s="311"/>
+      <c r="D10" s="311"/>
+      <c r="E10" s="311"/>
+      <c r="F10" s="312"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -7982,12 +7949,12 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="355"/>
-      <c r="B11" s="356"/>
-      <c r="C11" s="356"/>
-      <c r="D11" s="356"/>
-      <c r="E11" s="356"/>
-      <c r="F11" s="357"/>
+      <c r="A11" s="313"/>
+      <c r="B11" s="314"/>
+      <c r="C11" s="314"/>
+      <c r="D11" s="314"/>
+      <c r="E11" s="314"/>
+      <c r="F11" s="315"/>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
@@ -8006,10 +7973,10 @@
       <c r="A13" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="B13" s="349" t="s">
+      <c r="B13" s="307" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="349"/>
+      <c r="C13" s="307"/>
       <c r="D13" s="33" t="s">
         <v>4</v>
       </c>
@@ -8022,77 +7989,77 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="358">
+      <c r="A14" s="316">
         <v>1</v>
       </c>
-      <c r="B14" s="301" t="s">
+      <c r="B14" s="319" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="358" t="s">
+      <c r="C14" s="316" t="s">
         <v>328</v>
       </c>
       <c r="D14" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="338">
+      <c r="E14" s="322">
         <v>200000</v>
       </c>
-      <c r="F14" s="361"/>
+      <c r="F14" s="325"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="359"/>
-      <c r="B15" s="322"/>
-      <c r="C15" s="359"/>
+      <c r="A15" s="317"/>
+      <c r="B15" s="320"/>
+      <c r="C15" s="317"/>
       <c r="D15" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="339"/>
-      <c r="F15" s="362"/>
+      <c r="E15" s="323"/>
+      <c r="F15" s="326"/>
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="359"/>
-      <c r="B16" s="322"/>
-      <c r="C16" s="359"/>
+      <c r="A16" s="317"/>
+      <c r="B16" s="320"/>
+      <c r="C16" s="317"/>
       <c r="D16" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="339"/>
-      <c r="F16" s="362"/>
+      <c r="E16" s="323"/>
+      <c r="F16" s="326"/>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A17" s="359"/>
-      <c r="B17" s="322"/>
-      <c r="C17" s="359"/>
+      <c r="A17" s="317"/>
+      <c r="B17" s="320"/>
+      <c r="C17" s="317"/>
       <c r="D17" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="339"/>
-      <c r="F17" s="362"/>
+      <c r="E17" s="323"/>
+      <c r="F17" s="326"/>
       <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A18" s="359"/>
-      <c r="B18" s="322"/>
-      <c r="C18" s="359"/>
+      <c r="A18" s="317"/>
+      <c r="B18" s="320"/>
+      <c r="C18" s="317"/>
       <c r="D18" s="36" t="s">
         <v>413</v>
       </c>
-      <c r="E18" s="339"/>
-      <c r="F18" s="362"/>
+      <c r="E18" s="323"/>
+      <c r="F18" s="326"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="360"/>
-      <c r="B19" s="302"/>
-      <c r="C19" s="360"/>
+      <c r="A19" s="318"/>
+      <c r="B19" s="321"/>
+      <c r="C19" s="318"/>
       <c r="D19" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="340"/>
-      <c r="F19" s="363"/>
+      <c r="E19" s="324"/>
+      <c r="F19" s="327"/>
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -8175,7 +8142,7 @@
       <c r="A24" s="38">
         <v>6</v>
       </c>
-      <c r="B24" s="342" t="s">
+      <c r="B24" s="298" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="42" t="s">
@@ -8184,10 +8151,10 @@
       <c r="D24" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="348">
+      <c r="E24" s="304">
         <v>60000</v>
       </c>
-      <c r="F24" s="306" t="s">
+      <c r="F24" s="305" t="s">
         <v>383</v>
       </c>
       <c r="G24" s="12"/>
@@ -8196,15 +8163,15 @@
       <c r="A25" s="38">
         <v>7</v>
       </c>
-      <c r="B25" s="342"/>
+      <c r="B25" s="298"/>
       <c r="C25" s="42" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="348"/>
-      <c r="F25" s="307"/>
+      <c r="E25" s="304"/>
+      <c r="F25" s="306"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -8244,12 +8211,12 @@
       <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="346" t="s">
+      <c r="A28" s="302" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="350"/>
-      <c r="C28" s="350"/>
-      <c r="D28" s="347"/>
+      <c r="B28" s="308"/>
+      <c r="C28" s="308"/>
+      <c r="D28" s="303"/>
       <c r="E28" s="34">
         <f>SUM(E14:E27)</f>
         <v>564000</v>
@@ -8290,10 +8257,10 @@
       <c r="A32" s="63" t="s">
         <v>260</v>
       </c>
-      <c r="B32" s="346" t="s">
+      <c r="B32" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="347"/>
+      <c r="C32" s="303"/>
       <c r="D32" s="63" t="s">
         <v>4</v>
       </c>
@@ -8396,7 +8363,7 @@
       <c r="A38" s="38">
         <v>5</v>
       </c>
-      <c r="B38" s="301" t="s">
+      <c r="B38" s="319" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="42" t="s">
@@ -8417,7 +8384,7 @@
       <c r="A39" s="38">
         <v>6</v>
       </c>
-      <c r="B39" s="302"/>
+      <c r="B39" s="321"/>
       <c r="C39" s="42" t="s">
         <v>275</v>
       </c>
@@ -8436,7 +8403,7 @@
       <c r="A40" s="38">
         <v>7</v>
       </c>
-      <c r="B40" s="315" t="s">
+      <c r="B40" s="339" t="s">
         <v>61</v>
       </c>
       <c r="C40" s="42" t="s">
@@ -8448,7 +8415,7 @@
       <c r="E40" s="72">
         <v>41000</v>
       </c>
-      <c r="F40" s="303" t="s">
+      <c r="F40" s="336" t="s">
         <v>379</v>
       </c>
       <c r="G40" s="12"/>
@@ -8457,7 +8424,7 @@
       <c r="A41" s="38">
         <v>8</v>
       </c>
-      <c r="B41" s="315"/>
+      <c r="B41" s="339"/>
       <c r="C41" s="42" t="s">
         <v>64</v>
       </c>
@@ -8467,14 +8434,14 @@
       <c r="E41" s="72">
         <v>59000</v>
       </c>
-      <c r="F41" s="304"/>
+      <c r="F41" s="337"/>
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>9</v>
       </c>
-      <c r="B42" s="315"/>
+      <c r="B42" s="339"/>
       <c r="C42" s="42" t="s">
         <v>66</v>
       </c>
@@ -8484,14 +8451,14 @@
       <c r="E42" s="72">
         <v>59000</v>
       </c>
-      <c r="F42" s="304"/>
+      <c r="F42" s="337"/>
       <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>10</v>
       </c>
-      <c r="B43" s="315"/>
+      <c r="B43" s="339"/>
       <c r="C43" s="42" t="s">
         <v>68</v>
       </c>
@@ -8501,14 +8468,14 @@
       <c r="E43" s="72">
         <v>47000</v>
       </c>
-      <c r="F43" s="304"/>
+      <c r="F43" s="337"/>
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>11</v>
       </c>
-      <c r="B44" s="315"/>
+      <c r="B44" s="339"/>
       <c r="C44" s="42" t="s">
         <v>70</v>
       </c>
@@ -8518,7 +8485,7 @@
       <c r="E44" s="72">
         <v>41000</v>
       </c>
-      <c r="F44" s="305"/>
+      <c r="F44" s="338"/>
       <c r="G44" s="12"/>
     </row>
     <row r="45" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -8544,7 +8511,7 @@
       <c r="A46" s="38">
         <v>13</v>
       </c>
-      <c r="B46" s="301" t="s">
+      <c r="B46" s="319" t="s">
         <v>278</v>
       </c>
       <c r="C46" s="36" t="s">
@@ -8556,7 +8523,7 @@
       <c r="E46" s="75">
         <v>62000</v>
       </c>
-      <c r="F46" s="303" t="s">
+      <c r="F46" s="336" t="s">
         <v>380</v>
       </c>
       <c r="G46" s="12"/>
@@ -8565,7 +8532,7 @@
       <c r="A47" s="38">
         <v>14</v>
       </c>
-      <c r="B47" s="322"/>
+      <c r="B47" s="320"/>
       <c r="C47" s="36" t="s">
         <v>197</v>
       </c>
@@ -8575,14 +8542,14 @@
       <c r="E47" s="75">
         <v>165000</v>
       </c>
-      <c r="F47" s="304"/>
+      <c r="F47" s="337"/>
       <c r="G47" s="12"/>
     </row>
     <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>15</v>
       </c>
-      <c r="B48" s="302"/>
+      <c r="B48" s="321"/>
       <c r="C48" s="36" t="s">
         <v>202</v>
       </c>
@@ -8592,14 +8559,14 @@
       <c r="E48" s="75">
         <v>116000</v>
       </c>
-      <c r="F48" s="305"/>
+      <c r="F48" s="338"/>
       <c r="G48" s="12"/>
     </row>
     <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>16</v>
       </c>
-      <c r="B49" s="301" t="s">
+      <c r="B49" s="319" t="s">
         <v>273</v>
       </c>
       <c r="C49" s="36" t="s">
@@ -8618,7 +8585,7 @@
       <c r="A50" s="38">
         <v>17</v>
       </c>
-      <c r="B50" s="322"/>
+      <c r="B50" s="320"/>
       <c r="C50" s="36" t="s">
         <v>270</v>
       </c>
@@ -8628,7 +8595,7 @@
       <c r="E50" s="75">
         <v>130000</v>
       </c>
-      <c r="F50" s="303" t="s">
+      <c r="F50" s="336" t="s">
         <v>380</v>
       </c>
       <c r="G50" s="12"/>
@@ -8637,7 +8604,7 @@
       <c r="A51" s="38">
         <v>18</v>
       </c>
-      <c r="B51" s="322"/>
+      <c r="B51" s="320"/>
       <c r="C51" s="36" t="s">
         <v>271</v>
       </c>
@@ -8647,14 +8614,14 @@
       <c r="E51" s="75">
         <v>120000</v>
       </c>
-      <c r="F51" s="304"/>
+      <c r="F51" s="337"/>
       <c r="G51" s="12"/>
     </row>
     <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>19</v>
       </c>
-      <c r="B52" s="302"/>
+      <c r="B52" s="321"/>
       <c r="C52" s="36" t="s">
         <v>272</v>
       </c>
@@ -8664,7 +8631,7 @@
       <c r="E52" s="75">
         <v>282000</v>
       </c>
-      <c r="F52" s="305"/>
+      <c r="F52" s="338"/>
       <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -8690,7 +8657,7 @@
       <c r="A54" s="38">
         <v>21</v>
       </c>
-      <c r="B54" s="317" t="s">
+      <c r="B54" s="342" t="s">
         <v>131</v>
       </c>
       <c r="C54" s="36" t="s">
@@ -8702,7 +8669,7 @@
       <c r="E54" s="75">
         <v>71000</v>
       </c>
-      <c r="F54" s="306" t="s">
+      <c r="F54" s="305" t="s">
         <v>382</v>
       </c>
       <c r="G54" s="12"/>
@@ -8711,7 +8678,7 @@
       <c r="A55" s="38">
         <v>22</v>
       </c>
-      <c r="B55" s="318"/>
+      <c r="B55" s="344"/>
       <c r="C55" s="36" t="s">
         <v>134</v>
       </c>
@@ -8721,7 +8688,7 @@
       <c r="E55" s="71">
         <v>138000</v>
       </c>
-      <c r="F55" s="307"/>
+      <c r="F55" s="306"/>
       <c r="G55" s="12"/>
     </row>
     <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -8747,7 +8714,7 @@
       <c r="A57" s="38">
         <v>24</v>
       </c>
-      <c r="B57" s="316" t="s">
+      <c r="B57" s="360" t="s">
         <v>206</v>
       </c>
       <c r="C57" s="36" t="s">
@@ -8759,7 +8726,7 @@
       <c r="E57" s="75">
         <v>30000</v>
       </c>
-      <c r="F57" s="308" t="s">
+      <c r="F57" s="353" t="s">
         <v>384</v>
       </c>
       <c r="G57" s="13"/>
@@ -8768,7 +8735,7 @@
       <c r="A58" s="38">
         <v>25</v>
       </c>
-      <c r="B58" s="316"/>
+      <c r="B58" s="360"/>
       <c r="C58" s="36" t="s">
         <v>279</v>
       </c>
@@ -8778,16 +8745,16 @@
       <c r="E58" s="75">
         <v>20000</v>
       </c>
-      <c r="F58" s="309"/>
+      <c r="F58" s="354"/>
       <c r="G58" s="13"/>
     </row>
     <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="298" t="s">
+      <c r="A59" s="332" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="299"/>
-      <c r="C59" s="299"/>
-      <c r="D59" s="300"/>
+      <c r="B59" s="333"/>
+      <c r="C59" s="333"/>
+      <c r="D59" s="334"/>
       <c r="E59" s="69"/>
       <c r="F59" s="70"/>
       <c r="G59" s="12"/>
@@ -8796,7 +8763,7 @@
       <c r="A60" s="38">
         <v>26</v>
       </c>
-      <c r="B60" s="310" t="s">
+      <c r="B60" s="355" t="s">
         <v>261</v>
       </c>
       <c r="C60" s="76" t="s">
@@ -8815,7 +8782,7 @@
       <c r="A61" s="38">
         <v>27</v>
       </c>
-      <c r="B61" s="311"/>
+      <c r="B61" s="356"/>
       <c r="C61" s="76" t="s">
         <v>84</v>
       </c>
@@ -8832,7 +8799,7 @@
       <c r="A62" s="38">
         <v>28</v>
       </c>
-      <c r="B62" s="311"/>
+      <c r="B62" s="356"/>
       <c r="C62" s="76" t="s">
         <v>86</v>
       </c>
@@ -8849,7 +8816,7 @@
       <c r="A63" s="38">
         <v>29</v>
       </c>
-      <c r="B63" s="311"/>
+      <c r="B63" s="356"/>
       <c r="C63" s="76" t="s">
         <v>80</v>
       </c>
@@ -8866,7 +8833,7 @@
       <c r="A64" s="38">
         <v>30</v>
       </c>
-      <c r="B64" s="311"/>
+      <c r="B64" s="356"/>
       <c r="C64" s="76" t="s">
         <v>94</v>
       </c>
@@ -8883,7 +8850,7 @@
       <c r="A65" s="38">
         <v>31</v>
       </c>
-      <c r="B65" s="311"/>
+      <c r="B65" s="356"/>
       <c r="C65" s="76" t="s">
         <v>81</v>
       </c>
@@ -8900,7 +8867,7 @@
       <c r="A66" s="38">
         <v>32</v>
       </c>
-      <c r="B66" s="311"/>
+      <c r="B66" s="356"/>
       <c r="C66" s="76" t="s">
         <v>83</v>
       </c>
@@ -8919,7 +8886,7 @@
       <c r="A67" s="38">
         <v>33</v>
       </c>
-      <c r="B67" s="311"/>
+      <c r="B67" s="356"/>
       <c r="C67" s="80" t="s">
         <v>235</v>
       </c>
@@ -8936,7 +8903,7 @@
       <c r="A68" s="38">
         <v>34</v>
       </c>
-      <c r="B68" s="311"/>
+      <c r="B68" s="356"/>
       <c r="C68" s="76" t="s">
         <v>74</v>
       </c>
@@ -8955,7 +8922,7 @@
       <c r="A69" s="38">
         <v>35</v>
       </c>
-      <c r="B69" s="311"/>
+      <c r="B69" s="356"/>
       <c r="C69" s="76" t="s">
         <v>76</v>
       </c>
@@ -8972,7 +8939,7 @@
       <c r="A70" s="38">
         <v>36</v>
       </c>
-      <c r="B70" s="311"/>
+      <c r="B70" s="356"/>
       <c r="C70" s="76" t="s">
         <v>78</v>
       </c>
@@ -8989,7 +8956,7 @@
       <c r="A71" s="38">
         <v>37</v>
       </c>
-      <c r="B71" s="311"/>
+      <c r="B71" s="356"/>
       <c r="C71" s="76" t="s">
         <v>88</v>
       </c>
@@ -9006,7 +8973,7 @@
       <c r="A72" s="38">
         <v>38</v>
       </c>
-      <c r="B72" s="312"/>
+      <c r="B72" s="357"/>
       <c r="C72" s="76" t="s">
         <v>96</v>
       </c>
@@ -9023,19 +8990,19 @@
       <c r="A73" s="38">
         <v>39</v>
       </c>
-      <c r="B73" s="310" t="s">
+      <c r="B73" s="355" t="s">
         <v>91</v>
       </c>
       <c r="C73" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="D73" s="319" t="s">
+      <c r="D73" s="361" t="s">
         <v>398</v>
       </c>
       <c r="E73" s="78">
         <v>137000</v>
       </c>
-      <c r="F73" s="303" t="s">
+      <c r="F73" s="336" t="s">
         <v>381</v>
       </c>
       <c r="G73" s="13"/>
@@ -9044,43 +9011,43 @@
       <c r="A74" s="38">
         <v>40</v>
       </c>
-      <c r="B74" s="311"/>
+      <c r="B74" s="356"/>
       <c r="C74" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="D74" s="320"/>
+      <c r="D74" s="362"/>
       <c r="E74" s="78">
         <v>137000</v>
       </c>
-      <c r="F74" s="304"/>
+      <c r="F74" s="337"/>
       <c r="G74" s="13"/>
     </row>
     <row r="75" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A75" s="38">
         <v>41</v>
       </c>
-      <c r="B75" s="312"/>
+      <c r="B75" s="357"/>
       <c r="C75" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="D75" s="321"/>
+      <c r="D75" s="363"/>
       <c r="E75" s="78">
         <v>208000</v>
       </c>
-      <c r="F75" s="305"/>
+      <c r="F75" s="338"/>
       <c r="G75" s="13"/>
     </row>
     <row r="76" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>42</v>
       </c>
-      <c r="B76" s="310" t="s">
+      <c r="B76" s="355" t="s">
         <v>399</v>
       </c>
       <c r="C76" s="76" t="s">
         <v>400</v>
       </c>
-      <c r="D76" s="313" t="s">
+      <c r="D76" s="358" t="s">
         <v>402</v>
       </c>
       <c r="E76" s="78">
@@ -9093,11 +9060,11 @@
       <c r="A77" s="38">
         <v>43</v>
       </c>
-      <c r="B77" s="311"/>
+      <c r="B77" s="356"/>
       <c r="C77" s="76" t="s">
         <v>401</v>
       </c>
-      <c r="D77" s="314"/>
+      <c r="D77" s="359"/>
       <c r="E77" s="78">
         <v>323000</v>
       </c>
@@ -9108,7 +9075,7 @@
       <c r="A78" s="38">
         <v>44</v>
       </c>
-      <c r="B78" s="311"/>
+      <c r="B78" s="356"/>
       <c r="C78" s="76" t="s">
         <v>404</v>
       </c>
@@ -9125,7 +9092,7 @@
       <c r="A79" s="38">
         <v>45</v>
       </c>
-      <c r="B79" s="312"/>
+      <c r="B79" s="357"/>
       <c r="C79" s="76" t="s">
         <v>405</v>
       </c>
@@ -9139,12 +9106,12 @@
       <c r="G79" s="13"/>
     </row>
     <row r="80" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="298" t="s">
+      <c r="A80" s="332" t="s">
         <v>208</v>
       </c>
-      <c r="B80" s="299"/>
-      <c r="C80" s="299"/>
-      <c r="D80" s="300"/>
+      <c r="B80" s="333"/>
+      <c r="C80" s="333"/>
+      <c r="D80" s="334"/>
       <c r="E80" s="69"/>
       <c r="F80" s="70"/>
       <c r="G80" s="13"/>
@@ -9153,7 +9120,7 @@
       <c r="A81" s="38">
         <v>46</v>
       </c>
-      <c r="B81" s="315" t="s">
+      <c r="B81" s="339" t="s">
         <v>98</v>
       </c>
       <c r="C81" s="36" t="s">
@@ -9172,7 +9139,7 @@
       <c r="A82" s="38">
         <v>47</v>
       </c>
-      <c r="B82" s="315"/>
+      <c r="B82" s="339"/>
       <c r="C82" s="36" t="s">
         <v>101</v>
       </c>
@@ -9189,7 +9156,7 @@
       <c r="A83" s="38">
         <v>48</v>
       </c>
-      <c r="B83" s="315"/>
+      <c r="B83" s="339"/>
       <c r="C83" s="36" t="s">
         <v>103</v>
       </c>
@@ -9208,7 +9175,7 @@
       <c r="A84" s="38">
         <v>49</v>
       </c>
-      <c r="B84" s="315"/>
+      <c r="B84" s="339"/>
       <c r="C84" s="36" t="s">
         <v>106</v>
       </c>
@@ -9227,7 +9194,7 @@
       <c r="A85" s="38">
         <v>50</v>
       </c>
-      <c r="B85" s="315"/>
+      <c r="B85" s="339"/>
       <c r="C85" s="36" t="s">
         <v>407</v>
       </c>
@@ -9244,7 +9211,7 @@
       <c r="A86" s="38">
         <v>51</v>
       </c>
-      <c r="B86" s="315"/>
+      <c r="B86" s="339"/>
       <c r="C86" s="36" t="s">
         <v>108</v>
       </c>
@@ -9263,7 +9230,7 @@
       <c r="A87" s="38">
         <v>52</v>
       </c>
-      <c r="B87" s="315"/>
+      <c r="B87" s="339"/>
       <c r="C87" s="36" t="s">
         <v>111</v>
       </c>
@@ -9282,7 +9249,7 @@
       <c r="A88" s="38">
         <v>53</v>
       </c>
-      <c r="B88" s="315"/>
+      <c r="B88" s="339"/>
       <c r="C88" s="36" t="s">
         <v>114</v>
       </c>
@@ -9301,7 +9268,7 @@
       <c r="A89" s="38">
         <v>54</v>
       </c>
-      <c r="B89" s="315" t="s">
+      <c r="B89" s="339" t="s">
         <v>117</v>
       </c>
       <c r="C89" s="36" t="s">
@@ -9320,7 +9287,7 @@
       <c r="A90" s="38">
         <v>55</v>
       </c>
-      <c r="B90" s="315"/>
+      <c r="B90" s="339"/>
       <c r="C90" s="36" t="s">
         <v>120</v>
       </c>
@@ -9337,7 +9304,7 @@
       <c r="A91" s="38">
         <v>56</v>
       </c>
-      <c r="B91" s="317" t="s">
+      <c r="B91" s="342" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="36" t="s">
@@ -9356,7 +9323,7 @@
       <c r="A92" s="38">
         <v>57</v>
       </c>
-      <c r="B92" s="325"/>
+      <c r="B92" s="343"/>
       <c r="C92" s="36" t="s">
         <v>390</v>
       </c>
@@ -9373,7 +9340,7 @@
       <c r="A93" s="38">
         <v>58</v>
       </c>
-      <c r="B93" s="318"/>
+      <c r="B93" s="344"/>
       <c r="C93" s="36" t="s">
         <v>126</v>
       </c>
@@ -9387,12 +9354,12 @@
       <c r="G93" s="12"/>
     </row>
     <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="298" t="s">
+      <c r="A94" s="332" t="s">
         <v>262</v>
       </c>
-      <c r="B94" s="299"/>
-      <c r="C94" s="299"/>
-      <c r="D94" s="300"/>
+      <c r="B94" s="333"/>
+      <c r="C94" s="333"/>
+      <c r="D94" s="334"/>
       <c r="E94" s="83"/>
       <c r="F94" s="70"/>
       <c r="G94" s="12"/>
@@ -9401,7 +9368,7 @@
       <c r="A95" s="38">
         <v>59</v>
       </c>
-      <c r="B95" s="317" t="s">
+      <c r="B95" s="342" t="s">
         <v>241</v>
       </c>
       <c r="C95" s="36" t="s">
@@ -9420,7 +9387,7 @@
       <c r="A96" s="38">
         <v>60</v>
       </c>
-      <c r="B96" s="318"/>
+      <c r="B96" s="344"/>
       <c r="C96" s="36" t="s">
         <v>240</v>
       </c>
@@ -9437,7 +9404,7 @@
       <c r="A97" s="38">
         <v>61</v>
       </c>
-      <c r="B97" s="317" t="s">
+      <c r="B97" s="342" t="s">
         <v>244</v>
       </c>
       <c r="C97" s="36" t="s">
@@ -9454,7 +9421,7 @@
       <c r="A98" s="38">
         <v>62</v>
       </c>
-      <c r="B98" s="318"/>
+      <c r="B98" s="344"/>
       <c r="C98" s="36" t="s">
         <v>243</v>
       </c>
@@ -9488,7 +9455,7 @@
       <c r="A100" s="38">
         <v>64</v>
       </c>
-      <c r="B100" s="317" t="s">
+      <c r="B100" s="342" t="s">
         <v>259</v>
       </c>
       <c r="C100" s="36" t="s">
@@ -9505,7 +9472,7 @@
       <c r="A101" s="38">
         <v>65</v>
       </c>
-      <c r="B101" s="325"/>
+      <c r="B101" s="343"/>
       <c r="C101" s="36" t="s">
         <v>246</v>
       </c>
@@ -9520,7 +9487,7 @@
       <c r="A102" s="38">
         <v>66</v>
       </c>
-      <c r="B102" s="325"/>
+      <c r="B102" s="343"/>
       <c r="C102" s="36" t="s">
         <v>247</v>
       </c>
@@ -9535,7 +9502,7 @@
       <c r="A103" s="38">
         <v>67</v>
       </c>
-      <c r="B103" s="325"/>
+      <c r="B103" s="343"/>
       <c r="C103" s="36" t="s">
         <v>248</v>
       </c>
@@ -9550,7 +9517,7 @@
       <c r="A104" s="38">
         <v>68</v>
       </c>
-      <c r="B104" s="325"/>
+      <c r="B104" s="343"/>
       <c r="C104" s="36" t="s">
         <v>249</v>
       </c>
@@ -9565,7 +9532,7 @@
       <c r="A105" s="38">
         <v>69</v>
       </c>
-      <c r="B105" s="325"/>
+      <c r="B105" s="343"/>
       <c r="C105" s="36" t="s">
         <v>250</v>
       </c>
@@ -9580,7 +9547,7 @@
       <c r="A106" s="38">
         <v>70</v>
       </c>
-      <c r="B106" s="325"/>
+      <c r="B106" s="343"/>
       <c r="C106" s="36" t="s">
         <v>251</v>
       </c>
@@ -9595,7 +9562,7 @@
       <c r="A107" s="38">
         <v>71</v>
       </c>
-      <c r="B107" s="325"/>
+      <c r="B107" s="343"/>
       <c r="C107" s="36" t="s">
         <v>252</v>
       </c>
@@ -9610,7 +9577,7 @@
       <c r="A108" s="38">
         <v>72</v>
       </c>
-      <c r="B108" s="325"/>
+      <c r="B108" s="343"/>
       <c r="C108" s="36" t="s">
         <v>253</v>
       </c>
@@ -9625,7 +9592,7 @@
       <c r="A109" s="38">
         <v>73</v>
       </c>
-      <c r="B109" s="325"/>
+      <c r="B109" s="343"/>
       <c r="C109" s="36" t="s">
         <v>254</v>
       </c>
@@ -9640,7 +9607,7 @@
       <c r="A110" s="38">
         <v>74</v>
       </c>
-      <c r="B110" s="325"/>
+      <c r="B110" s="343"/>
       <c r="C110" s="36" t="s">
         <v>255</v>
       </c>
@@ -9655,7 +9622,7 @@
       <c r="A111" s="38">
         <v>75</v>
       </c>
-      <c r="B111" s="325"/>
+      <c r="B111" s="343"/>
       <c r="C111" s="36" t="s">
         <v>256</v>
       </c>
@@ -9670,7 +9637,7 @@
       <c r="A112" s="38">
         <v>76</v>
       </c>
-      <c r="B112" s="325"/>
+      <c r="B112" s="343"/>
       <c r="C112" s="36" t="s">
         <v>257</v>
       </c>
@@ -9685,7 +9652,7 @@
       <c r="A113" s="38">
         <v>77</v>
       </c>
-      <c r="B113" s="318"/>
+      <c r="B113" s="344"/>
       <c r="C113" s="36" t="s">
         <v>258</v>
       </c>
@@ -9697,12 +9664,12 @@
       <c r="G113" s="12"/>
     </row>
     <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="298" t="s">
+      <c r="A114" s="332" t="s">
         <v>227</v>
       </c>
-      <c r="B114" s="299"/>
-      <c r="C114" s="299"/>
-      <c r="D114" s="300"/>
+      <c r="B114" s="333"/>
+      <c r="C114" s="333"/>
+      <c r="D114" s="334"/>
       <c r="E114" s="69"/>
       <c r="F114" s="70"/>
       <c r="G114" s="12"/>
@@ -9746,12 +9713,12 @@
       <c r="G116" s="12"/>
     </row>
     <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="326" t="s">
+      <c r="A117" s="329" t="s">
         <v>263</v>
       </c>
-      <c r="B117" s="326"/>
-      <c r="C117" s="326"/>
-      <c r="D117" s="326"/>
+      <c r="B117" s="329"/>
+      <c r="C117" s="329"/>
+      <c r="D117" s="329"/>
       <c r="E117" s="84"/>
       <c r="F117" s="70"/>
       <c r="G117" s="12"/>
@@ -9760,7 +9727,7 @@
       <c r="A118" s="38">
         <v>80</v>
       </c>
-      <c r="B118" s="332" t="s">
+      <c r="B118" s="350" t="s">
         <v>205</v>
       </c>
       <c r="C118" s="37" t="s">
@@ -9779,7 +9746,7 @@
       <c r="A119" s="38">
         <v>81</v>
       </c>
-      <c r="B119" s="333"/>
+      <c r="B119" s="351"/>
       <c r="C119" s="37" t="s">
         <v>35</v>
       </c>
@@ -9796,7 +9763,7 @@
       <c r="A120" s="38">
         <v>82</v>
       </c>
-      <c r="B120" s="333"/>
+      <c r="B120" s="351"/>
       <c r="C120" s="37" t="s">
         <v>326</v>
       </c>
@@ -9810,10 +9777,10 @@
       <c r="G120" s="12"/>
     </row>
     <row r="121" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A121" s="327">
+      <c r="A121" s="345">
         <v>83</v>
       </c>
-      <c r="B121" s="333"/>
+      <c r="B121" s="351"/>
       <c r="C121" s="36" t="s">
         <v>409</v>
       </c>
@@ -9825,8 +9792,8 @@
       <c r="G121" s="12"/>
     </row>
     <row r="122" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="328"/>
-      <c r="B122" s="333"/>
+      <c r="A122" s="346"/>
+      <c r="B122" s="351"/>
       <c r="C122" s="36" t="s">
         <v>410</v>
       </c>
@@ -9838,8 +9805,8 @@
       <c r="G122" s="12"/>
     </row>
     <row r="123" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="329"/>
-      <c r="B123" s="333"/>
+      <c r="A123" s="347"/>
+      <c r="B123" s="351"/>
       <c r="C123" s="36" t="s">
         <v>411</v>
       </c>
@@ -9854,7 +9821,7 @@
       <c r="A124" s="38">
         <v>84</v>
       </c>
-      <c r="B124" s="333"/>
+      <c r="B124" s="351"/>
       <c r="C124" s="37" t="s">
         <v>412</v>
       </c>
@@ -9871,7 +9838,7 @@
       <c r="A125" s="38">
         <v>85</v>
       </c>
-      <c r="B125" s="333"/>
+      <c r="B125" s="351"/>
       <c r="C125" s="37" t="s">
         <v>139</v>
       </c>
@@ -9888,7 +9855,7 @@
       <c r="A126" s="38">
         <v>86</v>
       </c>
-      <c r="B126" s="334"/>
+      <c r="B126" s="352"/>
       <c r="C126" s="37" t="s">
         <v>140</v>
       </c>
@@ -9905,7 +9872,7 @@
       <c r="A127" s="38">
         <v>87</v>
       </c>
-      <c r="B127" s="301" t="s">
+      <c r="B127" s="319" t="s">
         <v>283</v>
       </c>
       <c r="C127" s="36" t="s">
@@ -9924,7 +9891,7 @@
       <c r="A128" s="38">
         <v>88</v>
       </c>
-      <c r="B128" s="322"/>
+      <c r="B128" s="320"/>
       <c r="C128" s="36" t="s">
         <v>144</v>
       </c>
@@ -9941,7 +9908,7 @@
       <c r="A129" s="38">
         <v>89</v>
       </c>
-      <c r="B129" s="322"/>
+      <c r="B129" s="320"/>
       <c r="C129" s="36" t="s">
         <v>394</v>
       </c>
@@ -9958,7 +9925,7 @@
       <c r="A130" s="38">
         <v>90</v>
       </c>
-      <c r="B130" s="322"/>
+      <c r="B130" s="320"/>
       <c r="C130" s="36" t="s">
         <v>396</v>
       </c>
@@ -9975,7 +9942,7 @@
       <c r="A131" s="38">
         <v>91</v>
       </c>
-      <c r="B131" s="322"/>
+      <c r="B131" s="320"/>
       <c r="C131" s="36" t="s">
         <v>371</v>
       </c>
@@ -9992,7 +9959,7 @@
       <c r="A132" s="38">
         <v>92</v>
       </c>
-      <c r="B132" s="302"/>
+      <c r="B132" s="321"/>
       <c r="C132" s="36" t="s">
         <v>146</v>
       </c>
@@ -10007,7 +9974,7 @@
       <c r="A133" s="38">
         <v>93</v>
       </c>
-      <c r="B133" s="322" t="s">
+      <c r="B133" s="320" t="s">
         <v>284</v>
       </c>
       <c r="C133" s="36" t="s">
@@ -10024,7 +9991,7 @@
       <c r="A134" s="38">
         <v>94</v>
       </c>
-      <c r="B134" s="322"/>
+      <c r="B134" s="320"/>
       <c r="C134" s="36" t="s">
         <v>332</v>
       </c>
@@ -10041,7 +10008,7 @@
       <c r="A135" s="38">
         <v>95</v>
       </c>
-      <c r="B135" s="322"/>
+      <c r="B135" s="320"/>
       <c r="C135" s="36" t="s">
         <v>152</v>
       </c>
@@ -10058,7 +10025,7 @@
       <c r="A136" s="38">
         <v>96</v>
       </c>
-      <c r="B136" s="322"/>
+      <c r="B136" s="320"/>
       <c r="C136" s="36" t="s">
         <v>154</v>
       </c>
@@ -10075,7 +10042,7 @@
       <c r="A137" s="38">
         <v>97</v>
       </c>
-      <c r="B137" s="322"/>
+      <c r="B137" s="320"/>
       <c r="C137" s="36" t="s">
         <v>156</v>
       </c>
@@ -10092,7 +10059,7 @@
       <c r="A138" s="38">
         <v>98</v>
       </c>
-      <c r="B138" s="322"/>
+      <c r="B138" s="320"/>
       <c r="C138" s="36" t="s">
         <v>158</v>
       </c>
@@ -10109,7 +10076,7 @@
       <c r="A139" s="38">
         <v>99</v>
       </c>
-      <c r="B139" s="322"/>
+      <c r="B139" s="320"/>
       <c r="C139" s="36" t="s">
         <v>159</v>
       </c>
@@ -10124,7 +10091,7 @@
       <c r="A140" s="38">
         <v>100</v>
       </c>
-      <c r="B140" s="342" t="s">
+      <c r="B140" s="298" t="s">
         <v>305</v>
       </c>
       <c r="C140" s="36" t="s">
@@ -10137,16 +10104,16 @@
         <v>3420000</v>
       </c>
       <c r="F140" s="41"/>
-      <c r="G140" s="323" t="s">
+      <c r="G140" s="340" t="s">
         <v>336</v>
       </c>
-      <c r="H140" s="324"/>
+      <c r="H140" s="341"/>
     </row>
     <row r="141" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A141" s="38">
         <v>101</v>
       </c>
-      <c r="B141" s="342"/>
+      <c r="B141" s="298"/>
       <c r="C141" s="36" t="s">
         <v>344</v>
       </c>
@@ -10163,7 +10130,7 @@
       <c r="A142" s="38">
         <v>102</v>
       </c>
-      <c r="B142" s="342"/>
+      <c r="B142" s="298"/>
       <c r="C142" s="36" t="s">
         <v>345</v>
       </c>
@@ -10174,16 +10141,16 @@
         <v>3420000</v>
       </c>
       <c r="F142" s="41"/>
-      <c r="G142" s="323" t="s">
+      <c r="G142" s="340" t="s">
         <v>336</v>
       </c>
-      <c r="H142" s="324"/>
+      <c r="H142" s="341"/>
     </row>
     <row r="143" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A143" s="38">
         <v>103</v>
       </c>
-      <c r="B143" s="342"/>
+      <c r="B143" s="298"/>
       <c r="C143" s="36" t="s">
         <v>346</v>
       </c>
@@ -10200,7 +10167,7 @@
       <c r="A144" s="38">
         <v>104</v>
       </c>
-      <c r="B144" s="342"/>
+      <c r="B144" s="298"/>
       <c r="C144" s="36" t="s">
         <v>347</v>
       </c>
@@ -10217,7 +10184,7 @@
       <c r="A145" s="38">
         <v>105</v>
       </c>
-      <c r="B145" s="342"/>
+      <c r="B145" s="298"/>
       <c r="C145" s="118" t="s">
         <v>374</v>
       </c>
@@ -10234,7 +10201,7 @@
       <c r="A146" s="38">
         <v>106</v>
       </c>
-      <c r="B146" s="342"/>
+      <c r="B146" s="298"/>
       <c r="C146" s="36" t="s">
         <v>348</v>
       </c>
@@ -10251,7 +10218,7 @@
       <c r="A147" s="38">
         <v>107</v>
       </c>
-      <c r="B147" s="342"/>
+      <c r="B147" s="298"/>
       <c r="C147" s="36" t="s">
         <v>349</v>
       </c>
@@ -10268,7 +10235,7 @@
       <c r="A148" s="38">
         <v>108</v>
       </c>
-      <c r="B148" s="342"/>
+      <c r="B148" s="298"/>
       <c r="C148" s="36" t="s">
         <v>350</v>
       </c>
@@ -10285,7 +10252,7 @@
       <c r="A149" s="38">
         <v>109</v>
       </c>
-      <c r="B149" s="342"/>
+      <c r="B149" s="298"/>
       <c r="C149" s="118" t="s">
         <v>373</v>
       </c>
@@ -10302,7 +10269,7 @@
       <c r="A150" s="38">
         <v>110</v>
       </c>
-      <c r="B150" s="342"/>
+      <c r="B150" s="298"/>
       <c r="C150" s="36" t="s">
         <v>351</v>
       </c>
@@ -10321,7 +10288,7 @@
       <c r="A151" s="38">
         <v>111</v>
       </c>
-      <c r="B151" s="342"/>
+      <c r="B151" s="298"/>
       <c r="C151" s="36" t="s">
         <v>352</v>
       </c>
@@ -10338,7 +10305,7 @@
       <c r="A152" s="38">
         <v>112</v>
       </c>
-      <c r="B152" s="342"/>
+      <c r="B152" s="298"/>
       <c r="C152" s="36" t="s">
         <v>353</v>
       </c>
@@ -10355,7 +10322,7 @@
       <c r="A153" s="38">
         <v>113</v>
       </c>
-      <c r="B153" s="342"/>
+      <c r="B153" s="298"/>
       <c r="C153" s="36" t="s">
         <v>354</v>
       </c>
@@ -10372,7 +10339,7 @@
       <c r="A154" s="38">
         <v>114</v>
       </c>
-      <c r="B154" s="342"/>
+      <c r="B154" s="298"/>
       <c r="C154" s="36" t="s">
         <v>355</v>
       </c>
@@ -10389,7 +10356,7 @@
       <c r="A155" s="38">
         <v>115</v>
       </c>
-      <c r="B155" s="342"/>
+      <c r="B155" s="298"/>
       <c r="C155" s="36" t="s">
         <v>356</v>
       </c>
@@ -10406,7 +10373,7 @@
       <c r="A156" s="38">
         <v>116</v>
       </c>
-      <c r="B156" s="342"/>
+      <c r="B156" s="298"/>
       <c r="C156" s="36" t="s">
         <v>357</v>
       </c>
@@ -10423,7 +10390,7 @@
       <c r="A157" s="38">
         <v>117</v>
       </c>
-      <c r="B157" s="342"/>
+      <c r="B157" s="298"/>
       <c r="C157" s="36" t="s">
         <v>358</v>
       </c>
@@ -10440,7 +10407,7 @@
       <c r="A158" s="38">
         <v>118</v>
       </c>
-      <c r="B158" s="342"/>
+      <c r="B158" s="298"/>
       <c r="C158" s="36" t="s">
         <v>359</v>
       </c>
@@ -10457,7 +10424,7 @@
       <c r="A159" s="38">
         <v>119</v>
       </c>
-      <c r="B159" s="342"/>
+      <c r="B159" s="298"/>
       <c r="C159" s="36" t="s">
         <v>360</v>
       </c>
@@ -10474,7 +10441,7 @@
       <c r="A160" s="38">
         <v>120</v>
       </c>
-      <c r="B160" s="342"/>
+      <c r="B160" s="298"/>
       <c r="C160" s="36" t="s">
         <v>361</v>
       </c>
@@ -10491,7 +10458,7 @@
       <c r="A161" s="38">
         <v>121</v>
       </c>
-      <c r="B161" s="342"/>
+      <c r="B161" s="298"/>
       <c r="C161" s="36" t="s">
         <v>362</v>
       </c>
@@ -10508,7 +10475,7 @@
       <c r="A162" s="38">
         <v>122</v>
       </c>
-      <c r="B162" s="342"/>
+      <c r="B162" s="298"/>
       <c r="C162" s="36" t="s">
         <v>363</v>
       </c>
@@ -10525,7 +10492,7 @@
       <c r="A163" s="38">
         <v>123</v>
       </c>
-      <c r="B163" s="342"/>
+      <c r="B163" s="298"/>
       <c r="C163" s="36" t="s">
         <v>364</v>
       </c>
@@ -10542,7 +10509,7 @@
       <c r="A164" s="38">
         <v>124</v>
       </c>
-      <c r="B164" s="342"/>
+      <c r="B164" s="298"/>
       <c r="C164" s="36" t="s">
         <v>365</v>
       </c>
@@ -10557,7 +10524,7 @@
       <c r="A165" s="38">
         <v>125</v>
       </c>
-      <c r="B165" s="342"/>
+      <c r="B165" s="298"/>
       <c r="C165" s="36" t="s">
         <v>366</v>
       </c>
@@ -10572,7 +10539,7 @@
       <c r="A166" s="38">
         <v>126</v>
       </c>
-      <c r="B166" s="342"/>
+      <c r="B166" s="298"/>
       <c r="C166" s="36" t="s">
         <v>367</v>
       </c>
@@ -10589,7 +10556,7 @@
       <c r="A167" s="38">
         <v>127</v>
       </c>
-      <c r="B167" s="342"/>
+      <c r="B167" s="298"/>
       <c r="C167" s="36" t="s">
         <v>368</v>
       </c>
@@ -10606,7 +10573,7 @@
       <c r="A168" s="38">
         <v>128</v>
       </c>
-      <c r="B168" s="342"/>
+      <c r="B168" s="298"/>
       <c r="C168" s="36" t="s">
         <v>369</v>
       </c>
@@ -10623,7 +10590,7 @@
       <c r="A169" s="38">
         <v>129</v>
       </c>
-      <c r="B169" s="342"/>
+      <c r="B169" s="298"/>
       <c r="C169" s="36" t="s">
         <v>370</v>
       </c>
@@ -10637,12 +10604,12 @@
       <c r="G169" s="12"/>
     </row>
     <row r="170" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="326" t="s">
+      <c r="A170" s="329" t="s">
         <v>207</v>
       </c>
-      <c r="B170" s="326"/>
-      <c r="C170" s="326"/>
-      <c r="D170" s="326"/>
+      <c r="B170" s="329"/>
+      <c r="C170" s="329"/>
+      <c r="D170" s="329"/>
       <c r="E170" s="84"/>
       <c r="F170" s="70"/>
       <c r="G170" s="12"/>
@@ -10703,7 +10670,7 @@
       <c r="A174" s="38">
         <v>133</v>
       </c>
-      <c r="B174" s="301" t="s">
+      <c r="B174" s="319" t="s">
         <v>204</v>
       </c>
       <c r="C174" s="36" t="s">
@@ -10721,7 +10688,7 @@
       <c r="A175" s="38">
         <v>134</v>
       </c>
-      <c r="B175" s="302"/>
+      <c r="B175" s="321"/>
       <c r="C175" s="36" t="s">
         <v>225</v>
       </c>
@@ -10734,12 +10701,12 @@
       <c r="F175" s="41"/>
     </row>
     <row r="176" spans="1:8" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="298" t="s">
+      <c r="A176" s="332" t="s">
         <v>164</v>
       </c>
-      <c r="B176" s="299"/>
-      <c r="C176" s="299"/>
-      <c r="D176" s="300"/>
+      <c r="B176" s="333"/>
+      <c r="C176" s="333"/>
+      <c r="D176" s="334"/>
       <c r="E176" s="65"/>
       <c r="F176" s="65"/>
     </row>
@@ -10757,7 +10724,7 @@
       <c r="E177" s="90">
         <v>71000</v>
       </c>
-      <c r="F177" s="330" t="s">
+      <c r="F177" s="348" t="s">
         <v>385</v>
       </c>
     </row>
@@ -10775,15 +10742,15 @@
       <c r="E178" s="90">
         <v>86000</v>
       </c>
-      <c r="F178" s="331"/>
+      <c r="F178" s="349"/>
     </row>
     <row r="179" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="326" t="s">
+      <c r="A179" s="329" t="s">
         <v>169</v>
       </c>
-      <c r="B179" s="326"/>
-      <c r="C179" s="326"/>
-      <c r="D179" s="326"/>
+      <c r="B179" s="329"/>
+      <c r="C179" s="329"/>
+      <c r="D179" s="329"/>
       <c r="E179" s="84"/>
       <c r="F179" s="70"/>
       <c r="G179" s="12"/>
@@ -10802,7 +10769,7 @@
       <c r="E180" s="116">
         <v>1968000</v>
       </c>
-      <c r="F180" s="336" t="s">
+      <c r="F180" s="330" t="s">
         <v>327</v>
       </c>
       <c r="G180" s="12"/>
@@ -10821,7 +10788,7 @@
       <c r="E181" s="116">
         <v>2952000</v>
       </c>
-      <c r="F181" s="336"/>
+      <c r="F181" s="330"/>
       <c r="G181" s="12"/>
     </row>
     <row r="182" spans="1:7" ht="66" x14ac:dyDescent="0.25">
@@ -10838,7 +10805,7 @@
       <c r="E182" s="116">
         <v>4100000</v>
       </c>
-      <c r="F182" s="336"/>
+      <c r="F182" s="330"/>
       <c r="G182" s="12"/>
     </row>
     <row r="183" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -10929,12 +10896,12 @@
       <c r="G187" s="12"/>
     </row>
     <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A188" s="326" t="s">
+      <c r="A188" s="329" t="s">
         <v>264</v>
       </c>
-      <c r="B188" s="326"/>
-      <c r="C188" s="326"/>
-      <c r="D188" s="326"/>
+      <c r="B188" s="329"/>
+      <c r="C188" s="329"/>
+      <c r="D188" s="329"/>
       <c r="E188" s="84"/>
       <c r="F188" s="70"/>
       <c r="G188" s="12"/>
@@ -10957,12 +10924,12 @@
       <c r="G189" s="12"/>
     </row>
     <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="326" t="s">
+      <c r="A190" s="329" t="s">
         <v>234</v>
       </c>
-      <c r="B190" s="326"/>
-      <c r="C190" s="326"/>
-      <c r="D190" s="326"/>
+      <c r="B190" s="329"/>
+      <c r="C190" s="329"/>
+      <c r="D190" s="329"/>
       <c r="E190" s="84"/>
       <c r="F190" s="70"/>
       <c r="G190" s="12"/>
@@ -11138,12 +11105,12 @@
       <c r="G200" s="12"/>
     </row>
     <row r="201" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="298" t="s">
+      <c r="A201" s="332" t="s">
         <v>323</v>
       </c>
-      <c r="B201" s="299"/>
-      <c r="C201" s="299"/>
-      <c r="D201" s="300"/>
+      <c r="B201" s="333"/>
+      <c r="C201" s="333"/>
+      <c r="D201" s="334"/>
       <c r="E201" s="69"/>
       <c r="F201" s="70"/>
       <c r="G201" s="12"/>
@@ -11232,12 +11199,12 @@
       <c r="G206" s="12"/>
     </row>
     <row r="207" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="298" t="s">
+      <c r="A207" s="332" t="s">
         <v>222</v>
       </c>
-      <c r="B207" s="299"/>
-      <c r="C207" s="299"/>
-      <c r="D207" s="300"/>
+      <c r="B207" s="333"/>
+      <c r="C207" s="333"/>
+      <c r="D207" s="334"/>
       <c r="E207" s="69"/>
       <c r="F207" s="70"/>
       <c r="G207" s="12"/>
@@ -11294,12 +11261,12 @@
       <c r="G210" s="12"/>
     </row>
     <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="298" t="s">
+      <c r="A211" s="332" t="s">
         <v>211</v>
       </c>
-      <c r="B211" s="299"/>
-      <c r="C211" s="299"/>
-      <c r="D211" s="300"/>
+      <c r="B211" s="333"/>
+      <c r="C211" s="333"/>
+      <c r="D211" s="334"/>
       <c r="E211" s="98"/>
       <c r="F211" s="70"/>
       <c r="G211" s="12"/>
@@ -11313,7 +11280,7 @@
         <v>212</v>
       </c>
       <c r="D212" s="36"/>
-      <c r="E212" s="338">
+      <c r="E212" s="322">
         <v>183000</v>
       </c>
       <c r="F212" s="41"/>
@@ -11328,7 +11295,7 @@
         <v>213</v>
       </c>
       <c r="D213" s="36"/>
-      <c r="E213" s="339"/>
+      <c r="E213" s="323"/>
       <c r="F213" s="41"/>
       <c r="G213" s="12"/>
     </row>
@@ -11341,7 +11308,7 @@
         <v>214</v>
       </c>
       <c r="D214" s="36"/>
-      <c r="E214" s="339"/>
+      <c r="E214" s="323"/>
       <c r="F214" s="41"/>
       <c r="G214" s="12"/>
     </row>
@@ -11354,17 +11321,17 @@
         <v>215</v>
       </c>
       <c r="D215" s="36"/>
-      <c r="E215" s="340"/>
+      <c r="E215" s="324"/>
       <c r="F215" s="41"/>
       <c r="G215" s="12"/>
     </row>
     <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="298" t="s">
+      <c r="A216" s="332" t="s">
         <v>415</v>
       </c>
-      <c r="B216" s="299"/>
-      <c r="C216" s="299"/>
-      <c r="D216" s="300"/>
+      <c r="B216" s="333"/>
+      <c r="C216" s="333"/>
+      <c r="D216" s="334"/>
       <c r="E216" s="98"/>
       <c r="F216" s="70"/>
       <c r="G216" s="12"/>
@@ -11438,64 +11405,64 @@
       <c r="F221" s="102"/>
     </row>
     <row r="222" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="337" t="s">
+      <c r="A222" s="331" t="s">
         <v>28</v>
       </c>
-      <c r="B222" s="337"/>
-      <c r="C222" s="337"/>
-      <c r="D222" s="337"/>
+      <c r="B222" s="331"/>
+      <c r="C222" s="331"/>
+      <c r="D222" s="331"/>
       <c r="E222" s="26"/>
       <c r="F222" s="103"/>
     </row>
     <row r="223" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A223" s="104"/>
-      <c r="B223" s="335" t="s">
+      <c r="B223" s="328" t="s">
         <v>267</v>
       </c>
-      <c r="C223" s="335"/>
-      <c r="D223" s="335"/>
-      <c r="E223" s="335"/>
-      <c r="F223" s="335"/>
+      <c r="C223" s="328"/>
+      <c r="D223" s="328"/>
+      <c r="E223" s="328"/>
+      <c r="F223" s="328"/>
     </row>
     <row r="224" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A224" s="104"/>
-      <c r="B224" s="335" t="s">
+      <c r="B224" s="328" t="s">
         <v>420</v>
       </c>
-      <c r="C224" s="335"/>
-      <c r="D224" s="335"/>
-      <c r="E224" s="335"/>
-      <c r="F224" s="335"/>
+      <c r="C224" s="328"/>
+      <c r="D224" s="328"/>
+      <c r="E224" s="328"/>
+      <c r="F224" s="328"/>
     </row>
     <row r="225" spans="1:6" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A225" s="105"/>
-      <c r="B225" s="335" t="s">
+      <c r="B225" s="328" t="s">
         <v>29</v>
       </c>
-      <c r="C225" s="335"/>
-      <c r="D225" s="335"/>
-      <c r="E225" s="335"/>
-      <c r="F225" s="335"/>
+      <c r="C225" s="328"/>
+      <c r="D225" s="328"/>
+      <c r="E225" s="328"/>
+      <c r="F225" s="328"/>
     </row>
     <row r="226" spans="1:6" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A226" s="106"/>
-      <c r="B226" s="341" t="s">
+      <c r="B226" s="335" t="s">
         <v>30</v>
       </c>
-      <c r="C226" s="341"/>
-      <c r="D226" s="341"/>
-      <c r="E226" s="341"/>
-      <c r="F226" s="341"/>
+      <c r="C226" s="335"/>
+      <c r="D226" s="335"/>
+      <c r="E226" s="335"/>
+      <c r="F226" s="335"/>
     </row>
     <row r="227" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A227" s="103"/>
-      <c r="B227" s="335" t="s">
+      <c r="B227" s="328" t="s">
         <v>31</v>
       </c>
-      <c r="C227" s="335"/>
-      <c r="D227" s="335"/>
-      <c r="E227" s="335"/>
-      <c r="F227" s="335"/>
+      <c r="C227" s="328"/>
+      <c r="D227" s="328"/>
+      <c r="E227" s="328"/>
+      <c r="F227" s="328"/>
     </row>
     <row r="228" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A228" s="103"/>
@@ -11559,6 +11526,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="A176:D176"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="B60:B72"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="B81:B88"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="B133:B139"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="A121:A123"/>
+    <mergeCell ref="F177:F178"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="B100:B113"/>
+    <mergeCell ref="A170:D170"/>
+    <mergeCell ref="B118:B126"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="B227:F227"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="F180:F182"/>
+    <mergeCell ref="A190:D190"/>
+    <mergeCell ref="A222:D222"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="E212:E215"/>
+    <mergeCell ref="A207:D207"/>
+    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="A201:D201"/>
     <mergeCell ref="B140:B169"/>
     <mergeCell ref="D1:F5"/>
     <mergeCell ref="A7:F7"/>
@@ -11575,59 +11595,6 @@
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="E14:E19"/>
     <mergeCell ref="F14:F19"/>
-    <mergeCell ref="B227:F227"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="F180:F182"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A222:D222"/>
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="E212:E215"/>
-    <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="G142:H142"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A121:A123"/>
-    <mergeCell ref="F177:F178"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="B100:B113"/>
-    <mergeCell ref="A170:D170"/>
-    <mergeCell ref="B118:B126"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A176:D176"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="B60:B72"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="B81:B88"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="B133:B139"/>
   </mergeCells>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="65" orientation="portrait" r:id="rId1"/>
@@ -12748,7 +12715,7 @@
       <c r="DS3" s="365"/>
     </row>
     <row r="4" spans="1:130" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="370">
+      <c r="A4" s="153">
         <v>1</v>
       </c>
       <c r="B4" s="153" t="s">
@@ -12924,7 +12891,7 @@
       </c>
     </row>
     <row r="5" spans="1:130" s="136" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="370">
+      <c r="A5" s="153">
         <v>2</v>
       </c>
       <c r="B5" s="153" t="s">
@@ -13126,7 +13093,7 @@
       </c>
     </row>
     <row r="6" spans="1:130" s="167" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="370">
+      <c r="A6" s="153">
         <v>3</v>
       </c>
       <c r="B6" s="153" t="s">
@@ -13317,7 +13284,7 @@
       </c>
     </row>
     <row r="7" spans="1:130" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="370">
+      <c r="A7" s="153">
         <v>4</v>
       </c>
       <c r="B7" s="153" t="s">
@@ -13531,7 +13498,7 @@
       </c>
     </row>
     <row r="8" spans="1:130" s="249" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="370">
+      <c r="A8" s="153">
         <v>5</v>
       </c>
       <c r="B8" s="239" t="s">
@@ -13714,7 +13681,7 @@
       </c>
     </row>
     <row r="9" spans="1:130" s="136" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="370">
+      <c r="A9" s="153">
         <v>6</v>
       </c>
       <c r="B9" s="153" t="s">
@@ -13901,7 +13868,7 @@
       </c>
     </row>
     <row r="10" spans="1:130" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="370">
+      <c r="A10" s="153">
         <v>7</v>
       </c>
       <c r="B10" s="153" t="s">
@@ -14103,7 +14070,7 @@
       </c>
     </row>
     <row r="11" spans="1:130" s="136" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="370">
+      <c r="A11" s="153">
         <v>8</v>
       </c>
       <c r="B11" s="153" t="s">
@@ -14310,7 +14277,7 @@
       </c>
     </row>
     <row r="12" spans="1:130" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="370">
+      <c r="A12" s="153">
         <v>9</v>
       </c>
       <c r="B12" s="153" t="s">
@@ -14518,7 +14485,7 @@
       </c>
     </row>
     <row r="13" spans="1:130" s="249" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="370">
+      <c r="A13" s="153">
         <v>10</v>
       </c>
       <c r="B13" s="239" t="s">
@@ -14724,7 +14691,7 @@
       </c>
     </row>
     <row r="14" spans="1:130" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="370">
+      <c r="A14" s="153">
         <v>11</v>
       </c>
       <c r="B14" s="153" t="s">
@@ -14916,7 +14883,7 @@
       </c>
     </row>
     <row r="15" spans="1:130" s="262" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="370">
+      <c r="A15" s="153">
         <v>12</v>
       </c>
       <c r="B15" s="250" t="s">
@@ -15127,7 +15094,7 @@
       </c>
     </row>
     <row r="16" spans="1:130" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="370">
+      <c r="A16" s="153">
         <v>13</v>
       </c>
       <c r="B16" s="153" t="s">
@@ -15334,7 +15301,7 @@
       </c>
     </row>
     <row r="17" spans="1:128" s="272" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="370">
+      <c r="A17" s="153">
         <v>14</v>
       </c>
       <c r="B17" s="263" t="s">
@@ -15518,7 +15485,7 @@
       </c>
     </row>
     <row r="18" spans="1:128" s="201" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="370">
+      <c r="A18" s="153">
         <v>15</v>
       </c>
       <c r="B18" s="190" t="s">
@@ -15718,7 +15685,7 @@
       </c>
     </row>
     <row r="19" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="370">
+      <c r="A19" s="153">
         <v>16</v>
       </c>
       <c r="B19" s="153" t="s">
@@ -15915,7 +15882,7 @@
       </c>
     </row>
     <row r="20" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="370">
+      <c r="A20" s="153">
         <v>17</v>
       </c>
       <c r="B20" s="153" t="s">
@@ -16105,7 +16072,7 @@
       </c>
     </row>
     <row r="21" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="370">
+      <c r="A21" s="153">
         <v>18</v>
       </c>
       <c r="B21" s="153" t="s">
@@ -16283,7 +16250,7 @@
       </c>
     </row>
     <row r="22" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="370">
+      <c r="A22" s="153">
         <v>19</v>
       </c>
       <c r="B22" s="153" t="s">
@@ -16460,7 +16427,7 @@
       </c>
     </row>
     <row r="23" spans="1:128" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="370">
+      <c r="A23" s="153">
         <v>20</v>
       </c>
       <c r="B23" s="190" t="s">
@@ -16667,7 +16634,7 @@
       </c>
     </row>
     <row r="24" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="370">
+      <c r="A24" s="153">
         <v>21</v>
       </c>
       <c r="B24" s="153" t="s">
@@ -16858,7 +16825,7 @@
       </c>
     </row>
     <row r="25" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="370">
+      <c r="A25" s="153">
         <v>22</v>
       </c>
       <c r="B25" s="153" t="s">
@@ -17046,7 +17013,7 @@
       </c>
     </row>
     <row r="26" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="370">
+      <c r="A26" s="153">
         <v>23</v>
       </c>
       <c r="B26" s="153" t="s">
@@ -17229,7 +17196,7 @@
       </c>
     </row>
     <row r="27" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="370">
+      <c r="A27" s="153">
         <v>24</v>
       </c>
       <c r="B27" s="153" t="s">
@@ -17430,7 +17397,7 @@
       </c>
     </row>
     <row r="28" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="370">
+      <c r="A28" s="153">
         <v>25</v>
       </c>
       <c r="B28" s="153" t="s">
@@ -17637,7 +17604,7 @@
       </c>
     </row>
     <row r="29" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="370">
+      <c r="A29" s="153">
         <v>26</v>
       </c>
       <c r="B29" s="153" t="s">
@@ -17811,7 +17778,7 @@
       </c>
     </row>
     <row r="30" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="370">
+      <c r="A30" s="153">
         <v>27</v>
       </c>
       <c r="B30" s="153" t="s">
@@ -17998,7 +17965,7 @@
       </c>
     </row>
     <row r="31" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="370">
+      <c r="A31" s="153">
         <v>28</v>
       </c>
       <c r="B31" s="153" t="s">
@@ -18187,7 +18154,7 @@
       </c>
     </row>
     <row r="32" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="370">
+      <c r="A32" s="153">
         <v>29</v>
       </c>
       <c r="B32" s="153" t="s">
@@ -18360,7 +18327,7 @@
       </c>
     </row>
     <row r="33" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="370">
+      <c r="A33" s="153">
         <v>30</v>
       </c>
       <c r="B33" s="153" t="s">
@@ -18549,7 +18516,7 @@
       </c>
     </row>
     <row r="34" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="370">
+      <c r="A34" s="153">
         <v>31</v>
       </c>
       <c r="B34" s="153" t="s">
@@ -18742,7 +18709,7 @@
       </c>
     </row>
     <row r="35" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="370">
+      <c r="A35" s="153">
         <v>32</v>
       </c>
       <c r="B35" s="153" t="s">
@@ -18929,7 +18896,7 @@
       </c>
     </row>
     <row r="36" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="370">
+      <c r="A36" s="153">
         <v>33</v>
       </c>
       <c r="B36" s="153" t="s">
@@ -19116,7 +19083,7 @@
       </c>
     </row>
     <row r="37" spans="1:128" s="286" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="370">
+      <c r="A37" s="153">
         <v>34</v>
       </c>
       <c r="B37" s="275" t="s">
@@ -19314,7 +19281,7 @@
       </c>
     </row>
     <row r="38" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="370">
+      <c r="A38" s="153">
         <v>35</v>
       </c>
       <c r="B38" s="153" t="s">
@@ -19561,7 +19528,7 @@
       </c>
     </row>
     <row r="39" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="370">
+      <c r="A39" s="153">
         <v>36</v>
       </c>
       <c r="B39" s="153" t="s">
@@ -19750,7 +19717,7 @@
       </c>
     </row>
     <row r="40" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="370">
+      <c r="A40" s="153">
         <v>37</v>
       </c>
       <c r="B40" s="153" t="s">
@@ -19927,7 +19894,7 @@
       </c>
     </row>
     <row r="41" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="370">
+      <c r="A41" s="153">
         <v>38</v>
       </c>
       <c r="B41" s="153" t="s">
@@ -20124,7 +20091,7 @@
       </c>
     </row>
     <row r="42" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="370">
+      <c r="A42" s="153">
         <v>39</v>
       </c>
       <c r="B42" s="153" t="s">
@@ -20315,7 +20282,7 @@
       </c>
     </row>
     <row r="43" spans="1:128" s="136" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="370">
+      <c r="A43" s="153">
         <v>40</v>
       </c>
       <c r="B43" s="153" t="s">
@@ -20516,7 +20483,7 @@
       </c>
     </row>
     <row r="44" spans="1:128" s="238" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="370">
+      <c r="A44" s="153">
         <v>41</v>
       </c>
       <c r="B44" s="227" t="s">
@@ -20732,7 +20699,7 @@
       </c>
     </row>
     <row r="45" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="370">
+      <c r="A45" s="153">
         <v>42</v>
       </c>
       <c r="B45" s="153" t="s">
@@ -20927,7 +20894,7 @@
       </c>
     </row>
     <row r="46" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="370">
+      <c r="A46" s="153">
         <v>43</v>
       </c>
       <c r="B46" s="153" t="s">
@@ -21130,7 +21097,7 @@
       </c>
     </row>
     <row r="47" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="370">
+      <c r="A47" s="153">
         <v>44</v>
       </c>
       <c r="B47" s="153" t="s">
@@ -21327,7 +21294,7 @@
       </c>
     </row>
     <row r="48" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="370">
+      <c r="A48" s="153">
         <v>45</v>
       </c>
       <c r="B48" s="153" t="s">
@@ -21534,7 +21501,7 @@
       </c>
     </row>
     <row r="49" spans="1:128" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="370">
+      <c r="A49" s="153">
         <v>46</v>
       </c>
       <c r="B49" s="190" t="s">
@@ -21750,7 +21717,7 @@
       </c>
     </row>
     <row r="50" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="370">
+      <c r="A50" s="153">
         <v>47</v>
       </c>
       <c r="B50" s="153" t="s">
@@ -21951,7 +21918,7 @@
       </c>
     </row>
     <row r="51" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="370">
+      <c r="A51" s="153">
         <v>48</v>
       </c>
       <c r="B51" s="153" t="s">
@@ -22124,7 +22091,7 @@
       </c>
     </row>
     <row r="52" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="370">
+      <c r="A52" s="153">
         <v>49</v>
       </c>
       <c r="B52" s="153" t="s">
@@ -22307,7 +22274,7 @@
       </c>
     </row>
     <row r="53" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="370">
+      <c r="A53" s="153">
         <v>50</v>
       </c>
       <c r="B53" s="153" t="s">
@@ -22500,7 +22467,7 @@
       </c>
     </row>
     <row r="54" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="370">
+      <c r="A54" s="153">
         <v>51</v>
       </c>
       <c r="B54" s="153" t="s">
@@ -22699,7 +22666,7 @@
       </c>
     </row>
     <row r="55" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="370">
+      <c r="A55" s="153">
         <v>52</v>
       </c>
       <c r="B55" s="153" t="s">
@@ -22908,7 +22875,7 @@
       </c>
     </row>
     <row r="56" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="370">
+      <c r="A56" s="153">
         <v>53</v>
       </c>
       <c r="B56" s="153" t="s">
@@ -23109,7 +23076,7 @@
       </c>
     </row>
     <row r="57" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="370">
+      <c r="A57" s="153">
         <v>54</v>
       </c>
       <c r="B57" s="153" t="s">
@@ -23312,7 +23279,7 @@
       </c>
     </row>
     <row r="58" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="370">
+      <c r="A58" s="153">
         <v>55</v>
       </c>
       <c r="B58" s="153" t="s">
@@ -23495,7 +23462,7 @@
       </c>
     </row>
     <row r="59" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="370">
+      <c r="A59" s="153">
         <v>56</v>
       </c>
       <c r="B59" s="153" t="s">
@@ -23684,7 +23651,7 @@
       </c>
     </row>
     <row r="60" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="370">
+      <c r="A60" s="153">
         <v>57</v>
       </c>
       <c r="B60" s="153" t="s">
@@ -23886,7 +23853,7 @@
       </c>
     </row>
     <row r="61" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="370">
+      <c r="A61" s="153">
         <v>58</v>
       </c>
       <c r="B61" s="153" t="s">
@@ -24079,7 +24046,7 @@
       </c>
     </row>
     <row r="62" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="370">
+      <c r="A62" s="153">
         <v>59</v>
       </c>
       <c r="B62" s="153" t="s">
@@ -24268,7 +24235,7 @@
       </c>
     </row>
     <row r="63" spans="1:128" s="201" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="370">
+      <c r="A63" s="153">
         <v>60</v>
       </c>
       <c r="B63" s="190" t="s">
@@ -24482,7 +24449,7 @@
       </c>
     </row>
     <row r="64" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="370">
+      <c r="A64" s="153">
         <v>61</v>
       </c>
       <c r="B64" s="153" t="s">
@@ -24691,7 +24658,7 @@
       </c>
     </row>
     <row r="65" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="370">
+      <c r="A65" s="153">
         <v>62</v>
       </c>
       <c r="B65" s="153" t="s">
@@ -24902,7 +24869,7 @@
       </c>
     </row>
     <row r="66" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="370">
+      <c r="A66" s="153">
         <v>63</v>
       </c>
       <c r="B66" s="153" t="s">
@@ -25090,7 +25057,7 @@
       </c>
     </row>
     <row r="67" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="370">
+      <c r="A67" s="153">
         <v>64</v>
       </c>
       <c r="B67" s="153" t="s">
@@ -25312,7 +25279,7 @@
       </c>
     </row>
     <row r="68" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="370">
+      <c r="A68" s="153">
         <v>65</v>
       </c>
       <c r="B68" s="153" t="s">
@@ -25505,7 +25472,7 @@
       </c>
     </row>
     <row r="69" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="370">
+      <c r="A69" s="153">
         <v>66</v>
       </c>
       <c r="B69" s="153" t="s">
@@ -25709,7 +25676,7 @@
       </c>
     </row>
     <row r="70" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="370">
+      <c r="A70" s="153">
         <v>67</v>
       </c>
       <c r="B70" s="153" t="s">
@@ -25916,7 +25883,7 @@
       </c>
     </row>
     <row r="71" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="370">
+      <c r="A71" s="153">
         <v>68</v>
       </c>
       <c r="B71" s="153" t="s">
@@ -26095,7 +26062,7 @@
       </c>
     </row>
     <row r="72" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="370">
+      <c r="A72" s="153">
         <v>69</v>
       </c>
       <c r="B72" s="153" t="s">
@@ -26278,7 +26245,7 @@
       </c>
     </row>
     <row r="73" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="370">
+      <c r="A73" s="153">
         <v>70</v>
       </c>
       <c r="B73" s="153" t="s">
@@ -26479,7 +26446,7 @@
       </c>
     </row>
     <row r="74" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="370">
+      <c r="A74" s="153">
         <v>71</v>
       </c>
       <c r="B74" s="153" t="s">
@@ -26630,7 +26597,7 @@
       </c>
     </row>
     <row r="75" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="370">
+      <c r="A75" s="153">
         <v>72</v>
       </c>
       <c r="B75" s="153" t="s">
@@ -26781,7 +26748,7 @@
       </c>
     </row>
     <row r="76" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="370">
+      <c r="A76" s="153">
         <v>73</v>
       </c>
       <c r="B76" s="153" t="s">
@@ -26932,7 +26899,7 @@
       </c>
     </row>
     <row r="77" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="370">
+      <c r="A77" s="153">
         <v>74</v>
       </c>
       <c r="B77" s="153" t="s">
@@ -27080,7 +27047,7 @@
       </c>
     </row>
     <row r="78" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="370">
+      <c r="A78" s="153">
         <v>75</v>
       </c>
       <c r="B78" s="153" t="s">
@@ -27231,7 +27198,7 @@
       </c>
     </row>
     <row r="79" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="370">
+      <c r="A79" s="153">
         <v>76</v>
       </c>
       <c r="B79" s="153" t="s">
@@ -27382,7 +27349,7 @@
       </c>
     </row>
     <row r="80" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="370">
+      <c r="A80" s="153">
         <v>77</v>
       </c>
       <c r="B80" s="153" t="s">
@@ -27533,7 +27500,7 @@
       </c>
     </row>
     <row r="81" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="370">
+      <c r="A81" s="153">
         <v>78</v>
       </c>
       <c r="B81" s="153" t="s">
@@ -27684,7 +27651,7 @@
       </c>
     </row>
     <row r="82" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="370">
+      <c r="A82" s="153">
         <v>79</v>
       </c>
       <c r="B82" s="153" t="s">
@@ -27835,7 +27802,7 @@
       </c>
     </row>
     <row r="83" spans="1:128" s="136" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="370">
+      <c r="A83" s="153">
         <v>80</v>
       </c>
       <c r="B83" s="153" t="s">
@@ -28473,7 +28440,7 @@
   </mergeCells>
   <phoneticPr fontId="29" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576 DZ1:DZ1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="J8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -30089,11 +30056,11 @@
   </sheetData>
   <autoFilter ref="A1:F81" xr:uid="{91D9F8ED-8F98-4628-A2C6-06CCD6FEFC96}">
     <filterColumn colId="0">
-      <colorFilter dxfId="6"/>
+      <colorFilter dxfId="3"/>
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="A1:A1048576 F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
